--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\601\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201AE733-E9A8-40C4-9094-E5C3190E0905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C4577A-6E1B-4035-9FE6-6F1791CF9982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4875" yWindow="4545" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BallParam" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
+    <author>Hannya T</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -80,6 +81,16 @@
           <t>Int
 Base crit multiplier of the ball</t>
         </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>, number here is viewed multiplicative, so 1.25 critDmg means that the ball will deal 125% damage compare to an uncrit attack.</t>
+        </r>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
@@ -136,6 +147,16 @@
           <t>String
 Skill ID</t>
         </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>, accociated with/referenced to an independent script</t>
+        </r>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
@@ -168,6 +189,55 @@
         </r>
       </text>
     </comment>
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{0CCE79F3-1155-4C1C-8F25-B37B627ECE9E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+The ball model's prefab ID for display</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{8C88C202-BB75-499A-9EB1-FAE2E4677B5C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+The ball icon's image ID for reference
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
@@ -177,7 +247,26 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Leave a fire trail when moving, dealing {Skilldamage} damage to the enemy within. The trial will last {Skillduration} seconds.
+          <t>Leave a fire trail when moving, dealing {Skilldamage} damage to the enemy within</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> per second</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">. The trial will last {Skillduration} seconds.
 </t>
         </r>
       </text>
@@ -191,7 +280,45 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The pinball will split into {Skillsplitcount} balls, each ball being able to split again once each of them reaches the point requirement again, but the next proc will require {Skillmultiplier} times more points.</t>
+          <t>The pinball will split into {Skill</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>effect</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>} balls, each ball being able to split again once each of them reaches the point requirement again, but the next proc will require {Skill</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>duration</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>} times more points.</t>
         </r>
       </text>
     </comment>
@@ -208,12 +335,60 @@
         </r>
       </text>
     </comment>
+    <comment ref="I10" authorId="1" shapeId="0" xr:uid="{C3C1EE87-3600-48BF-95EE-2FCCF973ADEB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Enemies within the area's movement speed will be reduced to zero. The area effect is {Skilleffect}(size multiplier), and the zone lasts{Skillduration}.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="1" shapeId="0" xr:uid="{660AC235-CB6E-4635-9325-C941676635C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Summons an invisible area surrounding the ball. The area will strike down lightning bolts to enemies contacted, dealing ball's base attack value to them. The area size is {Skilleffect}, and lasts {Skillduration}.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -269,9 +444,6 @@
     <t>Fireball</t>
   </si>
   <si>
-    <t>FireTrail</t>
-  </si>
-  <si>
     <t>Splitball</t>
   </si>
   <si>
@@ -281,13 +453,7 @@
     <t>Spikeball</t>
   </si>
   <si>
-    <t>Spikeblast</t>
-  </si>
-  <si>
     <t>Radiantball</t>
-  </si>
-  <si>
-    <t>Radiantspark</t>
   </si>
   <si>
     <t>float</t>
@@ -318,27 +484,152 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Normal pinball</t>
+    <t>BallIcon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A pinball with fire</t>
+    <t>Stentball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A pinball can split</t>
+    <t>Drops a fire trail that deals damage to enemies within overtime.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A pinball with spike?</t>
+    <t>Good old basic. Does not have any effect, but it's reliable in every aspect.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>A pinball with a special skill</t>
+    <t>Unleashes a ring of spikes that go through terrains and damages all collided enemies.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>BallIcon</t>
+    <t>A very round and shiny ball. Reminds you a certain someone that does not respond to messages often.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stenball</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passively has a bigger light radius.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Split into 2 smaller balls when triggered. Upon splitting, each individual ball can split again and again, but each split will requires more points.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iceball</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Freeze circle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as skill effect vfx.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drop an icy zone that stops enemies from moving within.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lightningball</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightningAura</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpikeBlast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IceZone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Plexus AoE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as skill effect vfx.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Infuse itself with lightning power for a duration, summons lightnings to strike down nearby enemies, dealing ball's attack damage to them.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireTrail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CFXR2 Firewall A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as skill effect vfx.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -346,7 +637,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -380,6 +671,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -401,7 +713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -412,9 +724,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -631,13 +949,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="34.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="69.33203125" customWidth="1"/>
+    <col min="15" max="15" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,15 +991,15 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
-      <c r="O1" s="1"/>
+      <c r="O1" s="2"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -696,7 +1015,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -707,16 +1026,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -731,13 +1050,13 @@
         <v>13</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -755,7 +1074,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -788,7 +1107,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -821,7 +1140,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -839,7 +1158,7 @@
         <v>1.5</v>
       </c>
       <c r="G5" s="1">
-        <v>1.5</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -852,13 +1171,13 @@
         <v>80</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -867,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="1">
         <v>1.25</v>
@@ -875,14 +1194,14 @@
       <c r="F6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" s="1">
-        <v>2</v>
+      <c r="G6" s="2">
+        <v>1.05</v>
       </c>
       <c r="H6" s="1">
         <v>500</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>18</v>
+      <c r="I6" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
@@ -891,15 +1210,17 @@
         <v>60</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>33</v>
+      <c r="M6" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="1"/>
+      <c r="O6" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -915,10 +1236,10 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
@@ -939,7 +1260,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1">
         <v>400</v>
@@ -948,13 +1269,13 @@
         <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>34</v>
+      <c r="M7" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -972,10 +1293,10 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>12</v>
@@ -990,28 +1311,28 @@
         <v>1.5</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>22</v>
+      <c r="I8" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
       </c>
       <c r="K8" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>35</v>
+      <c r="M8" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1029,16 +1350,16 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
       </c>
       <c r="D9" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="1">
         <v>1.25</v>
@@ -1047,14 +1368,12 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="1">
         <v>300</v>
       </c>
@@ -1062,15 +1381,17 @@
         <v>60</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -1086,22 +1407,50 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>750</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="1">
+        <v>200</v>
+      </c>
+      <c r="K10" s="1">
+        <v>70</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1117,22 +1466,50 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="1">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H11" s="1">
+        <v>900</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="1">
+        <v>800</v>
+      </c>
+      <c r="K11" s="1">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1148,7 +1525,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1179,7 +1556,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1210,7 +1587,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1241,7 +1618,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1272,7 +1649,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1303,7 +1680,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1334,7 +1711,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1365,7 +1742,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1396,7 +1773,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1427,7 +1804,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1458,7 +1835,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1489,7 +1866,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1520,7 +1897,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1551,7 +1928,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1582,7 +1959,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1613,7 +1990,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1644,7 +2021,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1675,7 +2052,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1706,7 +2083,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1737,7 +2114,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1768,7 +2145,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1799,7 +2176,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1830,7 +2207,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1861,7 +2238,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1892,7 +2269,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1923,7 +2300,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1954,7 +2331,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1985,7 +2362,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2016,7 +2393,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2047,7 +2424,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2078,7 +2455,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2109,7 +2486,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2140,7 +2517,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2171,7 +2548,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2202,7 +2579,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2233,7 +2610,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2264,7 +2641,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2295,7 +2672,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2326,7 +2703,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2357,7 +2734,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2388,7 +2765,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2419,7 +2796,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2450,7 +2827,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2481,7 +2858,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2512,7 +2889,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2543,7 +2920,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2574,7 +2951,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2605,7 +2982,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2636,7 +3013,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2667,7 +3044,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2698,7 +3075,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2729,7 +3106,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2760,7 +3137,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2791,7 +3168,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2822,7 +3199,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2853,7 +3230,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2884,7 +3261,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2915,7 +3292,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2946,7 +3323,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2977,7 +3354,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3008,7 +3385,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3039,7 +3416,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3070,7 +3447,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3101,7 +3478,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3132,7 +3509,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3163,7 +3540,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3194,7 +3571,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3225,7 +3602,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3256,7 +3633,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3287,7 +3664,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3318,7 +3695,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3349,7 +3726,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3380,7 +3757,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3411,7 +3788,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3442,7 +3819,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3473,7 +3850,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3504,7 +3881,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3535,7 +3912,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3566,7 +3943,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3597,7 +3974,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3628,7 +4005,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3659,7 +4036,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3690,7 +4067,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3721,7 +4098,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3752,7 +4129,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3783,7 +4160,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3814,7 +4191,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3845,7 +4222,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3876,7 +4253,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3907,7 +4284,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3938,7 +4315,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3969,7 +4346,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4000,7 +4377,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4031,7 +4408,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4062,7 +4439,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4093,7 +4470,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4124,7 +4501,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4155,7 +4532,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4186,7 +4563,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4217,7 +4594,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4248,7 +4625,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4279,7 +4656,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4310,7 +4687,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4341,7 +4718,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4372,7 +4749,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4403,7 +4780,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4434,7 +4811,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4465,7 +4842,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4496,7 +4873,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4527,7 +4904,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4558,7 +4935,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4589,7 +4966,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4620,7 +4997,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4651,7 +5028,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4682,7 +5059,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4713,7 +5090,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4744,7 +5121,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4775,7 +5152,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4806,7 +5183,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4837,7 +5214,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4868,7 +5245,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4899,7 +5276,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4930,7 +5307,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4961,7 +5338,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4992,7 +5369,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5023,7 +5400,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5054,7 +5431,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5085,7 +5462,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5116,7 +5493,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5147,7 +5524,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5178,7 +5555,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5209,7 +5586,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5240,7 +5617,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5271,7 +5648,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5302,7 +5679,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5333,7 +5710,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5364,7 +5741,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5395,7 +5772,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5426,7 +5803,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5457,7 +5834,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5488,7 +5865,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5519,7 +5896,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5550,7 +5927,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5581,7 +5958,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5612,7 +5989,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5643,7 +6020,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5674,7 +6051,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5705,7 +6082,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5736,7 +6113,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5767,7 +6144,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5798,7 +6175,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5829,7 +6206,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5860,7 +6237,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5891,7 +6268,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5922,7 +6299,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5953,7 +6330,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5984,7 +6361,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6015,7 +6392,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6046,7 +6423,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6077,7 +6454,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6108,7 +6485,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6139,7 +6516,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6170,7 +6547,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6201,7 +6578,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6232,7 +6609,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6263,7 +6640,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6294,7 +6671,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6325,7 +6702,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6356,7 +6733,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6387,7 +6764,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6418,7 +6795,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6449,7 +6826,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6480,7 +6857,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6511,7 +6888,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6542,7 +6919,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6573,7 +6950,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6604,7 +6981,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6635,7 +7012,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6666,7 +7043,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6697,7 +7074,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6728,7 +7105,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6759,7 +7136,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6790,7 +7167,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6821,7 +7198,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6852,7 +7229,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6883,7 +7260,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6914,7 +7291,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6945,7 +7322,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6976,7 +7353,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7007,7 +7384,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7038,7 +7415,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7069,7 +7446,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7100,7 +7477,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7131,7 +7508,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7162,7 +7539,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7193,7 +7570,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7224,7 +7601,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7255,7 +7632,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7286,7 +7663,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7317,7 +7694,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7348,7 +7725,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7379,7 +7756,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7410,7 +7787,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7441,7 +7818,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7472,7 +7849,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7503,7 +7880,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7534,7 +7911,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7565,7 +7942,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7596,7 +7973,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7627,7 +8004,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7658,7 +8035,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7689,7 +8066,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7720,7 +8097,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7751,7 +8128,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7782,7 +8159,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7813,7 +8190,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7844,7 +8221,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7875,7 +8252,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7906,7 +8283,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7937,7 +8314,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7968,7 +8345,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7999,7 +8376,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8030,7 +8407,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8061,7 +8438,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8092,7 +8469,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8123,7 +8500,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8154,7 +8531,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8185,7 +8562,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8216,7 +8593,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8247,7 +8624,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8278,7 +8655,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8309,7 +8686,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8340,7 +8717,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8371,7 +8748,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8402,7 +8779,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8433,7 +8810,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8464,7 +8841,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8495,7 +8872,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8526,7 +8903,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8557,7 +8934,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8588,7 +8965,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8619,7 +8996,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8650,7 +9027,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8681,7 +9058,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8712,7 +9089,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8743,7 +9120,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8774,7 +9151,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8805,7 +9182,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8836,7 +9213,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -8867,7 +9244,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -8898,7 +9275,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -8929,7 +9306,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -8960,7 +9337,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -8991,7 +9368,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9022,7 +9399,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9053,7 +9430,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9084,7 +9461,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9115,7 +9492,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9146,7 +9523,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9177,7 +9554,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9208,7 +9585,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9239,7 +9616,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9270,7 +9647,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9301,7 +9678,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9332,7 +9709,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9363,7 +9740,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9394,7 +9771,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9425,7 +9802,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9456,7 +9833,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9487,7 +9864,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9518,7 +9895,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9549,7 +9926,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9580,7 +9957,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9611,7 +9988,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -9642,7 +10019,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -9673,7 +10050,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -9704,7 +10081,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -9735,7 +10112,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -9766,7 +10143,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -9797,7 +10174,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -9828,7 +10205,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -9859,7 +10236,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -9890,7 +10267,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -9921,7 +10298,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -9952,7 +10329,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -9983,7 +10360,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10014,7 +10391,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10045,7 +10422,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10076,7 +10453,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10107,7 +10484,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10138,7 +10515,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10169,7 +10546,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10200,7 +10577,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10231,7 +10608,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10262,7 +10639,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10293,7 +10670,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10324,7 +10701,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10355,7 +10732,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10386,7 +10763,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10417,7 +10794,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10448,7 +10825,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10479,7 +10856,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10510,7 +10887,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10541,7 +10918,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10572,7 +10949,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10603,7 +10980,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -10634,7 +11011,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -10665,7 +11042,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -10696,7 +11073,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -10727,7 +11104,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -10758,7 +11135,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -10789,7 +11166,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -10820,7 +11197,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -10851,7 +11228,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -10882,7 +11259,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -10913,7 +11290,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -10944,7 +11321,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -10975,7 +11352,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11006,7 +11383,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11037,7 +11414,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11068,7 +11445,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11099,7 +11476,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11130,7 +11507,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11161,7 +11538,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11192,7 +11569,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11223,7 +11600,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11254,7 +11631,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11285,7 +11662,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11316,7 +11693,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11347,7 +11724,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11378,7 +11755,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11409,7 +11786,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11440,7 +11817,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11471,7 +11848,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11502,7 +11879,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11533,7 +11910,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11564,7 +11941,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11595,7 +11972,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11626,7 +12003,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11657,7 +12034,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11688,7 +12065,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11719,7 +12096,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -11750,7 +12127,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -11781,7 +12158,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -11812,7 +12189,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -11843,7 +12220,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -11874,7 +12251,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -11905,7 +12282,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -11936,7 +12313,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -11967,7 +12344,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -11998,7 +12375,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12029,7 +12406,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12060,7 +12437,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12091,7 +12468,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12122,7 +12499,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12153,7 +12530,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12184,7 +12561,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12215,7 +12592,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12246,7 +12623,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12277,7 +12654,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12308,7 +12685,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12339,7 +12716,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12370,7 +12747,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12401,7 +12778,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12432,7 +12809,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12463,7 +12840,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12494,7 +12871,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12525,7 +12902,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12556,7 +12933,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12587,7 +12964,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12618,7 +12995,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12649,7 +13026,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12680,7 +13057,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12711,7 +13088,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12742,7 +13119,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12773,7 +13150,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12804,7 +13181,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12835,7 +13212,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -12866,7 +13243,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -12897,7 +13274,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -12928,7 +13305,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -12959,7 +13336,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -12990,7 +13367,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13021,7 +13398,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13052,7 +13429,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13083,7 +13460,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13114,7 +13491,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13145,7 +13522,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13176,7 +13553,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13207,7 +13584,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13238,7 +13615,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13269,7 +13646,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13300,7 +13677,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13331,7 +13708,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13362,7 +13739,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13393,7 +13770,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13424,7 +13801,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13455,7 +13832,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13486,7 +13863,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13517,7 +13894,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13548,7 +13925,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13579,7 +13956,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13610,7 +13987,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13641,7 +14018,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13672,7 +14049,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13703,7 +14080,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13734,7 +14111,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13765,7 +14142,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13796,7 +14173,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13827,7 +14204,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13858,7 +14235,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13889,7 +14266,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13920,7 +14297,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13951,7 +14328,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -13982,7 +14359,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14013,7 +14390,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14044,7 +14421,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14075,7 +14452,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14106,7 +14483,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14137,7 +14514,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14168,7 +14545,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14199,7 +14576,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14230,7 +14607,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14261,7 +14638,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14292,7 +14669,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14323,7 +14700,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14354,7 +14731,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14385,7 +14762,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14416,7 +14793,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14447,7 +14824,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14478,7 +14855,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14509,7 +14886,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14540,7 +14917,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14571,7 +14948,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14602,7 +14979,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14633,7 +15010,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14664,7 +15041,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14695,7 +15072,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14726,7 +15103,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14757,7 +15134,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14788,7 +15165,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14819,7 +15196,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14850,7 +15227,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14881,7 +15258,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14912,7 +15289,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14943,7 +15320,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14974,7 +15351,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15005,7 +15382,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15036,7 +15413,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15067,7 +15444,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15098,7 +15475,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15129,7 +15506,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15160,7 +15537,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15191,7 +15568,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15222,7 +15599,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15253,7 +15630,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15284,7 +15661,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15315,7 +15692,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15346,7 +15723,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15377,7 +15754,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15408,7 +15785,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15439,7 +15816,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15470,7 +15847,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15501,7 +15878,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15532,7 +15909,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15563,7 +15940,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15594,7 +15971,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15625,7 +16002,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15656,7 +16033,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15687,7 +16064,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15718,7 +16095,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15749,7 +16126,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15780,7 +16157,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15811,7 +16188,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15842,7 +16219,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15873,7 +16250,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15904,7 +16281,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15935,7 +16312,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15966,7 +16343,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15997,7 +16374,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16028,7 +16405,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16059,7 +16436,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16090,7 +16467,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16121,7 +16498,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16152,7 +16529,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16183,7 +16560,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16214,7 +16591,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16245,7 +16622,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16276,7 +16653,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16307,7 +16684,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16338,7 +16715,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16369,7 +16746,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16400,7 +16777,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16431,7 +16808,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16462,7 +16839,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16493,7 +16870,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16524,7 +16901,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16555,7 +16932,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16586,7 +16963,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16617,7 +16994,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16648,7 +17025,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16679,7 +17056,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16710,7 +17087,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16741,7 +17118,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16772,7 +17149,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16803,7 +17180,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16834,7 +17211,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16865,7 +17242,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16896,7 +17273,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16927,7 +17304,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16958,7 +17335,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16989,7 +17366,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17020,7 +17397,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17051,7 +17428,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17082,7 +17459,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17113,7 +17490,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17144,7 +17521,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17175,7 +17552,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17206,7 +17583,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17237,7 +17614,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17268,7 +17645,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17299,7 +17676,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17330,7 +17707,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17361,7 +17738,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17392,7 +17769,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17423,7 +17800,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17454,7 +17831,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17485,7 +17862,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17516,7 +17893,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17547,7 +17924,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17578,7 +17955,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17609,7 +17986,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17640,7 +18017,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17671,7 +18048,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17702,7 +18079,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17733,7 +18110,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17764,7 +18141,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17795,7 +18172,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17826,7 +18203,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17857,7 +18234,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17888,7 +18265,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17919,7 +18296,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17950,7 +18327,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17981,7 +18358,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18012,7 +18389,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18043,7 +18420,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18074,7 +18451,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18105,7 +18482,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18136,7 +18513,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18167,7 +18544,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18198,7 +18575,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18229,7 +18606,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18260,7 +18637,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18291,7 +18668,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18322,7 +18699,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18353,7 +18730,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18384,7 +18761,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18415,7 +18792,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18446,7 +18823,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18477,7 +18854,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18508,7 +18885,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18539,7 +18916,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18570,7 +18947,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18601,7 +18978,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18632,7 +19009,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18663,7 +19040,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18694,7 +19071,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18725,7 +19102,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18756,7 +19133,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18787,7 +19164,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18818,7 +19195,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18849,7 +19226,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18880,7 +19257,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18911,7 +19288,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18942,7 +19319,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18973,7 +19350,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19004,7 +19381,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19035,7 +19412,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19066,7 +19443,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19097,7 +19474,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19128,7 +19505,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19159,7 +19536,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19190,7 +19567,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19221,7 +19598,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19252,7 +19629,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19283,7 +19660,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19314,7 +19691,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19345,7 +19722,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19376,7 +19753,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19407,7 +19784,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19438,7 +19815,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19469,7 +19846,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19500,7 +19877,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19531,7 +19908,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19562,7 +19939,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19593,7 +19970,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19624,7 +20001,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19655,7 +20032,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19686,7 +20063,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19717,7 +20094,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19748,7 +20125,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19779,7 +20156,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19810,7 +20187,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19841,7 +20218,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19872,7 +20249,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19903,7 +20280,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19934,7 +20311,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19965,7 +20342,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19996,7 +20373,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20027,7 +20404,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20058,7 +20435,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20089,7 +20466,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20120,7 +20497,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20151,7 +20528,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20182,7 +20559,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20213,7 +20590,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20244,7 +20621,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20275,7 +20652,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20306,7 +20683,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20337,7 +20714,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20368,7 +20745,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20399,7 +20776,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20430,7 +20807,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20461,7 +20838,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20492,7 +20869,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20523,7 +20900,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20554,7 +20931,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20585,7 +20962,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20616,7 +20993,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20647,7 +21024,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20678,7 +21055,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20709,7 +21086,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20740,7 +21117,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20771,7 +21148,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20802,7 +21179,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20833,7 +21210,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20864,7 +21241,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20895,7 +21272,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20926,7 +21303,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20957,7 +21334,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20988,7 +21365,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21019,7 +21396,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21050,7 +21427,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21081,7 +21458,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21112,7 +21489,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21143,7 +21520,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21174,7 +21551,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21205,7 +21582,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21236,7 +21613,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21267,7 +21644,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21298,7 +21675,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21329,7 +21706,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21360,7 +21737,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21391,7 +21768,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21422,7 +21799,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21453,7 +21830,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21484,7 +21861,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21515,7 +21892,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21546,7 +21923,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21577,7 +21954,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21608,7 +21985,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -21639,7 +22016,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -21670,7 +22047,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -21701,7 +22078,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21732,7 +22109,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21763,7 +22140,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21794,7 +22171,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21825,7 +22202,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21856,7 +22233,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21887,7 +22264,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21918,7 +22295,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21949,7 +22326,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21980,7 +22357,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22011,7 +22388,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22042,7 +22419,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22073,7 +22450,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22104,7 +22481,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22135,7 +22512,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22166,7 +22543,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22197,7 +22574,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22228,7 +22605,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22259,7 +22636,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22290,7 +22667,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22321,7 +22698,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22352,7 +22729,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22383,7 +22760,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22414,7 +22791,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22445,7 +22822,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22476,7 +22853,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22507,7 +22884,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22538,7 +22915,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22569,7 +22946,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22600,7 +22977,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -22631,7 +23008,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -22662,7 +23039,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -22693,7 +23070,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -22724,7 +23101,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -22755,7 +23132,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -22786,7 +23163,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22817,7 +23194,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22848,7 +23225,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22879,7 +23256,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22910,7 +23287,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22941,7 +23318,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22972,7 +23349,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23003,7 +23380,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23034,7 +23411,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23065,7 +23442,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23096,7 +23473,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23127,7 +23504,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23158,7 +23535,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23189,7 +23566,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23220,7 +23597,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23251,7 +23628,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23282,7 +23659,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23313,7 +23690,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23344,7 +23721,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23375,7 +23752,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23406,7 +23783,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23437,7 +23814,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23468,7 +23845,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23499,7 +23876,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23530,7 +23907,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -23561,7 +23938,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -23592,7 +23969,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -23623,7 +24000,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -23654,7 +24031,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -23685,7 +24062,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -23716,7 +24093,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -23747,7 +24124,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -23778,7 +24155,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -23809,7 +24186,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -23840,7 +24217,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -23871,7 +24248,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -23902,7 +24279,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23933,7 +24310,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23964,7 +24341,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23995,7 +24372,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24026,7 +24403,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24057,7 +24434,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24088,7 +24465,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24119,7 +24496,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24150,7 +24527,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24181,7 +24558,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24212,7 +24589,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24243,7 +24620,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24274,7 +24651,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24305,7 +24682,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24336,7 +24713,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24367,7 +24744,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24398,7 +24775,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24429,7 +24806,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24460,7 +24837,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24491,7 +24868,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24522,7 +24899,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -24553,7 +24930,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -24584,7 +24961,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -24615,7 +24992,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -24646,7 +25023,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -24677,7 +25054,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -24708,7 +25085,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -24739,7 +25116,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -24770,7 +25147,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -24801,7 +25178,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -24832,7 +25209,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -24863,7 +25240,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -24894,7 +25271,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -24925,7 +25302,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -24956,7 +25333,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -24987,7 +25364,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25018,7 +25395,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25049,7 +25426,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25080,7 +25457,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25111,7 +25488,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25142,7 +25519,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25173,7 +25550,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25204,7 +25581,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25235,7 +25612,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25266,7 +25643,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25297,7 +25674,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25328,7 +25705,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25359,7 +25736,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25390,7 +25767,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25421,7 +25798,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25452,7 +25829,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25483,7 +25860,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -25514,7 +25891,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -25545,7 +25922,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -25576,7 +25953,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -25607,7 +25984,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -25638,7 +26015,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -25669,7 +26046,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -25700,7 +26077,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -25731,7 +26108,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -25762,7 +26139,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -25793,7 +26170,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -25824,7 +26201,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -25855,7 +26232,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -25886,7 +26263,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -25917,7 +26294,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -25948,7 +26325,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -25979,7 +26356,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26010,7 +26387,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26041,7 +26418,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26072,7 +26449,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26103,7 +26480,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26134,7 +26511,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26165,7 +26542,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26196,7 +26573,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26227,7 +26604,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26258,7 +26635,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26289,7 +26666,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26320,7 +26697,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26351,7 +26728,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26382,7 +26759,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26413,7 +26790,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26444,7 +26821,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -26475,7 +26852,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -26506,7 +26883,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -26537,7 +26914,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -26568,7 +26945,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -26599,7 +26976,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -26630,7 +27007,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -26661,7 +27038,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -26692,7 +27069,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -26723,7 +27100,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -26754,7 +27131,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -26785,7 +27162,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -26816,7 +27193,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -26847,7 +27224,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -26878,7 +27255,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -26909,7 +27286,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -26940,7 +27317,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -26971,7 +27348,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27002,7 +27379,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27033,7 +27410,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27064,7 +27441,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27095,7 +27472,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27126,7 +27503,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27157,7 +27534,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27188,7 +27565,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27219,7 +27596,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27250,7 +27627,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27281,7 +27658,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27312,7 +27689,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27343,7 +27720,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27374,7 +27751,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27405,7 +27782,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -27436,7 +27813,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -27467,7 +27844,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -27498,7 +27875,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -27529,7 +27906,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -27560,7 +27937,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -27591,7 +27968,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -27622,7 +27999,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -27653,7 +28030,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -27684,7 +28061,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -27715,7 +28092,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -27746,7 +28123,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -27777,7 +28154,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -27808,7 +28185,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -27839,7 +28216,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -27870,7 +28247,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -27901,7 +28278,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -27932,7 +28309,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -27963,7 +28340,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -27994,7 +28371,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28025,7 +28402,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28056,7 +28433,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28087,7 +28464,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28118,7 +28495,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28149,7 +28526,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28180,7 +28557,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28211,7 +28588,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28242,7 +28619,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28273,7 +28650,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28304,7 +28681,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28335,7 +28712,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28366,7 +28743,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28397,7 +28774,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -28428,7 +28805,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -28459,7 +28836,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -28490,7 +28867,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -28521,7 +28898,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -28552,7 +28929,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -28583,7 +28960,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -28614,7 +28991,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -28645,7 +29022,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -28676,7 +29053,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -28707,7 +29084,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -28738,7 +29115,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -28769,7 +29146,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -28800,7 +29177,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -28831,7 +29208,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -28862,7 +29239,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -28893,7 +29270,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -28924,7 +29301,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -28955,7 +29332,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -28986,7 +29363,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29017,7 +29394,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29048,7 +29425,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29079,7 +29456,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29110,7 +29487,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29141,7 +29518,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29172,7 +29549,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29203,7 +29580,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29234,7 +29611,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29265,7 +29642,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29296,7 +29673,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29327,7 +29704,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29358,7 +29735,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -29389,7 +29766,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -29420,7 +29797,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -29451,7 +29828,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -29482,7 +29859,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -29513,7 +29890,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -29544,7 +29921,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -29575,7 +29952,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -29606,7 +29983,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -29637,7 +30014,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -29668,7 +30045,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -29699,7 +30076,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -29730,7 +30107,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -29761,7 +30138,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -29792,7 +30169,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -29823,7 +30200,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -29854,7 +30231,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -29885,7 +30262,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -29916,7 +30293,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -29947,7 +30324,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -29978,7 +30355,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30009,7 +30386,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30040,7 +30417,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30071,7 +30448,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30102,7 +30479,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30133,7 +30510,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30164,7 +30541,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30195,7 +30572,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30226,7 +30603,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30257,7 +30634,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30288,7 +30665,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30319,7 +30696,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -30350,7 +30727,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -30381,7 +30758,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -30412,7 +30789,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -30443,7 +30820,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -30474,7 +30851,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -30505,7 +30882,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -30536,7 +30913,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -30567,7 +30944,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -30598,7 +30975,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -30629,7 +31006,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -30660,7 +31037,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -30691,7 +31068,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -30722,7 +31099,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -30753,7 +31130,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -30784,7 +31161,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -30815,7 +31192,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -30846,7 +31223,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -30877,7 +31254,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -30908,7 +31285,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -30939,7 +31316,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -30970,7 +31347,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31001,7 +31378,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31032,7 +31409,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31063,7 +31440,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31094,7 +31471,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31125,7 +31502,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31156,7 +31533,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31187,7 +31564,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31218,7 +31595,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31249,7 +31626,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31280,7 +31657,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -31311,7 +31688,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -31342,7 +31719,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -31373,7 +31750,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -31404,7 +31781,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -31435,7 +31812,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -31466,7 +31843,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -31497,7 +31874,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -31528,7 +31905,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -31559,7 +31936,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -31590,7 +31967,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -31621,7 +31998,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -31652,7 +32029,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -31683,7 +32060,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -31714,7 +32091,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -31745,7 +32122,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -31776,7 +32153,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -31807,7 +32184,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\numbe_\OneDrive\Documents\GitHub\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C4577A-6E1B-4035-9FE6-6F1791CF9982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B59472-DB3F-44FD-A6E6-2B3EC1955EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BallParam" sheetId="1" r:id="rId1"/>
@@ -516,10 +516,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Split into 2 smaller balls when triggered. Upon splitting, each individual ball can split again and again, but each split will requires more points.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Iceball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -632,12 +628,15 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Split into 2 smaller balls when triggered. Balls created by this effect do not split again.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -732,7 +731,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -949,14 +948,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="69.33203125" customWidth="1"/>
     <col min="15" max="15" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1014,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1074,7 +1073,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,7 +1106,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1140,7 +1139,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="33.6" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -1177,7 +1176,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="45" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -1201,7 +1200,7 @@
         <v>500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
@@ -1219,7 +1218,7 @@
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1236,7 +1235,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="39" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -1257,7 +1256,7 @@
         <v>0.75</v>
       </c>
       <c r="H7" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>19</v>
@@ -1272,7 +1271,7 @@
         <v>27</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1293,7 +1292,7 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="44.4" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -1317,7 +1316,7 @@
         <v>700</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
@@ -1350,7 +1349,7 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="30.6" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>30</v>
@@ -1407,10 +1406,10 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -1431,7 +1430,7 @@
         <v>750</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="1">
         <v>200</v>
@@ -1440,16 +1439,16 @@
         <v>70</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1466,10 +1465,10 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="39.6" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1">
         <v>17</v>
@@ -1490,7 +1489,7 @@
         <v>900</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J11" s="1">
         <v>800</v>
@@ -1499,16 +1498,16 @@
         <v>30</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1525,7 +1524,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1556,7 +1555,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1587,7 +1586,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1618,7 +1617,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1649,7 +1648,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1680,7 +1679,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1711,7 +1710,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1742,7 +1741,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1773,7 +1772,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1804,7 +1803,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1835,7 +1834,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1866,7 +1865,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1897,7 +1896,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1928,7 +1927,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1959,7 +1958,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1990,7 +1989,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2021,7 +2020,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2052,7 +2051,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2083,7 +2082,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2114,7 +2113,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2145,7 +2144,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2176,7 +2175,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2207,7 +2206,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2238,7 +2237,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2269,7 +2268,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2300,7 +2299,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="13.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2331,7 +2330,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="13.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2362,7 +2361,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="13.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2393,7 +2392,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="13.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2424,7 +2423,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="13.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2455,7 +2454,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="13.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2486,7 +2485,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="13.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2517,7 +2516,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="13.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2548,7 +2547,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="13.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2579,7 +2578,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="13.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2610,7 +2609,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="13.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2641,7 +2640,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="13.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2672,7 +2671,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="13.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2703,7 +2702,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="13.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2734,7 +2733,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="13.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2765,7 +2764,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="13.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2796,7 +2795,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="13.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2827,7 +2826,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="13.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2858,7 +2857,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="13.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2889,7 +2888,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="13.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2920,7 +2919,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="13.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2951,7 +2950,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="13.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2982,7 +2981,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="13.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3013,7 +3012,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="13.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3044,7 +3043,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="13.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3075,7 +3074,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="13.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3106,7 +3105,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="13.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3137,7 +3136,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="13.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3168,7 +3167,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="13.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3199,7 +3198,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="13.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3230,7 +3229,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="13.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3261,7 +3260,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="13.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3292,7 +3291,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="13.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3323,7 +3322,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="13.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3354,7 +3353,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="13.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3385,7 +3384,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="13.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3416,7 +3415,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="13.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3447,7 +3446,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="13.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3478,7 +3477,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="13.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3509,7 +3508,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="13.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3540,7 +3539,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="13.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3571,7 +3570,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="13.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3602,7 +3601,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="13.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3633,7 +3632,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="13.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3664,7 +3663,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="13.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3695,7 +3694,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="13.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3726,7 +3725,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="13.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3757,7 +3756,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="13.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3788,7 +3787,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="13.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3819,7 +3818,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="13.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3850,7 +3849,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="13.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3881,7 +3880,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="13.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3912,7 +3911,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="13.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3943,7 +3942,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="13.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3974,7 +3973,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="13.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4005,7 +4004,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="13.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4036,7 +4035,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="13.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4067,7 +4066,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="13.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4098,7 +4097,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="13.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4129,7 +4128,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="13.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4160,7 +4159,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="13.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4191,7 +4190,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="13.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4222,7 +4221,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="13.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4253,7 +4252,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="13.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4284,7 +4283,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="13.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4315,7 +4314,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="13.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4346,7 +4345,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="13.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4377,7 +4376,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="13.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4408,7 +4407,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="13.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4439,7 +4438,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="13.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4470,7 +4469,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="13.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4501,7 +4500,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="13.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4532,7 +4531,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="13.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4563,7 +4562,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="13.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4594,7 +4593,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="13.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4625,7 +4624,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="13.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4656,7 +4655,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="13.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4687,7 +4686,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="13.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4718,7 +4717,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="13.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4749,7 +4748,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="13.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4780,7 +4779,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="13.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4811,7 +4810,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="13.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4842,7 +4841,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="13.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4873,7 +4872,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="13.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4904,7 +4903,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="13.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4935,7 +4934,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="13.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4966,7 +4965,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="13.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4997,7 +4996,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="13.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5028,7 +5027,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="13.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5059,7 +5058,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="13.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5090,7 +5089,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="13.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5121,7 +5120,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="13.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5152,7 +5151,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="13.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5183,7 +5182,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="13.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5214,7 +5213,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="13.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5245,7 +5244,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="13.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5276,7 +5275,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="13.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5307,7 +5306,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="13.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5338,7 +5337,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="13.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5369,7 +5368,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="13.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5400,7 +5399,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="13.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5431,7 +5430,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="13.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5462,7 +5461,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="13.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5493,7 +5492,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="13.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5524,7 +5523,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="13.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5555,7 +5554,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="13.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5586,7 +5585,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="13.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5617,7 +5616,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="13.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5648,7 +5647,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="13.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5679,7 +5678,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="13.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5710,7 +5709,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="13.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5741,7 +5740,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="13.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5772,7 +5771,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="13.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5803,7 +5802,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="13.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5834,7 +5833,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="13.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5865,7 +5864,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="13.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5896,7 +5895,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="13.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5927,7 +5926,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" ht="13.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5958,7 +5957,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" ht="13.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5989,7 +5988,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" ht="13.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6020,7 +6019,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" ht="13.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6051,7 +6050,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" ht="13.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6082,7 +6081,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" ht="13.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6113,7 +6112,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" ht="13.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6144,7 +6143,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" ht="13.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6175,7 +6174,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" ht="13.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6206,7 +6205,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" ht="13.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6237,7 +6236,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" ht="13.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6268,7 +6267,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" ht="13.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6299,7 +6298,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" ht="13.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6330,7 +6329,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" ht="13.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6361,7 +6360,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" ht="13.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6392,7 +6391,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" ht="13.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6423,7 +6422,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="13.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6454,7 +6453,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" ht="13.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6485,7 +6484,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" ht="13.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6516,7 +6515,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="13.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6547,7 +6546,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" ht="13.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6578,7 +6577,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" ht="13.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6609,7 +6608,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="13.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6640,7 +6639,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="13.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6671,7 +6670,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="13.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6702,7 +6701,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" ht="13.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6733,7 +6732,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" ht="13.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6764,7 +6763,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" ht="13.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6795,7 +6794,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" ht="13.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6826,7 +6825,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" ht="13.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6857,7 +6856,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" ht="13.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6888,7 +6887,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" ht="13.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6919,7 +6918,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" ht="13.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6950,7 +6949,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" ht="13.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6981,7 +6980,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" ht="13.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7012,7 +7011,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" ht="13.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7043,7 +7042,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" ht="13.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7074,7 +7073,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" ht="13.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7105,7 +7104,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" ht="13.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7136,7 +7135,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" ht="13.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7167,7 +7166,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" ht="13.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7198,7 +7197,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" ht="13.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7229,7 +7228,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" ht="13.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7260,7 +7259,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" ht="13.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7291,7 +7290,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" ht="13.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7322,7 +7321,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" ht="13.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7353,7 +7352,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" ht="13.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7384,7 +7383,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" ht="13.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7415,7 +7414,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" ht="13.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7446,7 +7445,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29" ht="13.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7477,7 +7476,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" ht="13.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7508,7 +7507,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" ht="13.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7539,7 +7538,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29" ht="13.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7570,7 +7569,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29" ht="13.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7601,7 +7600,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29" ht="13.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7632,7 +7631,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" ht="13.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7663,7 +7662,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29" ht="13.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7694,7 +7693,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:29" ht="13.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7725,7 +7724,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29" ht="13.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7756,7 +7755,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29" ht="13.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7787,7 +7786,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29" ht="13.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7818,7 +7817,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29" ht="13.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7849,7 +7848,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29" ht="13.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7880,7 +7879,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29" ht="13.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7911,7 +7910,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29" ht="13.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7942,7 +7941,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29" ht="13.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7973,7 +7972,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29" ht="13.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8004,7 +8003,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29" ht="13.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8035,7 +8034,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" ht="13.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8066,7 +8065,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29" ht="13.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8097,7 +8096,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29" ht="13.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8128,7 +8127,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29" ht="13.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8159,7 +8158,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29" ht="13.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8190,7 +8189,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29" ht="13.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8221,7 +8220,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29" ht="13.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8252,7 +8251,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" ht="13.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8283,7 +8282,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29" ht="13.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8314,7 +8313,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29" ht="13.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8345,7 +8344,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29" ht="13.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8376,7 +8375,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29" ht="13.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8407,7 +8406,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29" ht="13.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8438,7 +8437,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29" ht="13.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8469,7 +8468,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29" ht="13.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8500,7 +8499,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29" ht="13.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8531,7 +8530,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29" ht="13.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8562,7 +8561,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29" ht="13.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8593,7 +8592,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29" ht="13.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8624,7 +8623,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29" ht="13.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8655,7 +8654,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29" ht="13.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8686,7 +8685,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29" ht="13.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8717,7 +8716,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29" ht="13.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8748,7 +8747,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" ht="13.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8779,7 +8778,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29" ht="13.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8810,7 +8809,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29" ht="13.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8841,7 +8840,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29" ht="13.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8872,7 +8871,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29" ht="13.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8903,7 +8902,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29" ht="13.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8934,7 +8933,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:29" ht="13.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8965,7 +8964,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:29" ht="13.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8996,7 +8995,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:29" ht="13.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -9027,7 +9026,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:29" ht="13.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9058,7 +9057,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:29" ht="13.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9089,7 +9088,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:29" ht="13.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9120,7 +9119,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:29" ht="13.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9151,7 +9150,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:29" ht="13.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9182,7 +9181,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:29" ht="13.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9213,7 +9212,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:29" ht="13.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9244,7 +9243,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:29" ht="13.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9275,7 +9274,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:29" ht="13.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9306,7 +9305,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:29" ht="13.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9337,7 +9336,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:29" ht="13.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9368,7 +9367,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:29" ht="13.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9399,7 +9398,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:29" ht="13.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9430,7 +9429,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:29" ht="13.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9461,7 +9460,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:29" ht="13.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9492,7 +9491,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:29" ht="13.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9523,7 +9522,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:29" ht="13.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9554,7 +9553,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:29" ht="13.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9585,7 +9584,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:29" ht="13.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9616,7 +9615,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29" ht="13.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9647,7 +9646,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29" ht="13.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9678,7 +9677,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29" ht="13.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9709,7 +9708,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29" ht="13.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9740,7 +9739,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29" ht="13.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9771,7 +9770,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:29" ht="13.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9802,7 +9801,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:29" ht="13.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9833,7 +9832,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:29" ht="13.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9864,7 +9863,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:29" ht="13.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9895,7 +9894,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:29" ht="13.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9926,7 +9925,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:29" ht="13.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9957,7 +9956,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:29" ht="13.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9988,7 +9987,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:29" ht="13.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -10019,7 +10018,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:29" ht="13.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10050,7 +10049,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:29" ht="13.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10081,7 +10080,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:29" ht="13.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10112,7 +10111,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:29" ht="13.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10143,7 +10142,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:29" ht="13.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10174,7 +10173,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:29" ht="13.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10205,7 +10204,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:29" ht="13.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10236,7 +10235,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:29" ht="13.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10267,7 +10266,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:29" ht="13.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10298,7 +10297,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:29" ht="13.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10329,7 +10328,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:29" ht="13.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10360,7 +10359,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:29" ht="13.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10391,7 +10390,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:29" ht="13.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10422,7 +10421,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:29" ht="13.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10453,7 +10452,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:29" ht="13.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10484,7 +10483,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:29" ht="13.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10515,7 +10514,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:29" ht="13.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10546,7 +10545,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:29" ht="13.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10577,7 +10576,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:29" ht="13.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10608,7 +10607,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:29" ht="13.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10639,7 +10638,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:29" ht="13.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10670,7 +10669,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:29" ht="13.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10701,7 +10700,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:29" ht="13.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10732,7 +10731,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:29" ht="13.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10763,7 +10762,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:29" ht="13.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10794,7 +10793,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:29" ht="13.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10825,7 +10824,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:29" ht="13.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10856,7 +10855,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:29" ht="13.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10887,7 +10886,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:29" ht="13.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10918,7 +10917,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:29" ht="13.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10949,7 +10948,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:29" ht="13.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10980,7 +10979,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:29" ht="13.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11011,7 +11010,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:29" ht="13.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11042,7 +11041,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:29" ht="13.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11073,7 +11072,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:29" ht="13.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11104,7 +11103,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:29" ht="13.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11135,7 +11134,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:29" ht="13.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11166,7 +11165,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:29" ht="13.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11197,7 +11196,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:29" ht="13.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11228,7 +11227,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:29" ht="13.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11259,7 +11258,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:29" ht="13.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11290,7 +11289,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:29" ht="13.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11321,7 +11320,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:29" ht="13.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11352,7 +11351,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:29" ht="13.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11383,7 +11382,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:29" ht="13.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11414,7 +11413,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:29" ht="13.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11445,7 +11444,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:29" ht="13.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11476,7 +11475,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:29" ht="13.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11507,7 +11506,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:29" ht="13.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11538,7 +11537,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:29" ht="13.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11569,7 +11568,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:29" ht="13.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11600,7 +11599,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:29" ht="13.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11631,7 +11630,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:29" ht="13.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11662,7 +11661,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:29" ht="13.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11693,7 +11692,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:29" ht="13.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11724,7 +11723,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:29" ht="13.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11755,7 +11754,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:29" ht="13.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11786,7 +11785,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:29" ht="13.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11817,7 +11816,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:29" ht="13.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11848,7 +11847,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:29" ht="13.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11879,7 +11878,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:29" ht="13.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11910,7 +11909,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:29" ht="13.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11941,7 +11940,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:29" ht="13.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11972,7 +11971,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:29" ht="13.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12003,7 +12002,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:29" ht="13.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12034,7 +12033,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:29" ht="13.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12065,7 +12064,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:29" ht="13.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12096,7 +12095,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:29" ht="13.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12127,7 +12126,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:29" ht="13.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12158,7 +12157,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:29" ht="13.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12189,7 +12188,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:29" ht="13.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12220,7 +12219,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:29" ht="13.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12251,7 +12250,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:29" ht="13.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12282,7 +12281,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:29" ht="13.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12313,7 +12312,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:29" ht="13.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12344,7 +12343,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:29" ht="13.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12375,7 +12374,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:29" ht="13.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12406,7 +12405,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:29" ht="13.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12437,7 +12436,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:29" ht="13.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12468,7 +12467,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:29" ht="13.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12499,7 +12498,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:29" ht="13.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12530,7 +12529,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:29" ht="13.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12561,7 +12560,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:29" ht="13.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12592,7 +12591,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:29" ht="13.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12623,7 +12622,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:29" ht="13.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12654,7 +12653,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:29" ht="13.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12685,7 +12684,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:29" ht="13.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12716,7 +12715,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:29" ht="13.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12747,7 +12746,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:29" ht="13.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12778,7 +12777,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:29" ht="13.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12809,7 +12808,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:29" ht="13.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12840,7 +12839,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:29" ht="13.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12871,7 +12870,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:29" ht="13.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12902,7 +12901,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:29" ht="13.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12933,7 +12932,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:29" ht="13.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12964,7 +12963,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:29" ht="13.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12995,7 +12994,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:29" ht="13.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -13026,7 +13025,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:29" ht="13.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13057,7 +13056,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:29" ht="13.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13088,7 +13087,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:29" ht="13.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13119,7 +13118,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:29" ht="13.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13150,7 +13149,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:29" ht="13.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13181,7 +13180,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:29" ht="13.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13212,7 +13211,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:29" ht="13.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13243,7 +13242,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:29" ht="13.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13274,7 +13273,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:29" ht="13.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13305,7 +13304,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:29" ht="13.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13336,7 +13335,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:29" ht="13.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13367,7 +13366,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:29" ht="13.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13398,7 +13397,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:29" ht="13.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13429,7 +13428,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:29" ht="13.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13460,7 +13459,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:29" ht="13.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13491,7 +13490,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:29" ht="13.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13522,7 +13521,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:29" ht="13.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13553,7 +13552,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:29" ht="13.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13584,7 +13583,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:29" ht="13.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13615,7 +13614,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:29" ht="13.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13646,7 +13645,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:29" ht="13.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13677,7 +13676,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:29" ht="13.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13708,7 +13707,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:29" ht="13.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13739,7 +13738,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:29" ht="13.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13770,7 +13769,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:29" ht="13.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13801,7 +13800,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:29" ht="13.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13832,7 +13831,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:29" ht="13.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13863,7 +13862,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:29" ht="13.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13894,7 +13893,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:29" ht="13.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13925,7 +13924,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:29" ht="13.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13956,7 +13955,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:29" ht="13.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13987,7 +13986,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:29" ht="13.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -14018,7 +14017,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:29" ht="13.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -14049,7 +14048,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:29" ht="13.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -14080,7 +14079,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:29" ht="13.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -14111,7 +14110,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:29" ht="13.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -14142,7 +14141,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:29" ht="13.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -14173,7 +14172,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:29" ht="13.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -14204,7 +14203,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:29" ht="13.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14235,7 +14234,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:29" ht="13.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14266,7 +14265,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:29" ht="13.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14297,7 +14296,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:29" ht="13.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14328,7 +14327,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:29" ht="13.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14359,7 +14358,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:29" ht="13.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14390,7 +14389,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:29" ht="13.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14421,7 +14420,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:29" ht="13.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14452,7 +14451,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:29" ht="13.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14483,7 +14482,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:29" ht="13.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14514,7 +14513,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:29" ht="13.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14545,7 +14544,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:29" ht="13.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14576,7 +14575,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:29" ht="13.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14607,7 +14606,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:29" ht="13.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14638,7 +14637,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:29" ht="13.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14669,7 +14668,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:29" ht="13.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14700,7 +14699,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:29" ht="13.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14731,7 +14730,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:29" ht="13.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14762,7 +14761,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:29" ht="13.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14793,7 +14792,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:29" ht="13.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14824,7 +14823,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:29" ht="13.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14855,7 +14854,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:29" ht="13.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14886,7 +14885,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:29" ht="13.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14917,7 +14916,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:29" ht="13.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14948,7 +14947,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:29" ht="13.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14979,7 +14978,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:29" ht="13.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -15010,7 +15009,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:29" ht="13.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -15041,7 +15040,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:29" ht="13.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -15072,7 +15071,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:29" ht="13.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -15103,7 +15102,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:29" ht="13.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -15134,7 +15133,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:29" ht="13.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -15165,7 +15164,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:29" ht="13.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -15196,7 +15195,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:29" ht="13.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15227,7 +15226,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:29" ht="13.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15258,7 +15257,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:29" ht="13.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15289,7 +15288,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:29" ht="13.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15320,7 +15319,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:29" ht="13.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15351,7 +15350,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:29" ht="13.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15382,7 +15381,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:29" ht="13.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15413,7 +15412,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:29" ht="13.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15444,7 +15443,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:29" ht="13.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15475,7 +15474,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:29" ht="13.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15506,7 +15505,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:29" ht="13.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15537,7 +15536,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:29" ht="13.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15568,7 +15567,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:29" ht="13.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15599,7 +15598,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:29" ht="13.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15630,7 +15629,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:29" ht="13.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15661,7 +15660,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:29" ht="13.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15692,7 +15691,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:29" ht="13.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15723,7 +15722,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:29" ht="13.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15754,7 +15753,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:29" ht="13.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15785,7 +15784,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:29" ht="13.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15816,7 +15815,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:29" ht="13.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15847,7 +15846,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:29" ht="13.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15878,7 +15877,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:29" ht="13.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15909,7 +15908,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:29" ht="13.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15940,7 +15939,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:29" ht="13.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15971,7 +15970,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:29" ht="13.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -16002,7 +16001,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:29" ht="13.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -16033,7 +16032,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:29" ht="13.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -16064,7 +16063,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:29" ht="13.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -16095,7 +16094,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:29" ht="13.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -16126,7 +16125,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:29" ht="13.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -16157,7 +16156,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:29" ht="13.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16188,7 +16187,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:29" ht="13.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16219,7 +16218,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:29" ht="13.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16250,7 +16249,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:29" ht="13.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16281,7 +16280,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:29" ht="13.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16312,7 +16311,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:29" ht="13.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16343,7 +16342,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:29" ht="13.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16374,7 +16373,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:29" ht="13.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16405,7 +16404,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:29" ht="13.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16436,7 +16435,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:29" ht="13.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16467,7 +16466,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:29" ht="13.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16498,7 +16497,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:29" ht="13.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16529,7 +16528,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:29" ht="13.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16560,7 +16559,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:29" ht="13.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16591,7 +16590,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:29" ht="13.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16622,7 +16621,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:29" ht="13.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16653,7 +16652,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:29" ht="13.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16684,7 +16683,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:29" ht="13.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16715,7 +16714,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:29" ht="13.2">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16746,7 +16745,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:29" ht="13.2">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16777,7 +16776,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:29" ht="13.2">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16808,7 +16807,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:29" ht="13.2">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16839,7 +16838,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:29" ht="13.2">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16870,7 +16869,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:29" ht="13.2">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16901,7 +16900,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:29" ht="13.2">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16932,7 +16931,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:29" ht="13.2">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16963,7 +16962,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:29" ht="13.2">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16994,7 +16993,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:29" ht="13.2">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -17025,7 +17024,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:29" ht="13.2">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -17056,7 +17055,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:29" ht="13.2">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -17087,7 +17086,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:29" ht="13.2">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -17118,7 +17117,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:29" ht="13.2">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17149,7 +17148,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:29" ht="13.2">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17180,7 +17179,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:29" ht="13.2">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17211,7 +17210,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:29" ht="13.2">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17242,7 +17241,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:29" ht="13.2">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17273,7 +17272,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:29" ht="13.2">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17304,7 +17303,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:29" ht="13.2">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17335,7 +17334,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:29" ht="13.2">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17366,7 +17365,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:29" ht="13.2">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17397,7 +17396,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:29" ht="13.2">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17428,7 +17427,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:29" ht="13.2">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17459,7 +17458,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:29" ht="13.2">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17490,7 +17489,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:29" ht="13.2">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17521,7 +17520,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:29" ht="13.2">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17552,7 +17551,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:29" ht="13.2">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17583,7 +17582,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:29" ht="13.2">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17614,7 +17613,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:29" ht="13.2">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17645,7 +17644,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:29" ht="13.2">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17676,7 +17675,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:29" ht="13.2">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17707,7 +17706,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:29" ht="13.2">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17738,7 +17737,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:29" ht="13.2">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17769,7 +17768,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:29" ht="13.2">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17800,7 +17799,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:29" ht="13.2">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17831,7 +17830,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:29" ht="13.2">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17862,7 +17861,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:29" ht="13.2">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17893,7 +17892,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:29" ht="13.2">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17924,7 +17923,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:29" ht="13.2">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17955,7 +17954,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:29" ht="13.2">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17986,7 +17985,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:29" ht="13.2">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -18017,7 +18016,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:29" ht="13.2">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -18048,7 +18047,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:29" ht="13.2">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -18079,7 +18078,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:29" ht="13.2">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18110,7 +18109,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:29" ht="13.2">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18141,7 +18140,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:29" ht="13.2">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18172,7 +18171,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:29" ht="13.2">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18203,7 +18202,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:29" ht="13.2">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18234,7 +18233,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:29" ht="13.2">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18265,7 +18264,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:29" ht="13.2">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18296,7 +18295,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:29" ht="13.2">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18327,7 +18326,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:29" ht="13.2">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18358,7 +18357,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:29" ht="13.2">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18389,7 +18388,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:29" ht="13.2">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18420,7 +18419,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:29" ht="13.2">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18451,7 +18450,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:29" ht="13.2">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18482,7 +18481,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:29" ht="13.2">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18513,7 +18512,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:29" ht="13.2">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18544,7 +18543,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:29" ht="13.2">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18575,7 +18574,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:29" ht="13.2">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18606,7 +18605,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:29" ht="13.2">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18637,7 +18636,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:29" ht="13.2">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18668,7 +18667,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:29" ht="13.2">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18699,7 +18698,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:29" ht="13.2">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18730,7 +18729,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:29" ht="13.2">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18761,7 +18760,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:29" ht="13.2">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18792,7 +18791,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:29" ht="13.2">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18823,7 +18822,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:29" ht="13.2">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18854,7 +18853,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:29" ht="13.2">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18885,7 +18884,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:29" ht="13.2">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18916,7 +18915,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:29" ht="13.2">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18947,7 +18946,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:29" ht="13.2">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18978,7 +18977,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:29" ht="13.2">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -19009,7 +19008,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:29" ht="13.2">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -19040,7 +19039,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:29" ht="13.2">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -19071,7 +19070,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:29" ht="13.2">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19102,7 +19101,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:29" ht="13.2">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19133,7 +19132,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:29" ht="13.2">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19164,7 +19163,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:29" ht="13.2">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19195,7 +19194,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:29" ht="13.2">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19226,7 +19225,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:29" ht="13.2">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19257,7 +19256,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:29" ht="13.2">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19288,7 +19287,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:29" ht="13.2">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19319,7 +19318,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:29" ht="13.2">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19350,7 +19349,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:29" ht="13.2">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19381,7 +19380,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:29" ht="13.2">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19412,7 +19411,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:29" ht="13.2">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19443,7 +19442,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:29" ht="13.2">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19474,7 +19473,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:29" ht="13.2">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19505,7 +19504,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:29" ht="13.2">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19536,7 +19535,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:29" ht="13.2">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19567,7 +19566,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:29" ht="13.2">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19598,7 +19597,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:29" ht="13.2">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19629,7 +19628,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:29" ht="13.2">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19660,7 +19659,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:29" ht="13.2">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19691,7 +19690,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:29" ht="13.2">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19722,7 +19721,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:29" ht="13.2">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19753,7 +19752,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:29" ht="13.2">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19784,7 +19783,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:29" ht="13.2">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19815,7 +19814,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:29" ht="13.2">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19846,7 +19845,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:29" ht="13.2">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19877,7 +19876,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:29" ht="13.2">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19908,7 +19907,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:29" ht="13.2">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19939,7 +19938,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:29" ht="13.2">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19970,7 +19969,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:29" ht="13.2">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -20001,7 +20000,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:29" ht="13.2">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -20032,7 +20031,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:29" ht="13.2">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20063,7 +20062,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:29" ht="13.2">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20094,7 +20093,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:29" ht="13.2">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20125,7 +20124,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:29" ht="13.2">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20156,7 +20155,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:29" ht="13.2">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20187,7 +20186,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:29" ht="13.2">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20218,7 +20217,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:29" ht="13.2">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20249,7 +20248,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:29" ht="13.2">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20280,7 +20279,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:29" ht="13.2">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20311,7 +20310,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:29" ht="13.2">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20342,7 +20341,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:29" ht="13.2">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20373,7 +20372,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:29" ht="13.2">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20404,7 +20403,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:29" ht="13.2">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20435,7 +20434,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:29" ht="13.2">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20466,7 +20465,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:29" ht="13.2">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20497,7 +20496,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:29" ht="13.2">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20528,7 +20527,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:29" ht="13.2">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20559,7 +20558,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:29" ht="13.2">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20590,7 +20589,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:29" ht="13.2">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20621,7 +20620,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:29" ht="13.2">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20652,7 +20651,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:29" ht="13.2">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20683,7 +20682,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:29" ht="13.2">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20714,7 +20713,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:29" ht="13.2">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20745,7 +20744,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:29" ht="13.2">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20776,7 +20775,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:29" ht="13.2">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20807,7 +20806,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:29" ht="13.2">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20838,7 +20837,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:29" ht="13.2">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20869,7 +20868,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:29" ht="13.2">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20900,7 +20899,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:29" ht="13.2">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20931,7 +20930,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:29" ht="13.2">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20962,7 +20961,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:29" ht="13.2">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20993,7 +20992,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:29" ht="13.2">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -21024,7 +21023,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:29" ht="13.2">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21055,7 +21054,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:29" ht="13.2">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21086,7 +21085,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:29" ht="13.2">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21117,7 +21116,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:29" ht="13.2">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21148,7 +21147,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:29" ht="13.2">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21179,7 +21178,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:29" ht="13.2">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21210,7 +21209,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:29" ht="13.2">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21241,7 +21240,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:29" ht="13.2">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21272,7 +21271,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:29" ht="13.2">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21303,7 +21302,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:29" ht="13.2">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21334,7 +21333,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:29" ht="13.2">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21365,7 +21364,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:29" ht="13.2">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21396,7 +21395,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:29" ht="13.2">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21427,7 +21426,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:29" ht="13.2">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21458,7 +21457,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:29" ht="13.2">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21489,7 +21488,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:29" ht="13.2">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21520,7 +21519,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:29" ht="13.2">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21551,7 +21550,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:29" ht="13.2">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21582,7 +21581,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:29" ht="13.2">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21613,7 +21612,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:29" ht="13.2">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21644,7 +21643,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:29" ht="13.2">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21675,7 +21674,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:29" ht="13.2">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21706,7 +21705,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:29" ht="13.2">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21737,7 +21736,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:29" ht="13.2">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21768,7 +21767,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:29" ht="13.2">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21799,7 +21798,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:29" ht="13.2">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21830,7 +21829,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:29" ht="13.2">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21861,7 +21860,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:29" ht="13.2">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21892,7 +21891,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:29" ht="13.2">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21923,7 +21922,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:29" ht="13.2">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21954,7 +21953,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:29" ht="13.2">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21985,7 +21984,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:29" ht="13.2">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22016,7 +22015,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:29" ht="13.2">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22047,7 +22046,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:29" ht="13.2">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22078,7 +22077,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:29" ht="13.2">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22109,7 +22108,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:29" ht="13.2">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22140,7 +22139,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:29" ht="13.2">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22171,7 +22170,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:29" ht="13.2">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22202,7 +22201,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:29" ht="13.2">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22233,7 +22232,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:29" ht="13.2">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22264,7 +22263,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:29" ht="13.2">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22295,7 +22294,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:29" ht="13.2">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22326,7 +22325,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:29" ht="13.2">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22357,7 +22356,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:29" ht="13.2">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22388,7 +22387,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:29" ht="13.2">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22419,7 +22418,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:29" ht="13.2">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22450,7 +22449,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:29" ht="13.2">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22481,7 +22480,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:29" ht="13.2">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22512,7 +22511,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:29" ht="13.2">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22543,7 +22542,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:29" ht="13.2">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22574,7 +22573,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:29" ht="13.2">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22605,7 +22604,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:29" ht="13.2">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22636,7 +22635,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:29" ht="13.2">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22667,7 +22666,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:29" ht="13.2">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22698,7 +22697,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:29" ht="13.2">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22729,7 +22728,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:29" ht="13.2">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22760,7 +22759,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:29" ht="13.2">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22791,7 +22790,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:29" ht="13.2">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22822,7 +22821,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:29" ht="13.2">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22853,7 +22852,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:29" ht="13.2">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22884,7 +22883,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:29" ht="13.2">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22915,7 +22914,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:29" ht="13.2">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22946,7 +22945,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:29" ht="13.2">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22977,7 +22976,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:29" ht="13.2">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23008,7 +23007,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:29" ht="13.2">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23039,7 +23038,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:29" ht="13.2">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23070,7 +23069,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:29" ht="13.2">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23101,7 +23100,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:29" ht="13.2">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23132,7 +23131,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:29" ht="13.2">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23163,7 +23162,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:29" ht="13.2">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23194,7 +23193,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:29" ht="13.2">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23225,7 +23224,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:29" ht="13.2">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23256,7 +23255,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:29" ht="13.2">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23287,7 +23286,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:29" ht="13.2">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23318,7 +23317,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:29" ht="13.2">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23349,7 +23348,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:29" ht="13.2">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23380,7 +23379,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:29" ht="13.2">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23411,7 +23410,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:29" ht="13.2">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23442,7 +23441,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:29" ht="13.2">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23473,7 +23472,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:29" ht="13.2">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23504,7 +23503,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:29" ht="13.2">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23535,7 +23534,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:29" ht="13.2">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23566,7 +23565,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:29" ht="13.2">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23597,7 +23596,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:29" ht="13.2">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23628,7 +23627,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:29" ht="13.2">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23659,7 +23658,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:29" ht="13.2">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23690,7 +23689,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:29" ht="13.2">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23721,7 +23720,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:29" ht="13.2">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23752,7 +23751,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:29" ht="13.2">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23783,7 +23782,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:29" ht="13.2">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23814,7 +23813,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:29" ht="13.2">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23845,7 +23844,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:29" ht="13.2">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23876,7 +23875,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:29" ht="13.2">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23907,7 +23906,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:29" ht="13.2">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -23938,7 +23937,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:29" ht="13.2">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -23969,7 +23968,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:29" ht="13.2">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -24000,7 +23999,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:29" ht="13.2">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24031,7 +24030,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:29" ht="13.2">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24062,7 +24061,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:29" ht="13.2">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24093,7 +24092,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:29" ht="13.2">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24124,7 +24123,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:29" ht="13.2">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24155,7 +24154,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:29" ht="13.2">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24186,7 +24185,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:29" ht="13.2">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24217,7 +24216,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:29" ht="13.2">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24248,7 +24247,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:29" ht="13.2">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24279,7 +24278,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:29" ht="13.2">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24310,7 +24309,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:29" ht="13.2">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24341,7 +24340,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:29" ht="13.2">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24372,7 +24371,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:29" ht="13.2">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24403,7 +24402,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:29" ht="13.2">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24434,7 +24433,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:29" ht="13.2">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24465,7 +24464,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:29" ht="13.2">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24496,7 +24495,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:29" ht="13.2">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24527,7 +24526,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:29" ht="13.2">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24558,7 +24557,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:29" ht="13.2">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24589,7 +24588,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:29" ht="13.2">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24620,7 +24619,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:29" ht="13.2">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24651,7 +24650,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:29" ht="13.2">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24682,7 +24681,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:29" ht="13.2">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24713,7 +24712,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:29" ht="13.2">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24744,7 +24743,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:29" ht="13.2">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24775,7 +24774,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:29" ht="13.2">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24806,7 +24805,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:29" ht="13.2">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24837,7 +24836,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:29" ht="13.2">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24868,7 +24867,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:29" ht="13.2">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24899,7 +24898,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:29" ht="13.2">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -24930,7 +24929,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:29" ht="13.2">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -24961,7 +24960,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:29" ht="13.2">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -24992,7 +24991,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:29" ht="13.2">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25023,7 +25022,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:29" ht="13.2">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25054,7 +25053,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:29" ht="13.2">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25085,7 +25084,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:29" ht="13.2">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25116,7 +25115,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:29" ht="13.2">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25147,7 +25146,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:29" ht="13.2">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25178,7 +25177,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:29" ht="13.2">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25209,7 +25208,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:29" ht="13.2">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25240,7 +25239,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:29" ht="13.2">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25271,7 +25270,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:29" ht="13.2">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25302,7 +25301,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:29" ht="13.2">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25333,7 +25332,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:29" ht="13.2">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25364,7 +25363,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:29" ht="13.2">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25395,7 +25394,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:29" ht="13.2">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25426,7 +25425,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:29" ht="13.2">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25457,7 +25456,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:29" ht="13.2">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25488,7 +25487,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:29" ht="13.2">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25519,7 +25518,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:29" ht="13.2">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25550,7 +25549,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:29" ht="13.2">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25581,7 +25580,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:29" ht="13.2">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25612,7 +25611,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:29" ht="13.2">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25643,7 +25642,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:29" ht="13.2">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25674,7 +25673,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:29" ht="13.2">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25705,7 +25704,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:29" ht="13.2">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25736,7 +25735,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:29" ht="13.2">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25767,7 +25766,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:29" ht="13.2">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25798,7 +25797,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:29" ht="13.2">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25829,7 +25828,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:29" ht="13.2">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25860,7 +25859,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:29" ht="13.2">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -25891,7 +25890,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:29" ht="13.2">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -25922,7 +25921,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:29" ht="13.2">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -25953,7 +25952,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:29" ht="13.2">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -25984,7 +25983,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:29" ht="13.2">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26015,7 +26014,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:29" ht="13.2">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26046,7 +26045,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:29" ht="13.2">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26077,7 +26076,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:29" ht="13.2">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26108,7 +26107,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:29" ht="13.2">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26139,7 +26138,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:29" ht="13.2">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26170,7 +26169,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:29" ht="13.2">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26201,7 +26200,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:29" ht="13.2">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26232,7 +26231,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:29" ht="13.2">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26263,7 +26262,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:29" ht="13.2">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26294,7 +26293,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:29" ht="13.2">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26325,7 +26324,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:29" ht="13.2">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26356,7 +26355,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:29" ht="13.2">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26387,7 +26386,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:29" ht="13.2">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26418,7 +26417,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:29" ht="13.2">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26449,7 +26448,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:29" ht="13.2">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26480,7 +26479,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:29" ht="13.2">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26511,7 +26510,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:29" ht="13.2">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26542,7 +26541,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:29" ht="13.2">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26573,7 +26572,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:29" ht="13.2">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26604,7 +26603,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:29" ht="13.2">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26635,7 +26634,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:29" ht="13.2">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26666,7 +26665,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:29" ht="13.2">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26697,7 +26696,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:29" ht="13.2">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26728,7 +26727,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:29" ht="13.2">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26759,7 +26758,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:29" ht="13.2">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26790,7 +26789,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:29" ht="13.2">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26821,7 +26820,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:29" ht="13.2">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -26852,7 +26851,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:29" ht="13.2">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -26883,7 +26882,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:29" ht="13.2">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -26914,7 +26913,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:29" ht="13.2">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -26945,7 +26944,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:29" ht="13.2">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -26976,7 +26975,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:29" ht="13.2">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27007,7 +27006,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:29" ht="13.2">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27038,7 +27037,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:29" ht="13.2">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27069,7 +27068,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:29" ht="13.2">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27100,7 +27099,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:29" ht="13.2">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27131,7 +27130,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:29" ht="13.2">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27162,7 +27161,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:29" ht="13.2">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27193,7 +27192,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:29" ht="13.2">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27224,7 +27223,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:29" ht="13.2">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27255,7 +27254,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:29" ht="13.2">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27286,7 +27285,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:29" ht="13.2">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27317,7 +27316,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:29" ht="13.2">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27348,7 +27347,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:29" ht="13.2">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27379,7 +27378,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:29" ht="13.2">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27410,7 +27409,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:29" ht="13.2">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27441,7 +27440,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:29" ht="13.2">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27472,7 +27471,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:29" ht="13.2">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27503,7 +27502,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:29" ht="13.2">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27534,7 +27533,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:29" ht="13.2">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27565,7 +27564,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:29" ht="13.2">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27596,7 +27595,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:29" ht="13.2">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27627,7 +27626,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:29" ht="13.2">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27658,7 +27657,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:29" ht="13.2">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27689,7 +27688,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:29" ht="13.2">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27720,7 +27719,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:29" ht="13.2">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27751,7 +27750,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:29" ht="13.2">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27782,7 +27781,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:29" ht="13.2">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -27813,7 +27812,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:29" ht="13.2">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -27844,7 +27843,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:29" ht="13.2">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -27875,7 +27874,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:29" ht="13.2">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -27906,7 +27905,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:29" ht="13.2">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -27937,7 +27936,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:29" ht="13.2">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -27968,7 +27967,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:29" ht="13.2">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -27999,7 +27998,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:29" ht="13.2">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28030,7 +28029,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:29" ht="13.2">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28061,7 +28060,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:29" ht="13.2">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28092,7 +28091,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:29" ht="13.2">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28123,7 +28122,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:29" ht="13.2">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28154,7 +28153,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:29" ht="13.2">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28185,7 +28184,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:29" ht="13.2">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28216,7 +28215,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:29" ht="13.2">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28247,7 +28246,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:29" ht="13.2">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28278,7 +28277,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:29" ht="13.2">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28309,7 +28308,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:29" ht="13.2">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28340,7 +28339,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:29" ht="13.2">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28371,7 +28370,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:29" ht="13.2">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28402,7 +28401,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:29" ht="13.2">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28433,7 +28432,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:29" ht="13.2">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28464,7 +28463,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:29" ht="13.2">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28495,7 +28494,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:29" ht="13.2">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28526,7 +28525,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:29" ht="13.2">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28557,7 +28556,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:29" ht="13.2">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28588,7 +28587,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:29" ht="13.2">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28619,7 +28618,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:29" ht="13.2">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28650,7 +28649,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:29" ht="13.2">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28681,7 +28680,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:29" ht="13.2">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28712,7 +28711,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:29" ht="13.2">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28743,7 +28742,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:29" ht="13.2">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28774,7 +28773,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:29" ht="13.2">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -28805,7 +28804,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:29" ht="13.2">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -28836,7 +28835,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:29" ht="13.2">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -28867,7 +28866,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:29" ht="13.2">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -28898,7 +28897,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:29" ht="13.2">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -28929,7 +28928,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:29" ht="13.2">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -28960,7 +28959,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:29" ht="13.2">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -28991,7 +28990,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:29" ht="13.2">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29022,7 +29021,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:29" ht="13.2">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29053,7 +29052,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:29" ht="13.2">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29084,7 +29083,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:29" ht="13.2">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29115,7 +29114,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:29" ht="13.2">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29146,7 +29145,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:29" ht="13.2">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29177,7 +29176,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:29" ht="13.2">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29208,7 +29207,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:29" ht="13.2">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29239,7 +29238,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:29" ht="13.2">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29270,7 +29269,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:29" ht="13.2">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29301,7 +29300,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:29" ht="13.2">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29332,7 +29331,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:29" ht="13.2">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29363,7 +29362,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:29" ht="13.2">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29394,7 +29393,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:29" ht="13.2">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29425,7 +29424,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:29" ht="13.2">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29456,7 +29455,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:29" ht="13.2">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29487,7 +29486,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:29" ht="13.2">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29518,7 +29517,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:29" ht="13.2">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29549,7 +29548,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:29" ht="13.2">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29580,7 +29579,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:29" ht="13.2">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29611,7 +29610,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:29" ht="13.2">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29642,7 +29641,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:29" ht="13.2">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29673,7 +29672,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:29" ht="13.2">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29704,7 +29703,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:29" ht="13.2">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29735,7 +29734,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:29" ht="13.2">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -29766,7 +29765,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:29" ht="13.2">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -29797,7 +29796,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:29" ht="13.2">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -29828,7 +29827,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:29" ht="13.2">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -29859,7 +29858,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:29" ht="13.2">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -29890,7 +29889,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:29" ht="13.2">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -29921,7 +29920,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:29" ht="13.2">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -29952,7 +29951,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:29" ht="13.2">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -29983,7 +29982,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:29" ht="13.2">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30014,7 +30013,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:29" ht="13.2">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30045,7 +30044,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:29" ht="13.2">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30076,7 +30075,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:29" ht="13.2">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30107,7 +30106,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:29" ht="13.2">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30138,7 +30137,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:29" ht="13.2">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30169,7 +30168,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:29" ht="13.2">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30200,7 +30199,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:29" ht="13.2">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30231,7 +30230,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:29" ht="13.2">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30262,7 +30261,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:29" ht="13.2">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30293,7 +30292,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:29" ht="13.2">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30324,7 +30323,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:29" ht="13.2">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30355,7 +30354,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:29" ht="13.2">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30386,7 +30385,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:29" ht="13.2">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30417,7 +30416,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:29" ht="13.2">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30448,7 +30447,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:29" ht="13.2">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30479,7 +30478,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:29" ht="13.2">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30510,7 +30509,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:29" ht="13.2">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30541,7 +30540,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:29" ht="13.2">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30572,7 +30571,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:29" ht="13.2">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30603,7 +30602,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:29" ht="13.2">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30634,7 +30633,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:29" ht="13.2">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30665,7 +30664,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:29" ht="13.2">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30696,7 +30695,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:29" ht="13.2">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -30727,7 +30726,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:29" ht="13.2">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -30758,7 +30757,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:29" ht="13.2">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -30789,7 +30788,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:29" ht="13.2">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -30820,7 +30819,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:29" ht="13.2">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -30851,7 +30850,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:29" ht="13.2">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -30882,7 +30881,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:29" ht="13.2">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -30913,7 +30912,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:29" ht="13.2">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -30944,7 +30943,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:29" ht="13.2">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -30975,7 +30974,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:29" ht="13.2">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31006,7 +31005,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:29" ht="13.2">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31037,7 +31036,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:29" ht="13.2">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31068,7 +31067,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:29" ht="13.2">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31099,7 +31098,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:29" ht="13.2">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31130,7 +31129,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:29" ht="13.2">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31161,7 +31160,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:29" ht="13.2">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31192,7 +31191,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:29" ht="13.2">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31223,7 +31222,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:29" ht="13.2">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31254,7 +31253,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:29" ht="13.2">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31285,7 +31284,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:29" ht="13.2">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31316,7 +31315,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:29" ht="13.2">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31347,7 +31346,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:29" ht="13.2">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31378,7 +31377,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:29" ht="13.2">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31409,7 +31408,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:29" ht="13.2">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31440,7 +31439,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:29" ht="13.2">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31471,7 +31470,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:29" ht="13.2">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31502,7 +31501,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:29" ht="13.2">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31533,7 +31532,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:29" ht="13.2">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31564,7 +31563,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:29" ht="13.2">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31595,7 +31594,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:29" ht="13.2">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31626,7 +31625,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:29" ht="13.2">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31657,7 +31656,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:29" ht="13.2">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -31688,7 +31687,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:29" ht="13.2">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -31719,7 +31718,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:29" ht="13.2">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -31750,7 +31749,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:29" ht="13.2">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -31781,7 +31780,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:29" ht="13.2">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -31812,7 +31811,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:29" ht="13.2">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -31843,7 +31842,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:29" ht="13.2">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -31874,7 +31873,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:29" ht="13.2">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -31905,7 +31904,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:29" ht="13.2">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -31936,7 +31935,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:29" ht="13.2">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -31967,7 +31966,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:29" ht="13.2">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -31998,7 +31997,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:29" ht="13.2">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32029,7 +32028,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:29" ht="13.2">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32060,7 +32059,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:29" ht="13.2">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32091,7 +32090,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:29" ht="13.2">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32122,7 +32121,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:29" ht="13.2">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32153,7 +32152,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:29" ht="13.2">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32184,7 +32183,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:29" ht="13.2">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\numbe_\OneDrive\Documents\GitHub\monster-ball\LubanConfig\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B59472-DB3F-44FD-A6E6-2B3EC1955EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B70D5A4-DD5C-4205-A377-E45B698C91CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BallParam" sheetId="1" r:id="rId1"/>
@@ -299,7 +299,7 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>} balls, each ball being able to split again once each of them reaches the point requirement again, but the next proc will require {Skill</t>
+          <t xml:space="preserve">} balls, each ball </t>
         </r>
         <r>
           <rPr>
@@ -309,16 +309,8 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>duration</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>} times more points.</t>
+          <t xml:space="preserve">cannot be split again further.
+</t>
         </r>
       </text>
     </comment>
@@ -492,10 +484,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Drops a fire trail that deals damage to enemies within overtime.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Good old basic. Does not have any effect, but it's reliable in every aspect.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -594,10 +582,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Infuse itself with lightning power for a duration, summons lightnings to strike down nearby enemies, dealing ball's attack damage to them.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FireTrail</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -629,14 +613,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Split into 2 smaller balls when triggered. Balls created by this effect do not split again.</t>
+    <t>Split into multiple smaller balls when triggered. Balls created by this effect do not split again.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Infuse itself with lightning power for a duration, summons lightnings to strike down on nearby enemies, dealing ball's attack damage to them.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drops a fire trail that deals ball's attack damage to enemies within overtime.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -731,7 +724,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -948,14 +941,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="69.33203125" customWidth="1"/>
     <col min="15" max="15" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75" customHeight="1">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,7 +1007,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1073,7 +1066,7 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75" customHeight="1">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,7 +1099,7 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75" customHeight="1">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1139,7 +1132,7 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="33.6" customHeight="1">
+    <row r="5" spans="1:29" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>16</v>
@@ -1173,10 +1166,10 @@
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="45" customHeight="1">
+    <row r="6" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -1200,7 +1193,7 @@
         <v>500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
@@ -1212,13 +1205,13 @@
         <v>25</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1235,7 +1228,7 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
     </row>
-    <row r="7" spans="1:29" ht="39" customHeight="1">
+    <row r="7" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -1271,7 +1264,7 @@
         <v>27</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1292,7 +1285,7 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
     </row>
-    <row r="8" spans="1:29" ht="44.4" customHeight="1">
+    <row r="8" spans="1:29" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -1316,7 +1309,7 @@
         <v>700</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
@@ -1328,7 +1321,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>20</v>
@@ -1349,7 +1342,7 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
     </row>
-    <row r="9" spans="1:29" ht="30.6" customHeight="1">
+    <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>30</v>
@@ -1383,13 +1376,13 @@
         <v>21</v>
       </c>
       <c r="M9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1406,10 +1399,10 @@
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75" customHeight="1">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -1430,7 +1423,7 @@
         <v>750</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J10" s="1">
         <v>200</v>
@@ -1439,16 +1432,16 @@
         <v>70</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1465,10 +1458,10 @@
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
     </row>
-    <row r="11" spans="1:29" ht="39.6" customHeight="1">
+    <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1">
         <v>17</v>
@@ -1489,7 +1482,7 @@
         <v>900</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1">
         <v>800</v>
@@ -1498,16 +1491,16 @@
         <v>30</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1524,7 +1517,7 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1555,7 +1548,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75" customHeight="1">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1586,7 +1579,7 @@
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
     </row>
-    <row r="14" spans="1:29" ht="15.75" customHeight="1">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1617,7 +1610,7 @@
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
     </row>
-    <row r="15" spans="1:29" ht="15.75" customHeight="1">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1648,7 +1641,7 @@
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75" customHeight="1">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1679,7 +1672,7 @@
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75" customHeight="1">
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1710,7 +1703,7 @@
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75" customHeight="1">
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1741,7 +1734,7 @@
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
     </row>
-    <row r="19" spans="1:29" ht="15.75" customHeight="1">
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1772,7 +1765,7 @@
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75" customHeight="1">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1803,7 +1796,7 @@
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75" customHeight="1">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1834,7 +1827,7 @@
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75" customHeight="1">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1865,7 +1858,7 @@
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75" customHeight="1">
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1896,7 +1889,7 @@
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75" customHeight="1">
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1927,7 +1920,7 @@
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75" customHeight="1">
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1958,7 +1951,7 @@
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75" customHeight="1">
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1989,7 +1982,7 @@
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75" customHeight="1">
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2020,7 +2013,7 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75" customHeight="1">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2051,7 +2044,7 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2082,7 +2075,7 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75" customHeight="1">
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2113,7 +2106,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75" customHeight="1">
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2144,7 +2137,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" spans="1:29" ht="15.75" customHeight="1">
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2175,7 +2168,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75" customHeight="1">
+    <row r="33" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2206,7 +2199,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" customHeight="1">
+    <row r="34" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2237,7 +2230,7 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75" customHeight="1">
+    <row r="35" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2268,7 +2261,7 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75" customHeight="1">
+    <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2299,7 +2292,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="1:29" ht="13.2">
+    <row r="37" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2330,7 +2323,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="1:29" ht="13.2">
+    <row r="38" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2361,7 +2354,7 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="1:29" ht="13.2">
+    <row r="39" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2392,7 +2385,7 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
     </row>
-    <row r="40" spans="1:29" ht="13.2">
+    <row r="40" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2423,7 +2416,7 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
     </row>
-    <row r="41" spans="1:29" ht="13.2">
+    <row r="41" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2454,7 +2447,7 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
     </row>
-    <row r="42" spans="1:29" ht="13.2">
+    <row r="42" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2485,7 +2478,7 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
     </row>
-    <row r="43" spans="1:29" ht="13.2">
+    <row r="43" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2516,7 +2509,7 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
     </row>
-    <row r="44" spans="1:29" ht="13.2">
+    <row r="44" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2547,7 +2540,7 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
     </row>
-    <row r="45" spans="1:29" ht="13.2">
+    <row r="45" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2578,7 +2571,7 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
     </row>
-    <row r="46" spans="1:29" ht="13.2">
+    <row r="46" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2609,7 +2602,7 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
     </row>
-    <row r="47" spans="1:29" ht="13.2">
+    <row r="47" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2640,7 +2633,7 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
     </row>
-    <row r="48" spans="1:29" ht="13.2">
+    <row r="48" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2671,7 +2664,7 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
     </row>
-    <row r="49" spans="1:29" ht="13.2">
+    <row r="49" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2702,7 +2695,7 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
     </row>
-    <row r="50" spans="1:29" ht="13.2">
+    <row r="50" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2733,7 +2726,7 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
     </row>
-    <row r="51" spans="1:29" ht="13.2">
+    <row r="51" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2764,7 +2757,7 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" spans="1:29" ht="13.2">
+    <row r="52" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2795,7 +2788,7 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
     </row>
-    <row r="53" spans="1:29" ht="13.2">
+    <row r="53" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2826,7 +2819,7 @@
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
     </row>
-    <row r="54" spans="1:29" ht="13.2">
+    <row r="54" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2857,7 +2850,7 @@
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
     </row>
-    <row r="55" spans="1:29" ht="13.2">
+    <row r="55" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2888,7 +2881,7 @@
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
     </row>
-    <row r="56" spans="1:29" ht="13.2">
+    <row r="56" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2919,7 +2912,7 @@
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
     </row>
-    <row r="57" spans="1:29" ht="13.2">
+    <row r="57" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2950,7 +2943,7 @@
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
     </row>
-    <row r="58" spans="1:29" ht="13.2">
+    <row r="58" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2981,7 +2974,7 @@
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
     </row>
-    <row r="59" spans="1:29" ht="13.2">
+    <row r="59" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3012,7 +3005,7 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
     </row>
-    <row r="60" spans="1:29" ht="13.2">
+    <row r="60" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3043,7 +3036,7 @@
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
     </row>
-    <row r="61" spans="1:29" ht="13.2">
+    <row r="61" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3074,7 +3067,7 @@
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
     </row>
-    <row r="62" spans="1:29" ht="13.2">
+    <row r="62" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3105,7 +3098,7 @@
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
     </row>
-    <row r="63" spans="1:29" ht="13.2">
+    <row r="63" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3136,7 +3129,7 @@
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
     </row>
-    <row r="64" spans="1:29" ht="13.2">
+    <row r="64" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3167,7 +3160,7 @@
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
     </row>
-    <row r="65" spans="1:29" ht="13.2">
+    <row r="65" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3198,7 +3191,7 @@
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
     </row>
-    <row r="66" spans="1:29" ht="13.2">
+    <row r="66" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3229,7 +3222,7 @@
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
     </row>
-    <row r="67" spans="1:29" ht="13.2">
+    <row r="67" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3260,7 +3253,7 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
     </row>
-    <row r="68" spans="1:29" ht="13.2">
+    <row r="68" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3291,7 +3284,7 @@
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
     </row>
-    <row r="69" spans="1:29" ht="13.2">
+    <row r="69" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3322,7 +3315,7 @@
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
     </row>
-    <row r="70" spans="1:29" ht="13.2">
+    <row r="70" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3353,7 +3346,7 @@
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
     </row>
-    <row r="71" spans="1:29" ht="13.2">
+    <row r="71" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3384,7 +3377,7 @@
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
     </row>
-    <row r="72" spans="1:29" ht="13.2">
+    <row r="72" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3415,7 +3408,7 @@
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
     </row>
-    <row r="73" spans="1:29" ht="13.2">
+    <row r="73" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3446,7 +3439,7 @@
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
     </row>
-    <row r="74" spans="1:29" ht="13.2">
+    <row r="74" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3477,7 +3470,7 @@
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
     </row>
-    <row r="75" spans="1:29" ht="13.2">
+    <row r="75" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3508,7 +3501,7 @@
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
     </row>
-    <row r="76" spans="1:29" ht="13.2">
+    <row r="76" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3539,7 +3532,7 @@
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
     </row>
-    <row r="77" spans="1:29" ht="13.2">
+    <row r="77" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3570,7 +3563,7 @@
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="13.2">
+    <row r="78" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3601,7 +3594,7 @@
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
     </row>
-    <row r="79" spans="1:29" ht="13.2">
+    <row r="79" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3632,7 +3625,7 @@
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
     </row>
-    <row r="80" spans="1:29" ht="13.2">
+    <row r="80" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3663,7 +3656,7 @@
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
     </row>
-    <row r="81" spans="1:29" ht="13.2">
+    <row r="81" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3694,7 +3687,7 @@
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
     </row>
-    <row r="82" spans="1:29" ht="13.2">
+    <row r="82" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3725,7 +3718,7 @@
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
     </row>
-    <row r="83" spans="1:29" ht="13.2">
+    <row r="83" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3756,7 +3749,7 @@
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
     </row>
-    <row r="84" spans="1:29" ht="13.2">
+    <row r="84" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3787,7 +3780,7 @@
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
     </row>
-    <row r="85" spans="1:29" ht="13.2">
+    <row r="85" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3818,7 +3811,7 @@
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
     </row>
-    <row r="86" spans="1:29" ht="13.2">
+    <row r="86" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3849,7 +3842,7 @@
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
     </row>
-    <row r="87" spans="1:29" ht="13.2">
+    <row r="87" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3880,7 +3873,7 @@
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
     </row>
-    <row r="88" spans="1:29" ht="13.2">
+    <row r="88" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3911,7 +3904,7 @@
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
     </row>
-    <row r="89" spans="1:29" ht="13.2">
+    <row r="89" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3942,7 +3935,7 @@
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
     </row>
-    <row r="90" spans="1:29" ht="13.2">
+    <row r="90" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3973,7 +3966,7 @@
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
     </row>
-    <row r="91" spans="1:29" ht="13.2">
+    <row r="91" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4004,7 +3997,7 @@
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
     </row>
-    <row r="92" spans="1:29" ht="13.2">
+    <row r="92" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4035,7 +4028,7 @@
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
     </row>
-    <row r="93" spans="1:29" ht="13.2">
+    <row r="93" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4066,7 +4059,7 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
     </row>
-    <row r="94" spans="1:29" ht="13.2">
+    <row r="94" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4097,7 +4090,7 @@
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
     </row>
-    <row r="95" spans="1:29" ht="13.2">
+    <row r="95" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4128,7 +4121,7 @@
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
     </row>
-    <row r="96" spans="1:29" ht="13.2">
+    <row r="96" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4159,7 +4152,7 @@
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
     </row>
-    <row r="97" spans="1:29" ht="13.2">
+    <row r="97" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4190,7 +4183,7 @@
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
     </row>
-    <row r="98" spans="1:29" ht="13.2">
+    <row r="98" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4221,7 +4214,7 @@
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
     </row>
-    <row r="99" spans="1:29" ht="13.2">
+    <row r="99" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4252,7 +4245,7 @@
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
     </row>
-    <row r="100" spans="1:29" ht="13.2">
+    <row r="100" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4283,7 +4276,7 @@
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
     </row>
-    <row r="101" spans="1:29" ht="13.2">
+    <row r="101" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4314,7 +4307,7 @@
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
     </row>
-    <row r="102" spans="1:29" ht="13.2">
+    <row r="102" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4345,7 +4338,7 @@
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
     </row>
-    <row r="103" spans="1:29" ht="13.2">
+    <row r="103" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4376,7 +4369,7 @@
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
     </row>
-    <row r="104" spans="1:29" ht="13.2">
+    <row r="104" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4407,7 +4400,7 @@
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
     </row>
-    <row r="105" spans="1:29" ht="13.2">
+    <row r="105" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4438,7 +4431,7 @@
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
     </row>
-    <row r="106" spans="1:29" ht="13.2">
+    <row r="106" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4469,7 +4462,7 @@
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
     </row>
-    <row r="107" spans="1:29" ht="13.2">
+    <row r="107" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4500,7 +4493,7 @@
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
     </row>
-    <row r="108" spans="1:29" ht="13.2">
+    <row r="108" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4531,7 +4524,7 @@
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
     </row>
-    <row r="109" spans="1:29" ht="13.2">
+    <row r="109" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4562,7 +4555,7 @@
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
     </row>
-    <row r="110" spans="1:29" ht="13.2">
+    <row r="110" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4593,7 +4586,7 @@
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
     </row>
-    <row r="111" spans="1:29" ht="13.2">
+    <row r="111" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4624,7 +4617,7 @@
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
     </row>
-    <row r="112" spans="1:29" ht="13.2">
+    <row r="112" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4655,7 +4648,7 @@
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="13.2">
+    <row r="113" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4686,7 +4679,7 @@
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="13.2">
+    <row r="114" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4717,7 +4710,7 @@
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
     </row>
-    <row r="115" spans="1:29" ht="13.2">
+    <row r="115" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4748,7 +4741,7 @@
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="13.2">
+    <row r="116" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4779,7 +4772,7 @@
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="13.2">
+    <row r="117" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4810,7 +4803,7 @@
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="13.2">
+    <row r="118" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4841,7 +4834,7 @@
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="13.2">
+    <row r="119" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4872,7 +4865,7 @@
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="13.2">
+    <row r="120" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4903,7 +4896,7 @@
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
     </row>
-    <row r="121" spans="1:29" ht="13.2">
+    <row r="121" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4934,7 +4927,7 @@
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
     </row>
-    <row r="122" spans="1:29" ht="13.2">
+    <row r="122" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4965,7 +4958,7 @@
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
     </row>
-    <row r="123" spans="1:29" ht="13.2">
+    <row r="123" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4996,7 +4989,7 @@
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
     </row>
-    <row r="124" spans="1:29" ht="13.2">
+    <row r="124" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5027,7 +5020,7 @@
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
     </row>
-    <row r="125" spans="1:29" ht="13.2">
+    <row r="125" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5058,7 +5051,7 @@
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
     </row>
-    <row r="126" spans="1:29" ht="13.2">
+    <row r="126" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5089,7 +5082,7 @@
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
     </row>
-    <row r="127" spans="1:29" ht="13.2">
+    <row r="127" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5120,7 +5113,7 @@
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
     </row>
-    <row r="128" spans="1:29" ht="13.2">
+    <row r="128" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5151,7 +5144,7 @@
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
     </row>
-    <row r="129" spans="1:29" ht="13.2">
+    <row r="129" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5182,7 +5175,7 @@
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
     </row>
-    <row r="130" spans="1:29" ht="13.2">
+    <row r="130" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5213,7 +5206,7 @@
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
     </row>
-    <row r="131" spans="1:29" ht="13.2">
+    <row r="131" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5244,7 +5237,7 @@
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
     </row>
-    <row r="132" spans="1:29" ht="13.2">
+    <row r="132" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5275,7 +5268,7 @@
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
     </row>
-    <row r="133" spans="1:29" ht="13.2">
+    <row r="133" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5306,7 +5299,7 @@
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
     </row>
-    <row r="134" spans="1:29" ht="13.2">
+    <row r="134" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5337,7 +5330,7 @@
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="13.2">
+    <row r="135" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5368,7 +5361,7 @@
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="13.2">
+    <row r="136" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5399,7 +5392,7 @@
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="13.2">
+    <row r="137" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5430,7 +5423,7 @@
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="13.2">
+    <row r="138" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5461,7 +5454,7 @@
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="13.2">
+    <row r="139" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5492,7 +5485,7 @@
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="13.2">
+    <row r="140" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5523,7 +5516,7 @@
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="13.2">
+    <row r="141" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5554,7 +5547,7 @@
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
     </row>
-    <row r="142" spans="1:29" ht="13.2">
+    <row r="142" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5585,7 +5578,7 @@
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
     </row>
-    <row r="143" spans="1:29" ht="13.2">
+    <row r="143" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5616,7 +5609,7 @@
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
     </row>
-    <row r="144" spans="1:29" ht="13.2">
+    <row r="144" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5647,7 +5640,7 @@
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
     </row>
-    <row r="145" spans="1:29" ht="13.2">
+    <row r="145" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5678,7 +5671,7 @@
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
     </row>
-    <row r="146" spans="1:29" ht="13.2">
+    <row r="146" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5709,7 +5702,7 @@
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
     </row>
-    <row r="147" spans="1:29" ht="13.2">
+    <row r="147" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5740,7 +5733,7 @@
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
     </row>
-    <row r="148" spans="1:29" ht="13.2">
+    <row r="148" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5771,7 +5764,7 @@
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
     </row>
-    <row r="149" spans="1:29" ht="13.2">
+    <row r="149" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5802,7 +5795,7 @@
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
     </row>
-    <row r="150" spans="1:29" ht="13.2">
+    <row r="150" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5833,7 +5826,7 @@
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
     </row>
-    <row r="151" spans="1:29" ht="13.2">
+    <row r="151" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5864,7 +5857,7 @@
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
     </row>
-    <row r="152" spans="1:29" ht="13.2">
+    <row r="152" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5895,7 +5888,7 @@
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
     </row>
-    <row r="153" spans="1:29" ht="13.2">
+    <row r="153" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5926,7 +5919,7 @@
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
     </row>
-    <row r="154" spans="1:29" ht="13.2">
+    <row r="154" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5957,7 +5950,7 @@
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
     </row>
-    <row r="155" spans="1:29" ht="13.2">
+    <row r="155" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5988,7 +5981,7 @@
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
     </row>
-    <row r="156" spans="1:29" ht="13.2">
+    <row r="156" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6019,7 +6012,7 @@
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
     </row>
-    <row r="157" spans="1:29" ht="13.2">
+    <row r="157" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6050,7 +6043,7 @@
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
     </row>
-    <row r="158" spans="1:29" ht="13.2">
+    <row r="158" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6081,7 +6074,7 @@
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
     </row>
-    <row r="159" spans="1:29" ht="13.2">
+    <row r="159" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6112,7 +6105,7 @@
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
     </row>
-    <row r="160" spans="1:29" ht="13.2">
+    <row r="160" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6143,7 +6136,7 @@
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
     </row>
-    <row r="161" spans="1:29" ht="13.2">
+    <row r="161" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6174,7 +6167,7 @@
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
     </row>
-    <row r="162" spans="1:29" ht="13.2">
+    <row r="162" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6205,7 +6198,7 @@
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
     </row>
-    <row r="163" spans="1:29" ht="13.2">
+    <row r="163" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6236,7 +6229,7 @@
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
     </row>
-    <row r="164" spans="1:29" ht="13.2">
+    <row r="164" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6267,7 +6260,7 @@
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
     </row>
-    <row r="165" spans="1:29" ht="13.2">
+    <row r="165" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6298,7 +6291,7 @@
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
     </row>
-    <row r="166" spans="1:29" ht="13.2">
+    <row r="166" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6329,7 +6322,7 @@
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
     </row>
-    <row r="167" spans="1:29" ht="13.2">
+    <row r="167" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6360,7 +6353,7 @@
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
     </row>
-    <row r="168" spans="1:29" ht="13.2">
+    <row r="168" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6391,7 +6384,7 @@
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
     </row>
-    <row r="169" spans="1:29" ht="13.2">
+    <row r="169" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6422,7 +6415,7 @@
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
     </row>
-    <row r="170" spans="1:29" ht="13.2">
+    <row r="170" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6453,7 +6446,7 @@
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
     </row>
-    <row r="171" spans="1:29" ht="13.2">
+    <row r="171" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6484,7 +6477,7 @@
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
     </row>
-    <row r="172" spans="1:29" ht="13.2">
+    <row r="172" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6515,7 +6508,7 @@
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
     </row>
-    <row r="173" spans="1:29" ht="13.2">
+    <row r="173" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6546,7 +6539,7 @@
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
     </row>
-    <row r="174" spans="1:29" ht="13.2">
+    <row r="174" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6577,7 +6570,7 @@
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
     </row>
-    <row r="175" spans="1:29" ht="13.2">
+    <row r="175" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6608,7 +6601,7 @@
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
     </row>
-    <row r="176" spans="1:29" ht="13.2">
+    <row r="176" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6639,7 +6632,7 @@
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
     </row>
-    <row r="177" spans="1:29" ht="13.2">
+    <row r="177" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6670,7 +6663,7 @@
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
     </row>
-    <row r="178" spans="1:29" ht="13.2">
+    <row r="178" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6701,7 +6694,7 @@
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
     </row>
-    <row r="179" spans="1:29" ht="13.2">
+    <row r="179" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6732,7 +6725,7 @@
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
     </row>
-    <row r="180" spans="1:29" ht="13.2">
+    <row r="180" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6763,7 +6756,7 @@
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
     </row>
-    <row r="181" spans="1:29" ht="13.2">
+    <row r="181" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6794,7 +6787,7 @@
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
     </row>
-    <row r="182" spans="1:29" ht="13.2">
+    <row r="182" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6825,7 +6818,7 @@
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
     </row>
-    <row r="183" spans="1:29" ht="13.2">
+    <row r="183" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6856,7 +6849,7 @@
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
     </row>
-    <row r="184" spans="1:29" ht="13.2">
+    <row r="184" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6887,7 +6880,7 @@
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
     </row>
-    <row r="185" spans="1:29" ht="13.2">
+    <row r="185" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6918,7 +6911,7 @@
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
     </row>
-    <row r="186" spans="1:29" ht="13.2">
+    <row r="186" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6949,7 +6942,7 @@
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
     </row>
-    <row r="187" spans="1:29" ht="13.2">
+    <row r="187" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6980,7 +6973,7 @@
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
     </row>
-    <row r="188" spans="1:29" ht="13.2">
+    <row r="188" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7011,7 +7004,7 @@
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
     </row>
-    <row r="189" spans="1:29" ht="13.2">
+    <row r="189" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7042,7 +7035,7 @@
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
     </row>
-    <row r="190" spans="1:29" ht="13.2">
+    <row r="190" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7073,7 +7066,7 @@
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
     </row>
-    <row r="191" spans="1:29" ht="13.2">
+    <row r="191" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7104,7 +7097,7 @@
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
     </row>
-    <row r="192" spans="1:29" ht="13.2">
+    <row r="192" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7135,7 +7128,7 @@
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
     </row>
-    <row r="193" spans="1:29" ht="13.2">
+    <row r="193" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7166,7 +7159,7 @@
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
     </row>
-    <row r="194" spans="1:29" ht="13.2">
+    <row r="194" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7197,7 +7190,7 @@
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
     </row>
-    <row r="195" spans="1:29" ht="13.2">
+    <row r="195" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7228,7 +7221,7 @@
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
     </row>
-    <row r="196" spans="1:29" ht="13.2">
+    <row r="196" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7259,7 +7252,7 @@
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
     </row>
-    <row r="197" spans="1:29" ht="13.2">
+    <row r="197" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7290,7 +7283,7 @@
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
     </row>
-    <row r="198" spans="1:29" ht="13.2">
+    <row r="198" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7321,7 +7314,7 @@
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
     </row>
-    <row r="199" spans="1:29" ht="13.2">
+    <row r="199" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7352,7 +7345,7 @@
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
     </row>
-    <row r="200" spans="1:29" ht="13.2">
+    <row r="200" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7383,7 +7376,7 @@
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
     </row>
-    <row r="201" spans="1:29" ht="13.2">
+    <row r="201" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7414,7 +7407,7 @@
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
     </row>
-    <row r="202" spans="1:29" ht="13.2">
+    <row r="202" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7445,7 +7438,7 @@
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
     </row>
-    <row r="203" spans="1:29" ht="13.2">
+    <row r="203" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7476,7 +7469,7 @@
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
     </row>
-    <row r="204" spans="1:29" ht="13.2">
+    <row r="204" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7507,7 +7500,7 @@
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
     </row>
-    <row r="205" spans="1:29" ht="13.2">
+    <row r="205" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7538,7 +7531,7 @@
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
     </row>
-    <row r="206" spans="1:29" ht="13.2">
+    <row r="206" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7569,7 +7562,7 @@
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
     </row>
-    <row r="207" spans="1:29" ht="13.2">
+    <row r="207" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7600,7 +7593,7 @@
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
     </row>
-    <row r="208" spans="1:29" ht="13.2">
+    <row r="208" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7631,7 +7624,7 @@
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
     </row>
-    <row r="209" spans="1:29" ht="13.2">
+    <row r="209" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7662,7 +7655,7 @@
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
     </row>
-    <row r="210" spans="1:29" ht="13.2">
+    <row r="210" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7693,7 +7686,7 @@
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
     </row>
-    <row r="211" spans="1:29" ht="13.2">
+    <row r="211" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7724,7 +7717,7 @@
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
     </row>
-    <row r="212" spans="1:29" ht="13.2">
+    <row r="212" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7755,7 +7748,7 @@
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
     </row>
-    <row r="213" spans="1:29" ht="13.2">
+    <row r="213" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7786,7 +7779,7 @@
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
     </row>
-    <row r="214" spans="1:29" ht="13.2">
+    <row r="214" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7817,7 +7810,7 @@
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
     </row>
-    <row r="215" spans="1:29" ht="13.2">
+    <row r="215" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7848,7 +7841,7 @@
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
     </row>
-    <row r="216" spans="1:29" ht="13.2">
+    <row r="216" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7879,7 +7872,7 @@
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
     </row>
-    <row r="217" spans="1:29" ht="13.2">
+    <row r="217" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7910,7 +7903,7 @@
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
     </row>
-    <row r="218" spans="1:29" ht="13.2">
+    <row r="218" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7941,7 +7934,7 @@
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
     </row>
-    <row r="219" spans="1:29" ht="13.2">
+    <row r="219" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7972,7 +7965,7 @@
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
     </row>
-    <row r="220" spans="1:29" ht="13.2">
+    <row r="220" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8003,7 +7996,7 @@
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
     </row>
-    <row r="221" spans="1:29" ht="13.2">
+    <row r="221" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8034,7 +8027,7 @@
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
     </row>
-    <row r="222" spans="1:29" ht="13.2">
+    <row r="222" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8065,7 +8058,7 @@
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
     </row>
-    <row r="223" spans="1:29" ht="13.2">
+    <row r="223" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8096,7 +8089,7 @@
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
     </row>
-    <row r="224" spans="1:29" ht="13.2">
+    <row r="224" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8127,7 +8120,7 @@
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
     </row>
-    <row r="225" spans="1:29" ht="13.2">
+    <row r="225" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8158,7 +8151,7 @@
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
     </row>
-    <row r="226" spans="1:29" ht="13.2">
+    <row r="226" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8189,7 +8182,7 @@
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
     </row>
-    <row r="227" spans="1:29" ht="13.2">
+    <row r="227" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8220,7 +8213,7 @@
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
     </row>
-    <row r="228" spans="1:29" ht="13.2">
+    <row r="228" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8251,7 +8244,7 @@
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
     </row>
-    <row r="229" spans="1:29" ht="13.2">
+    <row r="229" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8282,7 +8275,7 @@
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
     </row>
-    <row r="230" spans="1:29" ht="13.2">
+    <row r="230" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8313,7 +8306,7 @@
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
     </row>
-    <row r="231" spans="1:29" ht="13.2">
+    <row r="231" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8344,7 +8337,7 @@
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
     </row>
-    <row r="232" spans="1:29" ht="13.2">
+    <row r="232" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8375,7 +8368,7 @@
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
     </row>
-    <row r="233" spans="1:29" ht="13.2">
+    <row r="233" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8406,7 +8399,7 @@
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
     </row>
-    <row r="234" spans="1:29" ht="13.2">
+    <row r="234" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8437,7 +8430,7 @@
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
     </row>
-    <row r="235" spans="1:29" ht="13.2">
+    <row r="235" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8468,7 +8461,7 @@
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
     </row>
-    <row r="236" spans="1:29" ht="13.2">
+    <row r="236" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8499,7 +8492,7 @@
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
     </row>
-    <row r="237" spans="1:29" ht="13.2">
+    <row r="237" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8530,7 +8523,7 @@
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
     </row>
-    <row r="238" spans="1:29" ht="13.2">
+    <row r="238" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8561,7 +8554,7 @@
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
     </row>
-    <row r="239" spans="1:29" ht="13.2">
+    <row r="239" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8592,7 +8585,7 @@
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
     </row>
-    <row r="240" spans="1:29" ht="13.2">
+    <row r="240" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8623,7 +8616,7 @@
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
     </row>
-    <row r="241" spans="1:29" ht="13.2">
+    <row r="241" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8654,7 +8647,7 @@
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
     </row>
-    <row r="242" spans="1:29" ht="13.2">
+    <row r="242" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8685,7 +8678,7 @@
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
     </row>
-    <row r="243" spans="1:29" ht="13.2">
+    <row r="243" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8716,7 +8709,7 @@
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
     </row>
-    <row r="244" spans="1:29" ht="13.2">
+    <row r="244" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8747,7 +8740,7 @@
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
     </row>
-    <row r="245" spans="1:29" ht="13.2">
+    <row r="245" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8778,7 +8771,7 @@
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
     </row>
-    <row r="246" spans="1:29" ht="13.2">
+    <row r="246" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -8809,7 +8802,7 @@
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
     </row>
-    <row r="247" spans="1:29" ht="13.2">
+    <row r="247" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -8840,7 +8833,7 @@
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
     </row>
-    <row r="248" spans="1:29" ht="13.2">
+    <row r="248" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -8871,7 +8864,7 @@
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
     </row>
-    <row r="249" spans="1:29" ht="13.2">
+    <row r="249" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8902,7 +8895,7 @@
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
     </row>
-    <row r="250" spans="1:29" ht="13.2">
+    <row r="250" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8933,7 +8926,7 @@
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
     </row>
-    <row r="251" spans="1:29" ht="13.2">
+    <row r="251" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8964,7 +8957,7 @@
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
     </row>
-    <row r="252" spans="1:29" ht="13.2">
+    <row r="252" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8995,7 +8988,7 @@
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
     </row>
-    <row r="253" spans="1:29" ht="13.2">
+    <row r="253" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -9026,7 +9019,7 @@
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
     </row>
-    <row r="254" spans="1:29" ht="13.2">
+    <row r="254" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9057,7 +9050,7 @@
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
     </row>
-    <row r="255" spans="1:29" ht="13.2">
+    <row r="255" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9088,7 +9081,7 @@
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
     </row>
-    <row r="256" spans="1:29" ht="13.2">
+    <row r="256" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9119,7 +9112,7 @@
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
     </row>
-    <row r="257" spans="1:29" ht="13.2">
+    <row r="257" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9150,7 +9143,7 @@
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
     </row>
-    <row r="258" spans="1:29" ht="13.2">
+    <row r="258" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9181,7 +9174,7 @@
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
     </row>
-    <row r="259" spans="1:29" ht="13.2">
+    <row r="259" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9212,7 +9205,7 @@
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
     </row>
-    <row r="260" spans="1:29" ht="13.2">
+    <row r="260" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9243,7 +9236,7 @@
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
     </row>
-    <row r="261" spans="1:29" ht="13.2">
+    <row r="261" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9274,7 +9267,7 @@
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
     </row>
-    <row r="262" spans="1:29" ht="13.2">
+    <row r="262" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9305,7 +9298,7 @@
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
     </row>
-    <row r="263" spans="1:29" ht="13.2">
+    <row r="263" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9336,7 +9329,7 @@
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
     </row>
-    <row r="264" spans="1:29" ht="13.2">
+    <row r="264" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9367,7 +9360,7 @@
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
     </row>
-    <row r="265" spans="1:29" ht="13.2">
+    <row r="265" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9398,7 +9391,7 @@
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
     </row>
-    <row r="266" spans="1:29" ht="13.2">
+    <row r="266" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9429,7 +9422,7 @@
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
     </row>
-    <row r="267" spans="1:29" ht="13.2">
+    <row r="267" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9460,7 +9453,7 @@
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
     </row>
-    <row r="268" spans="1:29" ht="13.2">
+    <row r="268" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9491,7 +9484,7 @@
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
     </row>
-    <row r="269" spans="1:29" ht="13.2">
+    <row r="269" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9522,7 +9515,7 @@
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
     </row>
-    <row r="270" spans="1:29" ht="13.2">
+    <row r="270" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9553,7 +9546,7 @@
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
     </row>
-    <row r="271" spans="1:29" ht="13.2">
+    <row r="271" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9584,7 +9577,7 @@
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
     </row>
-    <row r="272" spans="1:29" ht="13.2">
+    <row r="272" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9615,7 +9608,7 @@
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
     </row>
-    <row r="273" spans="1:29" ht="13.2">
+    <row r="273" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9646,7 +9639,7 @@
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
     </row>
-    <row r="274" spans="1:29" ht="13.2">
+    <row r="274" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9677,7 +9670,7 @@
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
     </row>
-    <row r="275" spans="1:29" ht="13.2">
+    <row r="275" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9708,7 +9701,7 @@
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
     </row>
-    <row r="276" spans="1:29" ht="13.2">
+    <row r="276" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9739,7 +9732,7 @@
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
     </row>
-    <row r="277" spans="1:29" ht="13.2">
+    <row r="277" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9770,7 +9763,7 @@
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
     </row>
-    <row r="278" spans="1:29" ht="13.2">
+    <row r="278" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9801,7 +9794,7 @@
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
     </row>
-    <row r="279" spans="1:29" ht="13.2">
+    <row r="279" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9832,7 +9825,7 @@
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
     </row>
-    <row r="280" spans="1:29" ht="13.2">
+    <row r="280" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9863,7 +9856,7 @@
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
     </row>
-    <row r="281" spans="1:29" ht="13.2">
+    <row r="281" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9894,7 +9887,7 @@
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
     </row>
-    <row r="282" spans="1:29" ht="13.2">
+    <row r="282" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -9925,7 +9918,7 @@
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
     </row>
-    <row r="283" spans="1:29" ht="13.2">
+    <row r="283" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -9956,7 +9949,7 @@
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
     </row>
-    <row r="284" spans="1:29" ht="13.2">
+    <row r="284" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -9987,7 +9980,7 @@
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
     </row>
-    <row r="285" spans="1:29" ht="13.2">
+    <row r="285" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -10018,7 +10011,7 @@
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
     </row>
-    <row r="286" spans="1:29" ht="13.2">
+    <row r="286" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10049,7 +10042,7 @@
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
     </row>
-    <row r="287" spans="1:29" ht="13.2">
+    <row r="287" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10080,7 +10073,7 @@
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
     </row>
-    <row r="288" spans="1:29" ht="13.2">
+    <row r="288" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10111,7 +10104,7 @@
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
     </row>
-    <row r="289" spans="1:29" ht="13.2">
+    <row r="289" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10142,7 +10135,7 @@
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
     </row>
-    <row r="290" spans="1:29" ht="13.2">
+    <row r="290" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10173,7 +10166,7 @@
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
     </row>
-    <row r="291" spans="1:29" ht="13.2">
+    <row r="291" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10204,7 +10197,7 @@
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
     </row>
-    <row r="292" spans="1:29" ht="13.2">
+    <row r="292" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10235,7 +10228,7 @@
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
     </row>
-    <row r="293" spans="1:29" ht="13.2">
+    <row r="293" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10266,7 +10259,7 @@
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
     </row>
-    <row r="294" spans="1:29" ht="13.2">
+    <row r="294" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10297,7 +10290,7 @@
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
     </row>
-    <row r="295" spans="1:29" ht="13.2">
+    <row r="295" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10328,7 +10321,7 @@
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
     </row>
-    <row r="296" spans="1:29" ht="13.2">
+    <row r="296" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10359,7 +10352,7 @@
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
     </row>
-    <row r="297" spans="1:29" ht="13.2">
+    <row r="297" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10390,7 +10383,7 @@
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
     </row>
-    <row r="298" spans="1:29" ht="13.2">
+    <row r="298" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10421,7 +10414,7 @@
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
     </row>
-    <row r="299" spans="1:29" ht="13.2">
+    <row r="299" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10452,7 +10445,7 @@
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
     </row>
-    <row r="300" spans="1:29" ht="13.2">
+    <row r="300" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10483,7 +10476,7 @@
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
     </row>
-    <row r="301" spans="1:29" ht="13.2">
+    <row r="301" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10514,7 +10507,7 @@
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
     </row>
-    <row r="302" spans="1:29" ht="13.2">
+    <row r="302" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10545,7 +10538,7 @@
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
     </row>
-    <row r="303" spans="1:29" ht="13.2">
+    <row r="303" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10576,7 +10569,7 @@
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
     </row>
-    <row r="304" spans="1:29" ht="13.2">
+    <row r="304" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10607,7 +10600,7 @@
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
     </row>
-    <row r="305" spans="1:29" ht="13.2">
+    <row r="305" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10638,7 +10631,7 @@
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
     </row>
-    <row r="306" spans="1:29" ht="13.2">
+    <row r="306" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10669,7 +10662,7 @@
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
     </row>
-    <row r="307" spans="1:29" ht="13.2">
+    <row r="307" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10700,7 +10693,7 @@
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
     </row>
-    <row r="308" spans="1:29" ht="13.2">
+    <row r="308" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10731,7 +10724,7 @@
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
     </row>
-    <row r="309" spans="1:29" ht="13.2">
+    <row r="309" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10762,7 +10755,7 @@
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
     </row>
-    <row r="310" spans="1:29" ht="13.2">
+    <row r="310" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10793,7 +10786,7 @@
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
     </row>
-    <row r="311" spans="1:29" ht="13.2">
+    <row r="311" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10824,7 +10817,7 @@
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
     </row>
-    <row r="312" spans="1:29" ht="13.2">
+    <row r="312" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10855,7 +10848,7 @@
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
     </row>
-    <row r="313" spans="1:29" ht="13.2">
+    <row r="313" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10886,7 +10879,7 @@
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
     </row>
-    <row r="314" spans="1:29" ht="13.2">
+    <row r="314" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10917,7 +10910,7 @@
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
     </row>
-    <row r="315" spans="1:29" ht="13.2">
+    <row r="315" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10948,7 +10941,7 @@
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
     </row>
-    <row r="316" spans="1:29" ht="13.2">
+    <row r="316" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10979,7 +10972,7 @@
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
     </row>
-    <row r="317" spans="1:29" ht="13.2">
+    <row r="317" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11010,7 +11003,7 @@
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
     </row>
-    <row r="318" spans="1:29" ht="13.2">
+    <row r="318" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11041,7 +11034,7 @@
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
     </row>
-    <row r="319" spans="1:29" ht="13.2">
+    <row r="319" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11072,7 +11065,7 @@
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
     </row>
-    <row r="320" spans="1:29" ht="13.2">
+    <row r="320" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11103,7 +11096,7 @@
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
     </row>
-    <row r="321" spans="1:29" ht="13.2">
+    <row r="321" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11134,7 +11127,7 @@
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
     </row>
-    <row r="322" spans="1:29" ht="13.2">
+    <row r="322" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11165,7 +11158,7 @@
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
     </row>
-    <row r="323" spans="1:29" ht="13.2">
+    <row r="323" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11196,7 +11189,7 @@
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
     </row>
-    <row r="324" spans="1:29" ht="13.2">
+    <row r="324" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11227,7 +11220,7 @@
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
     </row>
-    <row r="325" spans="1:29" ht="13.2">
+    <row r="325" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11258,7 +11251,7 @@
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
     </row>
-    <row r="326" spans="1:29" ht="13.2">
+    <row r="326" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11289,7 +11282,7 @@
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
     </row>
-    <row r="327" spans="1:29" ht="13.2">
+    <row r="327" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11320,7 +11313,7 @@
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
     </row>
-    <row r="328" spans="1:29" ht="13.2">
+    <row r="328" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11351,7 +11344,7 @@
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
     </row>
-    <row r="329" spans="1:29" ht="13.2">
+    <row r="329" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11382,7 +11375,7 @@
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
     </row>
-    <row r="330" spans="1:29" ht="13.2">
+    <row r="330" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11413,7 +11406,7 @@
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
     </row>
-    <row r="331" spans="1:29" ht="13.2">
+    <row r="331" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11444,7 +11437,7 @@
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
     </row>
-    <row r="332" spans="1:29" ht="13.2">
+    <row r="332" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11475,7 +11468,7 @@
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
     </row>
-    <row r="333" spans="1:29" ht="13.2">
+    <row r="333" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11506,7 +11499,7 @@
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
     </row>
-    <row r="334" spans="1:29" ht="13.2">
+    <row r="334" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11537,7 +11530,7 @@
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
     </row>
-    <row r="335" spans="1:29" ht="13.2">
+    <row r="335" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11568,7 +11561,7 @@
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
     </row>
-    <row r="336" spans="1:29" ht="13.2">
+    <row r="336" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11599,7 +11592,7 @@
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
     </row>
-    <row r="337" spans="1:29" ht="13.2">
+    <row r="337" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11630,7 +11623,7 @@
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
     </row>
-    <row r="338" spans="1:29" ht="13.2">
+    <row r="338" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11661,7 +11654,7 @@
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
     </row>
-    <row r="339" spans="1:29" ht="13.2">
+    <row r="339" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11692,7 +11685,7 @@
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
     </row>
-    <row r="340" spans="1:29" ht="13.2">
+    <row r="340" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11723,7 +11716,7 @@
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
     </row>
-    <row r="341" spans="1:29" ht="13.2">
+    <row r="341" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11754,7 +11747,7 @@
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
     </row>
-    <row r="342" spans="1:29" ht="13.2">
+    <row r="342" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11785,7 +11778,7 @@
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
     </row>
-    <row r="343" spans="1:29" ht="13.2">
+    <row r="343" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11816,7 +11809,7 @@
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
     </row>
-    <row r="344" spans="1:29" ht="13.2">
+    <row r="344" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11847,7 +11840,7 @@
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
     </row>
-    <row r="345" spans="1:29" ht="13.2">
+    <row r="345" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11878,7 +11871,7 @@
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
     </row>
-    <row r="346" spans="1:29" ht="13.2">
+    <row r="346" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11909,7 +11902,7 @@
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
     </row>
-    <row r="347" spans="1:29" ht="13.2">
+    <row r="347" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11940,7 +11933,7 @@
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
     </row>
-    <row r="348" spans="1:29" ht="13.2">
+    <row r="348" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11971,7 +11964,7 @@
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
     </row>
-    <row r="349" spans="1:29" ht="13.2">
+    <row r="349" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -12002,7 +11995,7 @@
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
     </row>
-    <row r="350" spans="1:29" ht="13.2">
+    <row r="350" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -12033,7 +12026,7 @@
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
     </row>
-    <row r="351" spans="1:29" ht="13.2">
+    <row r="351" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12064,7 +12057,7 @@
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
     </row>
-    <row r="352" spans="1:29" ht="13.2">
+    <row r="352" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -12095,7 +12088,7 @@
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
     </row>
-    <row r="353" spans="1:29" ht="13.2">
+    <row r="353" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12126,7 +12119,7 @@
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
     </row>
-    <row r="354" spans="1:29" ht="13.2">
+    <row r="354" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12157,7 +12150,7 @@
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
     </row>
-    <row r="355" spans="1:29" ht="13.2">
+    <row r="355" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12188,7 +12181,7 @@
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
     </row>
-    <row r="356" spans="1:29" ht="13.2">
+    <row r="356" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12219,7 +12212,7 @@
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
     </row>
-    <row r="357" spans="1:29" ht="13.2">
+    <row r="357" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12250,7 +12243,7 @@
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
     </row>
-    <row r="358" spans="1:29" ht="13.2">
+    <row r="358" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12281,7 +12274,7 @@
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
     </row>
-    <row r="359" spans="1:29" ht="13.2">
+    <row r="359" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12312,7 +12305,7 @@
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
     </row>
-    <row r="360" spans="1:29" ht="13.2">
+    <row r="360" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12343,7 +12336,7 @@
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
     </row>
-    <row r="361" spans="1:29" ht="13.2">
+    <row r="361" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12374,7 +12367,7 @@
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
     </row>
-    <row r="362" spans="1:29" ht="13.2">
+    <row r="362" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12405,7 +12398,7 @@
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
     </row>
-    <row r="363" spans="1:29" ht="13.2">
+    <row r="363" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12436,7 +12429,7 @@
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
     </row>
-    <row r="364" spans="1:29" ht="13.2">
+    <row r="364" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12467,7 +12460,7 @@
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
     </row>
-    <row r="365" spans="1:29" ht="13.2">
+    <row r="365" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12498,7 +12491,7 @@
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
     </row>
-    <row r="366" spans="1:29" ht="13.2">
+    <row r="366" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12529,7 +12522,7 @@
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
     </row>
-    <row r="367" spans="1:29" ht="13.2">
+    <row r="367" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12560,7 +12553,7 @@
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
     </row>
-    <row r="368" spans="1:29" ht="13.2">
+    <row r="368" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12591,7 +12584,7 @@
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
     </row>
-    <row r="369" spans="1:29" ht="13.2">
+    <row r="369" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12622,7 +12615,7 @@
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
     </row>
-    <row r="370" spans="1:29" ht="13.2">
+    <row r="370" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12653,7 +12646,7 @@
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
     </row>
-    <row r="371" spans="1:29" ht="13.2">
+    <row r="371" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12684,7 +12677,7 @@
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
     </row>
-    <row r="372" spans="1:29" ht="13.2">
+    <row r="372" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12715,7 +12708,7 @@
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
     </row>
-    <row r="373" spans="1:29" ht="13.2">
+    <row r="373" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12746,7 +12739,7 @@
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
     </row>
-    <row r="374" spans="1:29" ht="13.2">
+    <row r="374" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12777,7 +12770,7 @@
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
     </row>
-    <row r="375" spans="1:29" ht="13.2">
+    <row r="375" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12808,7 +12801,7 @@
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
     </row>
-    <row r="376" spans="1:29" ht="13.2">
+    <row r="376" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12839,7 +12832,7 @@
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
     </row>
-    <row r="377" spans="1:29" ht="13.2">
+    <row r="377" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12870,7 +12863,7 @@
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
     </row>
-    <row r="378" spans="1:29" ht="13.2">
+    <row r="378" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12901,7 +12894,7 @@
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
     </row>
-    <row r="379" spans="1:29" ht="13.2">
+    <row r="379" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12932,7 +12925,7 @@
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
     </row>
-    <row r="380" spans="1:29" ht="13.2">
+    <row r="380" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12963,7 +12956,7 @@
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
     </row>
-    <row r="381" spans="1:29" ht="13.2">
+    <row r="381" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12994,7 +12987,7 @@
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
     </row>
-    <row r="382" spans="1:29" ht="13.2">
+    <row r="382" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -13025,7 +13018,7 @@
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
     </row>
-    <row r="383" spans="1:29" ht="13.2">
+    <row r="383" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -13056,7 +13049,7 @@
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
     </row>
-    <row r="384" spans="1:29" ht="13.2">
+    <row r="384" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -13087,7 +13080,7 @@
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
     </row>
-    <row r="385" spans="1:29" ht="13.2">
+    <row r="385" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -13118,7 +13111,7 @@
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
     </row>
-    <row r="386" spans="1:29" ht="13.2">
+    <row r="386" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -13149,7 +13142,7 @@
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
     </row>
-    <row r="387" spans="1:29" ht="13.2">
+    <row r="387" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -13180,7 +13173,7 @@
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
     </row>
-    <row r="388" spans="1:29" ht="13.2">
+    <row r="388" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -13211,7 +13204,7 @@
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
     </row>
-    <row r="389" spans="1:29" ht="13.2">
+    <row r="389" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13242,7 +13235,7 @@
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
     </row>
-    <row r="390" spans="1:29" ht="13.2">
+    <row r="390" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13273,7 +13266,7 @@
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
     </row>
-    <row r="391" spans="1:29" ht="13.2">
+    <row r="391" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13304,7 +13297,7 @@
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
     </row>
-    <row r="392" spans="1:29" ht="13.2">
+    <row r="392" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13335,7 +13328,7 @@
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
     </row>
-    <row r="393" spans="1:29" ht="13.2">
+    <row r="393" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13366,7 +13359,7 @@
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
     </row>
-    <row r="394" spans="1:29" ht="13.2">
+    <row r="394" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13397,7 +13390,7 @@
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
     </row>
-    <row r="395" spans="1:29" ht="13.2">
+    <row r="395" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13428,7 +13421,7 @@
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
     </row>
-    <row r="396" spans="1:29" ht="13.2">
+    <row r="396" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13459,7 +13452,7 @@
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
     </row>
-    <row r="397" spans="1:29" ht="13.2">
+    <row r="397" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13490,7 +13483,7 @@
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
     </row>
-    <row r="398" spans="1:29" ht="13.2">
+    <row r="398" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13521,7 +13514,7 @@
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
     </row>
-    <row r="399" spans="1:29" ht="13.2">
+    <row r="399" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13552,7 +13545,7 @@
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
     </row>
-    <row r="400" spans="1:29" ht="13.2">
+    <row r="400" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13583,7 +13576,7 @@
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
     </row>
-    <row r="401" spans="1:29" ht="13.2">
+    <row r="401" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13614,7 +13607,7 @@
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
     </row>
-    <row r="402" spans="1:29" ht="13.2">
+    <row r="402" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13645,7 +13638,7 @@
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
     </row>
-    <row r="403" spans="1:29" ht="13.2">
+    <row r="403" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13676,7 +13669,7 @@
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
     </row>
-    <row r="404" spans="1:29" ht="13.2">
+    <row r="404" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13707,7 +13700,7 @@
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
     </row>
-    <row r="405" spans="1:29" ht="13.2">
+    <row r="405" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13738,7 +13731,7 @@
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
     </row>
-    <row r="406" spans="1:29" ht="13.2">
+    <row r="406" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13769,7 +13762,7 @@
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
     </row>
-    <row r="407" spans="1:29" ht="13.2">
+    <row r="407" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13800,7 +13793,7 @@
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
     </row>
-    <row r="408" spans="1:29" ht="13.2">
+    <row r="408" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13831,7 +13824,7 @@
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
     </row>
-    <row r="409" spans="1:29" ht="13.2">
+    <row r="409" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13862,7 +13855,7 @@
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
     </row>
-    <row r="410" spans="1:29" ht="13.2">
+    <row r="410" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13893,7 +13886,7 @@
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
     </row>
-    <row r="411" spans="1:29" ht="13.2">
+    <row r="411" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13924,7 +13917,7 @@
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
     </row>
-    <row r="412" spans="1:29" ht="13.2">
+    <row r="412" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13955,7 +13948,7 @@
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
     </row>
-    <row r="413" spans="1:29" ht="13.2">
+    <row r="413" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13986,7 +13979,7 @@
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
     </row>
-    <row r="414" spans="1:29" ht="13.2">
+    <row r="414" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -14017,7 +14010,7 @@
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
     </row>
-    <row r="415" spans="1:29" ht="13.2">
+    <row r="415" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -14048,7 +14041,7 @@
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
     </row>
-    <row r="416" spans="1:29" ht="13.2">
+    <row r="416" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -14079,7 +14072,7 @@
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
     </row>
-    <row r="417" spans="1:29" ht="13.2">
+    <row r="417" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -14110,7 +14103,7 @@
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
     </row>
-    <row r="418" spans="1:29" ht="13.2">
+    <row r="418" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -14141,7 +14134,7 @@
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
     </row>
-    <row r="419" spans="1:29" ht="13.2">
+    <row r="419" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -14172,7 +14165,7 @@
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
     </row>
-    <row r="420" spans="1:29" ht="13.2">
+    <row r="420" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -14203,7 +14196,7 @@
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
     </row>
-    <row r="421" spans="1:29" ht="13.2">
+    <row r="421" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -14234,7 +14227,7 @@
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
     </row>
-    <row r="422" spans="1:29" ht="13.2">
+    <row r="422" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -14265,7 +14258,7 @@
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
     </row>
-    <row r="423" spans="1:29" ht="13.2">
+    <row r="423" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -14296,7 +14289,7 @@
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
     </row>
-    <row r="424" spans="1:29" ht="13.2">
+    <row r="424" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -14327,7 +14320,7 @@
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
     </row>
-    <row r="425" spans="1:29" ht="13.2">
+    <row r="425" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14358,7 +14351,7 @@
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
     </row>
-    <row r="426" spans="1:29" ht="13.2">
+    <row r="426" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14389,7 +14382,7 @@
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
     </row>
-    <row r="427" spans="1:29" ht="13.2">
+    <row r="427" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14420,7 +14413,7 @@
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
     </row>
-    <row r="428" spans="1:29" ht="13.2">
+    <row r="428" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14451,7 +14444,7 @@
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
     </row>
-    <row r="429" spans="1:29" ht="13.2">
+    <row r="429" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14482,7 +14475,7 @@
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
     </row>
-    <row r="430" spans="1:29" ht="13.2">
+    <row r="430" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14513,7 +14506,7 @@
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
     </row>
-    <row r="431" spans="1:29" ht="13.2">
+    <row r="431" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14544,7 +14537,7 @@
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
     </row>
-    <row r="432" spans="1:29" ht="13.2">
+    <row r="432" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14575,7 +14568,7 @@
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
     </row>
-    <row r="433" spans="1:29" ht="13.2">
+    <row r="433" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14606,7 +14599,7 @@
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
     </row>
-    <row r="434" spans="1:29" ht="13.2">
+    <row r="434" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14637,7 +14630,7 @@
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
     </row>
-    <row r="435" spans="1:29" ht="13.2">
+    <row r="435" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14668,7 +14661,7 @@
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
     </row>
-    <row r="436" spans="1:29" ht="13.2">
+    <row r="436" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14699,7 +14692,7 @@
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
     </row>
-    <row r="437" spans="1:29" ht="13.2">
+    <row r="437" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14730,7 +14723,7 @@
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
     </row>
-    <row r="438" spans="1:29" ht="13.2">
+    <row r="438" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14761,7 +14754,7 @@
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
     </row>
-    <row r="439" spans="1:29" ht="13.2">
+    <row r="439" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14792,7 +14785,7 @@
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
     </row>
-    <row r="440" spans="1:29" ht="13.2">
+    <row r="440" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14823,7 +14816,7 @@
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
     </row>
-    <row r="441" spans="1:29" ht="13.2">
+    <row r="441" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14854,7 +14847,7 @@
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
     </row>
-    <row r="442" spans="1:29" ht="13.2">
+    <row r="442" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14885,7 +14878,7 @@
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
     </row>
-    <row r="443" spans="1:29" ht="13.2">
+    <row r="443" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14916,7 +14909,7 @@
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
     </row>
-    <row r="444" spans="1:29" ht="13.2">
+    <row r="444" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14947,7 +14940,7 @@
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
     </row>
-    <row r="445" spans="1:29" ht="13.2">
+    <row r="445" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14978,7 +14971,7 @@
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
     </row>
-    <row r="446" spans="1:29" ht="13.2">
+    <row r="446" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -15009,7 +15002,7 @@
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
     </row>
-    <row r="447" spans="1:29" ht="13.2">
+    <row r="447" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -15040,7 +15033,7 @@
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
     </row>
-    <row r="448" spans="1:29" ht="13.2">
+    <row r="448" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -15071,7 +15064,7 @@
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
     </row>
-    <row r="449" spans="1:29" ht="13.2">
+    <row r="449" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -15102,7 +15095,7 @@
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
     </row>
-    <row r="450" spans="1:29" ht="13.2">
+    <row r="450" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -15133,7 +15126,7 @@
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
     </row>
-    <row r="451" spans="1:29" ht="13.2">
+    <row r="451" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -15164,7 +15157,7 @@
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
     </row>
-    <row r="452" spans="1:29" ht="13.2">
+    <row r="452" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -15195,7 +15188,7 @@
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
     </row>
-    <row r="453" spans="1:29" ht="13.2">
+    <row r="453" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -15226,7 +15219,7 @@
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
     </row>
-    <row r="454" spans="1:29" ht="13.2">
+    <row r="454" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -15257,7 +15250,7 @@
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
     </row>
-    <row r="455" spans="1:29" ht="13.2">
+    <row r="455" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -15288,7 +15281,7 @@
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
     </row>
-    <row r="456" spans="1:29" ht="13.2">
+    <row r="456" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -15319,7 +15312,7 @@
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
     </row>
-    <row r="457" spans="1:29" ht="13.2">
+    <row r="457" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -15350,7 +15343,7 @@
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
     </row>
-    <row r="458" spans="1:29" ht="13.2">
+    <row r="458" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -15381,7 +15374,7 @@
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
     </row>
-    <row r="459" spans="1:29" ht="13.2">
+    <row r="459" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -15412,7 +15405,7 @@
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
     </row>
-    <row r="460" spans="1:29" ht="13.2">
+    <row r="460" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15443,7 +15436,7 @@
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
     </row>
-    <row r="461" spans="1:29" ht="13.2">
+    <row r="461" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15474,7 +15467,7 @@
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
     </row>
-    <row r="462" spans="1:29" ht="13.2">
+    <row r="462" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15505,7 +15498,7 @@
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
     </row>
-    <row r="463" spans="1:29" ht="13.2">
+    <row r="463" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15536,7 +15529,7 @@
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
     </row>
-    <row r="464" spans="1:29" ht="13.2">
+    <row r="464" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15567,7 +15560,7 @@
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
     </row>
-    <row r="465" spans="1:29" ht="13.2">
+    <row r="465" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15598,7 +15591,7 @@
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
     </row>
-    <row r="466" spans="1:29" ht="13.2">
+    <row r="466" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15629,7 +15622,7 @@
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
     </row>
-    <row r="467" spans="1:29" ht="13.2">
+    <row r="467" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15660,7 +15653,7 @@
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
     </row>
-    <row r="468" spans="1:29" ht="13.2">
+    <row r="468" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15691,7 +15684,7 @@
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
     </row>
-    <row r="469" spans="1:29" ht="13.2">
+    <row r="469" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15722,7 +15715,7 @@
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
     </row>
-    <row r="470" spans="1:29" ht="13.2">
+    <row r="470" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15753,7 +15746,7 @@
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
     </row>
-    <row r="471" spans="1:29" ht="13.2">
+    <row r="471" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15784,7 +15777,7 @@
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
     </row>
-    <row r="472" spans="1:29" ht="13.2">
+    <row r="472" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15815,7 +15808,7 @@
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
     </row>
-    <row r="473" spans="1:29" ht="13.2">
+    <row r="473" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15846,7 +15839,7 @@
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
     </row>
-    <row r="474" spans="1:29" ht="13.2">
+    <row r="474" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15877,7 +15870,7 @@
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
     </row>
-    <row r="475" spans="1:29" ht="13.2">
+    <row r="475" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15908,7 +15901,7 @@
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
     </row>
-    <row r="476" spans="1:29" ht="13.2">
+    <row r="476" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15939,7 +15932,7 @@
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
     </row>
-    <row r="477" spans="1:29" ht="13.2">
+    <row r="477" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15970,7 +15963,7 @@
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
     </row>
-    <row r="478" spans="1:29" ht="13.2">
+    <row r="478" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -16001,7 +15994,7 @@
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
     </row>
-    <row r="479" spans="1:29" ht="13.2">
+    <row r="479" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -16032,7 +16025,7 @@
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
     </row>
-    <row r="480" spans="1:29" ht="13.2">
+    <row r="480" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -16063,7 +16056,7 @@
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
     </row>
-    <row r="481" spans="1:29" ht="13.2">
+    <row r="481" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -16094,7 +16087,7 @@
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
     </row>
-    <row r="482" spans="1:29" ht="13.2">
+    <row r="482" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -16125,7 +16118,7 @@
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
     </row>
-    <row r="483" spans="1:29" ht="13.2">
+    <row r="483" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -16156,7 +16149,7 @@
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
     </row>
-    <row r="484" spans="1:29" ht="13.2">
+    <row r="484" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -16187,7 +16180,7 @@
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
     </row>
-    <row r="485" spans="1:29" ht="13.2">
+    <row r="485" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -16218,7 +16211,7 @@
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
     </row>
-    <row r="486" spans="1:29" ht="13.2">
+    <row r="486" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -16249,7 +16242,7 @@
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
     </row>
-    <row r="487" spans="1:29" ht="13.2">
+    <row r="487" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -16280,7 +16273,7 @@
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
     </row>
-    <row r="488" spans="1:29" ht="13.2">
+    <row r="488" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -16311,7 +16304,7 @@
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
     </row>
-    <row r="489" spans="1:29" ht="13.2">
+    <row r="489" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -16342,7 +16335,7 @@
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
     </row>
-    <row r="490" spans="1:29" ht="13.2">
+    <row r="490" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -16373,7 +16366,7 @@
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
     </row>
-    <row r="491" spans="1:29" ht="13.2">
+    <row r="491" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -16404,7 +16397,7 @@
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
     </row>
-    <row r="492" spans="1:29" ht="13.2">
+    <row r="492" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -16435,7 +16428,7 @@
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
     </row>
-    <row r="493" spans="1:29" ht="13.2">
+    <row r="493" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -16466,7 +16459,7 @@
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
     </row>
-    <row r="494" spans="1:29" ht="13.2">
+    <row r="494" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -16497,7 +16490,7 @@
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
     </row>
-    <row r="495" spans="1:29" ht="13.2">
+    <row r="495" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -16528,7 +16521,7 @@
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
     </row>
-    <row r="496" spans="1:29" ht="13.2">
+    <row r="496" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16559,7 +16552,7 @@
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
     </row>
-    <row r="497" spans="1:29" ht="13.2">
+    <row r="497" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16590,7 +16583,7 @@
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
     </row>
-    <row r="498" spans="1:29" ht="13.2">
+    <row r="498" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16621,7 +16614,7 @@
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
     </row>
-    <row r="499" spans="1:29" ht="13.2">
+    <row r="499" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16652,7 +16645,7 @@
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
     </row>
-    <row r="500" spans="1:29" ht="13.2">
+    <row r="500" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16683,7 +16676,7 @@
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
     </row>
-    <row r="501" spans="1:29" ht="13.2">
+    <row r="501" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16714,7 +16707,7 @@
       <c r="AB501" s="1"/>
       <c r="AC501" s="1"/>
     </row>
-    <row r="502" spans="1:29" ht="13.2">
+    <row r="502" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16745,7 +16738,7 @@
       <c r="AB502" s="1"/>
       <c r="AC502" s="1"/>
     </row>
-    <row r="503" spans="1:29" ht="13.2">
+    <row r="503" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16776,7 +16769,7 @@
       <c r="AB503" s="1"/>
       <c r="AC503" s="1"/>
     </row>
-    <row r="504" spans="1:29" ht="13.2">
+    <row r="504" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16807,7 +16800,7 @@
       <c r="AB504" s="1"/>
       <c r="AC504" s="1"/>
     </row>
-    <row r="505" spans="1:29" ht="13.2">
+    <row r="505" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16838,7 +16831,7 @@
       <c r="AB505" s="1"/>
       <c r="AC505" s="1"/>
     </row>
-    <row r="506" spans="1:29" ht="13.2">
+    <row r="506" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16869,7 +16862,7 @@
       <c r="AB506" s="1"/>
       <c r="AC506" s="1"/>
     </row>
-    <row r="507" spans="1:29" ht="13.2">
+    <row r="507" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16900,7 +16893,7 @@
       <c r="AB507" s="1"/>
       <c r="AC507" s="1"/>
     </row>
-    <row r="508" spans="1:29" ht="13.2">
+    <row r="508" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16931,7 +16924,7 @@
       <c r="AB508" s="1"/>
       <c r="AC508" s="1"/>
     </row>
-    <row r="509" spans="1:29" ht="13.2">
+    <row r="509" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16962,7 +16955,7 @@
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
     </row>
-    <row r="510" spans="1:29" ht="13.2">
+    <row r="510" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16993,7 +16986,7 @@
       <c r="AB510" s="1"/>
       <c r="AC510" s="1"/>
     </row>
-    <row r="511" spans="1:29" ht="13.2">
+    <row r="511" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -17024,7 +17017,7 @@
       <c r="AB511" s="1"/>
       <c r="AC511" s="1"/>
     </row>
-    <row r="512" spans="1:29" ht="13.2">
+    <row r="512" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -17055,7 +17048,7 @@
       <c r="AB512" s="1"/>
       <c r="AC512" s="1"/>
     </row>
-    <row r="513" spans="1:29" ht="13.2">
+    <row r="513" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -17086,7 +17079,7 @@
       <c r="AB513" s="1"/>
       <c r="AC513" s="1"/>
     </row>
-    <row r="514" spans="1:29" ht="13.2">
+    <row r="514" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -17117,7 +17110,7 @@
       <c r="AB514" s="1"/>
       <c r="AC514" s="1"/>
     </row>
-    <row r="515" spans="1:29" ht="13.2">
+    <row r="515" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -17148,7 +17141,7 @@
       <c r="AB515" s="1"/>
       <c r="AC515" s="1"/>
     </row>
-    <row r="516" spans="1:29" ht="13.2">
+    <row r="516" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -17179,7 +17172,7 @@
       <c r="AB516" s="1"/>
       <c r="AC516" s="1"/>
     </row>
-    <row r="517" spans="1:29" ht="13.2">
+    <row r="517" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -17210,7 +17203,7 @@
       <c r="AB517" s="1"/>
       <c r="AC517" s="1"/>
     </row>
-    <row r="518" spans="1:29" ht="13.2">
+    <row r="518" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -17241,7 +17234,7 @@
       <c r="AB518" s="1"/>
       <c r="AC518" s="1"/>
     </row>
-    <row r="519" spans="1:29" ht="13.2">
+    <row r="519" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -17272,7 +17265,7 @@
       <c r="AB519" s="1"/>
       <c r="AC519" s="1"/>
     </row>
-    <row r="520" spans="1:29" ht="13.2">
+    <row r="520" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -17303,7 +17296,7 @@
       <c r="AB520" s="1"/>
       <c r="AC520" s="1"/>
     </row>
-    <row r="521" spans="1:29" ht="13.2">
+    <row r="521" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -17334,7 +17327,7 @@
       <c r="AB521" s="1"/>
       <c r="AC521" s="1"/>
     </row>
-    <row r="522" spans="1:29" ht="13.2">
+    <row r="522" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -17365,7 +17358,7 @@
       <c r="AB522" s="1"/>
       <c r="AC522" s="1"/>
     </row>
-    <row r="523" spans="1:29" ht="13.2">
+    <row r="523" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -17396,7 +17389,7 @@
       <c r="AB523" s="1"/>
       <c r="AC523" s="1"/>
     </row>
-    <row r="524" spans="1:29" ht="13.2">
+    <row r="524" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -17427,7 +17420,7 @@
       <c r="AB524" s="1"/>
       <c r="AC524" s="1"/>
     </row>
-    <row r="525" spans="1:29" ht="13.2">
+    <row r="525" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -17458,7 +17451,7 @@
       <c r="AB525" s="1"/>
       <c r="AC525" s="1"/>
     </row>
-    <row r="526" spans="1:29" ht="13.2">
+    <row r="526" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -17489,7 +17482,7 @@
       <c r="AB526" s="1"/>
       <c r="AC526" s="1"/>
     </row>
-    <row r="527" spans="1:29" ht="13.2">
+    <row r="527" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -17520,7 +17513,7 @@
       <c r="AB527" s="1"/>
       <c r="AC527" s="1"/>
     </row>
-    <row r="528" spans="1:29" ht="13.2">
+    <row r="528" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -17551,7 +17544,7 @@
       <c r="AB528" s="1"/>
       <c r="AC528" s="1"/>
     </row>
-    <row r="529" spans="1:29" ht="13.2">
+    <row r="529" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -17582,7 +17575,7 @@
       <c r="AB529" s="1"/>
       <c r="AC529" s="1"/>
     </row>
-    <row r="530" spans="1:29" ht="13.2">
+    <row r="530" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -17613,7 +17606,7 @@
       <c r="AB530" s="1"/>
       <c r="AC530" s="1"/>
     </row>
-    <row r="531" spans="1:29" ht="13.2">
+    <row r="531" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -17644,7 +17637,7 @@
       <c r="AB531" s="1"/>
       <c r="AC531" s="1"/>
     </row>
-    <row r="532" spans="1:29" ht="13.2">
+    <row r="532" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17675,7 +17668,7 @@
       <c r="AB532" s="1"/>
       <c r="AC532" s="1"/>
     </row>
-    <row r="533" spans="1:29" ht="13.2">
+    <row r="533" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17706,7 +17699,7 @@
       <c r="AB533" s="1"/>
       <c r="AC533" s="1"/>
     </row>
-    <row r="534" spans="1:29" ht="13.2">
+    <row r="534" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17737,7 +17730,7 @@
       <c r="AB534" s="1"/>
       <c r="AC534" s="1"/>
     </row>
-    <row r="535" spans="1:29" ht="13.2">
+    <row r="535" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17768,7 +17761,7 @@
       <c r="AB535" s="1"/>
       <c r="AC535" s="1"/>
     </row>
-    <row r="536" spans="1:29" ht="13.2">
+    <row r="536" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17799,7 +17792,7 @@
       <c r="AB536" s="1"/>
       <c r="AC536" s="1"/>
     </row>
-    <row r="537" spans="1:29" ht="13.2">
+    <row r="537" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17830,7 +17823,7 @@
       <c r="AB537" s="1"/>
       <c r="AC537" s="1"/>
     </row>
-    <row r="538" spans="1:29" ht="13.2">
+    <row r="538" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17861,7 +17854,7 @@
       <c r="AB538" s="1"/>
       <c r="AC538" s="1"/>
     </row>
-    <row r="539" spans="1:29" ht="13.2">
+    <row r="539" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17892,7 +17885,7 @@
       <c r="AB539" s="1"/>
       <c r="AC539" s="1"/>
     </row>
-    <row r="540" spans="1:29" ht="13.2">
+    <row r="540" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17923,7 +17916,7 @@
       <c r="AB540" s="1"/>
       <c r="AC540" s="1"/>
     </row>
-    <row r="541" spans="1:29" ht="13.2">
+    <row r="541" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17954,7 +17947,7 @@
       <c r="AB541" s="1"/>
       <c r="AC541" s="1"/>
     </row>
-    <row r="542" spans="1:29" ht="13.2">
+    <row r="542" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17985,7 +17978,7 @@
       <c r="AB542" s="1"/>
       <c r="AC542" s="1"/>
     </row>
-    <row r="543" spans="1:29" ht="13.2">
+    <row r="543" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -18016,7 +18009,7 @@
       <c r="AB543" s="1"/>
       <c r="AC543" s="1"/>
     </row>
-    <row r="544" spans="1:29" ht="13.2">
+    <row r="544" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -18047,7 +18040,7 @@
       <c r="AB544" s="1"/>
       <c r="AC544" s="1"/>
     </row>
-    <row r="545" spans="1:29" ht="13.2">
+    <row r="545" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -18078,7 +18071,7 @@
       <c r="AB545" s="1"/>
       <c r="AC545" s="1"/>
     </row>
-    <row r="546" spans="1:29" ht="13.2">
+    <row r="546" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -18109,7 +18102,7 @@
       <c r="AB546" s="1"/>
       <c r="AC546" s="1"/>
     </row>
-    <row r="547" spans="1:29" ht="13.2">
+    <row r="547" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -18140,7 +18133,7 @@
       <c r="AB547" s="1"/>
       <c r="AC547" s="1"/>
     </row>
-    <row r="548" spans="1:29" ht="13.2">
+    <row r="548" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -18171,7 +18164,7 @@
       <c r="AB548" s="1"/>
       <c r="AC548" s="1"/>
     </row>
-    <row r="549" spans="1:29" ht="13.2">
+    <row r="549" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -18202,7 +18195,7 @@
       <c r="AB549" s="1"/>
       <c r="AC549" s="1"/>
     </row>
-    <row r="550" spans="1:29" ht="13.2">
+    <row r="550" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -18233,7 +18226,7 @@
       <c r="AB550" s="1"/>
       <c r="AC550" s="1"/>
     </row>
-    <row r="551" spans="1:29" ht="13.2">
+    <row r="551" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -18264,7 +18257,7 @@
       <c r="AB551" s="1"/>
       <c r="AC551" s="1"/>
     </row>
-    <row r="552" spans="1:29" ht="13.2">
+    <row r="552" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -18295,7 +18288,7 @@
       <c r="AB552" s="1"/>
       <c r="AC552" s="1"/>
     </row>
-    <row r="553" spans="1:29" ht="13.2">
+    <row r="553" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -18326,7 +18319,7 @@
       <c r="AB553" s="1"/>
       <c r="AC553" s="1"/>
     </row>
-    <row r="554" spans="1:29" ht="13.2">
+    <row r="554" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -18357,7 +18350,7 @@
       <c r="AB554" s="1"/>
       <c r="AC554" s="1"/>
     </row>
-    <row r="555" spans="1:29" ht="13.2">
+    <row r="555" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -18388,7 +18381,7 @@
       <c r="AB555" s="1"/>
       <c r="AC555" s="1"/>
     </row>
-    <row r="556" spans="1:29" ht="13.2">
+    <row r="556" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -18419,7 +18412,7 @@
       <c r="AB556" s="1"/>
       <c r="AC556" s="1"/>
     </row>
-    <row r="557" spans="1:29" ht="13.2">
+    <row r="557" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -18450,7 +18443,7 @@
       <c r="AB557" s="1"/>
       <c r="AC557" s="1"/>
     </row>
-    <row r="558" spans="1:29" ht="13.2">
+    <row r="558" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -18481,7 +18474,7 @@
       <c r="AB558" s="1"/>
       <c r="AC558" s="1"/>
     </row>
-    <row r="559" spans="1:29" ht="13.2">
+    <row r="559" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -18512,7 +18505,7 @@
       <c r="AB559" s="1"/>
       <c r="AC559" s="1"/>
     </row>
-    <row r="560" spans="1:29" ht="13.2">
+    <row r="560" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -18543,7 +18536,7 @@
       <c r="AB560" s="1"/>
       <c r="AC560" s="1"/>
     </row>
-    <row r="561" spans="1:29" ht="13.2">
+    <row r="561" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -18574,7 +18567,7 @@
       <c r="AB561" s="1"/>
       <c r="AC561" s="1"/>
     </row>
-    <row r="562" spans="1:29" ht="13.2">
+    <row r="562" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -18605,7 +18598,7 @@
       <c r="AB562" s="1"/>
       <c r="AC562" s="1"/>
     </row>
-    <row r="563" spans="1:29" ht="13.2">
+    <row r="563" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -18636,7 +18629,7 @@
       <c r="AB563" s="1"/>
       <c r="AC563" s="1"/>
     </row>
-    <row r="564" spans="1:29" ht="13.2">
+    <row r="564" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -18667,7 +18660,7 @@
       <c r="AB564" s="1"/>
       <c r="AC564" s="1"/>
     </row>
-    <row r="565" spans="1:29" ht="13.2">
+    <row r="565" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -18698,7 +18691,7 @@
       <c r="AB565" s="1"/>
       <c r="AC565" s="1"/>
     </row>
-    <row r="566" spans="1:29" ht="13.2">
+    <row r="566" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -18729,7 +18722,7 @@
       <c r="AB566" s="1"/>
       <c r="AC566" s="1"/>
     </row>
-    <row r="567" spans="1:29" ht="13.2">
+    <row r="567" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18760,7 +18753,7 @@
       <c r="AB567" s="1"/>
       <c r="AC567" s="1"/>
     </row>
-    <row r="568" spans="1:29" ht="13.2">
+    <row r="568" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18791,7 +18784,7 @@
       <c r="AB568" s="1"/>
       <c r="AC568" s="1"/>
     </row>
-    <row r="569" spans="1:29" ht="13.2">
+    <row r="569" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18822,7 +18815,7 @@
       <c r="AB569" s="1"/>
       <c r="AC569" s="1"/>
     </row>
-    <row r="570" spans="1:29" ht="13.2">
+    <row r="570" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18853,7 +18846,7 @@
       <c r="AB570" s="1"/>
       <c r="AC570" s="1"/>
     </row>
-    <row r="571" spans="1:29" ht="13.2">
+    <row r="571" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18884,7 +18877,7 @@
       <c r="AB571" s="1"/>
       <c r="AC571" s="1"/>
     </row>
-    <row r="572" spans="1:29" ht="13.2">
+    <row r="572" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18915,7 +18908,7 @@
       <c r="AB572" s="1"/>
       <c r="AC572" s="1"/>
     </row>
-    <row r="573" spans="1:29" ht="13.2">
+    <row r="573" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18946,7 +18939,7 @@
       <c r="AB573" s="1"/>
       <c r="AC573" s="1"/>
     </row>
-    <row r="574" spans="1:29" ht="13.2">
+    <row r="574" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18977,7 +18970,7 @@
       <c r="AB574" s="1"/>
       <c r="AC574" s="1"/>
     </row>
-    <row r="575" spans="1:29" ht="13.2">
+    <row r="575" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -19008,7 +19001,7 @@
       <c r="AB575" s="1"/>
       <c r="AC575" s="1"/>
     </row>
-    <row r="576" spans="1:29" ht="13.2">
+    <row r="576" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -19039,7 +19032,7 @@
       <c r="AB576" s="1"/>
       <c r="AC576" s="1"/>
     </row>
-    <row r="577" spans="1:29" ht="13.2">
+    <row r="577" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -19070,7 +19063,7 @@
       <c r="AB577" s="1"/>
       <c r="AC577" s="1"/>
     </row>
-    <row r="578" spans="1:29" ht="13.2">
+    <row r="578" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -19101,7 +19094,7 @@
       <c r="AB578" s="1"/>
       <c r="AC578" s="1"/>
     </row>
-    <row r="579" spans="1:29" ht="13.2">
+    <row r="579" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -19132,7 +19125,7 @@
       <c r="AB579" s="1"/>
       <c r="AC579" s="1"/>
     </row>
-    <row r="580" spans="1:29" ht="13.2">
+    <row r="580" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -19163,7 +19156,7 @@
       <c r="AB580" s="1"/>
       <c r="AC580" s="1"/>
     </row>
-    <row r="581" spans="1:29" ht="13.2">
+    <row r="581" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -19194,7 +19187,7 @@
       <c r="AB581" s="1"/>
       <c r="AC581" s="1"/>
     </row>
-    <row r="582" spans="1:29" ht="13.2">
+    <row r="582" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -19225,7 +19218,7 @@
       <c r="AB582" s="1"/>
       <c r="AC582" s="1"/>
     </row>
-    <row r="583" spans="1:29" ht="13.2">
+    <row r="583" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -19256,7 +19249,7 @@
       <c r="AB583" s="1"/>
       <c r="AC583" s="1"/>
     </row>
-    <row r="584" spans="1:29" ht="13.2">
+    <row r="584" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -19287,7 +19280,7 @@
       <c r="AB584" s="1"/>
       <c r="AC584" s="1"/>
     </row>
-    <row r="585" spans="1:29" ht="13.2">
+    <row r="585" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -19318,7 +19311,7 @@
       <c r="AB585" s="1"/>
       <c r="AC585" s="1"/>
     </row>
-    <row r="586" spans="1:29" ht="13.2">
+    <row r="586" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -19349,7 +19342,7 @@
       <c r="AB586" s="1"/>
       <c r="AC586" s="1"/>
     </row>
-    <row r="587" spans="1:29" ht="13.2">
+    <row r="587" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -19380,7 +19373,7 @@
       <c r="AB587" s="1"/>
       <c r="AC587" s="1"/>
     </row>
-    <row r="588" spans="1:29" ht="13.2">
+    <row r="588" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -19411,7 +19404,7 @@
       <c r="AB588" s="1"/>
       <c r="AC588" s="1"/>
     </row>
-    <row r="589" spans="1:29" ht="13.2">
+    <row r="589" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -19442,7 +19435,7 @@
       <c r="AB589" s="1"/>
       <c r="AC589" s="1"/>
     </row>
-    <row r="590" spans="1:29" ht="13.2">
+    <row r="590" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -19473,7 +19466,7 @@
       <c r="AB590" s="1"/>
       <c r="AC590" s="1"/>
     </row>
-    <row r="591" spans="1:29" ht="13.2">
+    <row r="591" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -19504,7 +19497,7 @@
       <c r="AB591" s="1"/>
       <c r="AC591" s="1"/>
     </row>
-    <row r="592" spans="1:29" ht="13.2">
+    <row r="592" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -19535,7 +19528,7 @@
       <c r="AB592" s="1"/>
       <c r="AC592" s="1"/>
     </row>
-    <row r="593" spans="1:29" ht="13.2">
+    <row r="593" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -19566,7 +19559,7 @@
       <c r="AB593" s="1"/>
       <c r="AC593" s="1"/>
     </row>
-    <row r="594" spans="1:29" ht="13.2">
+    <row r="594" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -19597,7 +19590,7 @@
       <c r="AB594" s="1"/>
       <c r="AC594" s="1"/>
     </row>
-    <row r="595" spans="1:29" ht="13.2">
+    <row r="595" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -19628,7 +19621,7 @@
       <c r="AB595" s="1"/>
       <c r="AC595" s="1"/>
     </row>
-    <row r="596" spans="1:29" ht="13.2">
+    <row r="596" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -19659,7 +19652,7 @@
       <c r="AB596" s="1"/>
       <c r="AC596" s="1"/>
     </row>
-    <row r="597" spans="1:29" ht="13.2">
+    <row r="597" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -19690,7 +19683,7 @@
       <c r="AB597" s="1"/>
       <c r="AC597" s="1"/>
     </row>
-    <row r="598" spans="1:29" ht="13.2">
+    <row r="598" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -19721,7 +19714,7 @@
       <c r="AB598" s="1"/>
       <c r="AC598" s="1"/>
     </row>
-    <row r="599" spans="1:29" ht="13.2">
+    <row r="599" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -19752,7 +19745,7 @@
       <c r="AB599" s="1"/>
       <c r="AC599" s="1"/>
     </row>
-    <row r="600" spans="1:29" ht="13.2">
+    <row r="600" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -19783,7 +19776,7 @@
       <c r="AB600" s="1"/>
       <c r="AC600" s="1"/>
     </row>
-    <row r="601" spans="1:29" ht="13.2">
+    <row r="601" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -19814,7 +19807,7 @@
       <c r="AB601" s="1"/>
       <c r="AC601" s="1"/>
     </row>
-    <row r="602" spans="1:29" ht="13.2">
+    <row r="602" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -19845,7 +19838,7 @@
       <c r="AB602" s="1"/>
       <c r="AC602" s="1"/>
     </row>
-    <row r="603" spans="1:29" ht="13.2">
+    <row r="603" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19876,7 +19869,7 @@
       <c r="AB603" s="1"/>
       <c r="AC603" s="1"/>
     </row>
-    <row r="604" spans="1:29" ht="13.2">
+    <row r="604" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19907,7 +19900,7 @@
       <c r="AB604" s="1"/>
       <c r="AC604" s="1"/>
     </row>
-    <row r="605" spans="1:29" ht="13.2">
+    <row r="605" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19938,7 +19931,7 @@
       <c r="AB605" s="1"/>
       <c r="AC605" s="1"/>
     </row>
-    <row r="606" spans="1:29" ht="13.2">
+    <row r="606" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19969,7 +19962,7 @@
       <c r="AB606" s="1"/>
       <c r="AC606" s="1"/>
     </row>
-    <row r="607" spans="1:29" ht="13.2">
+    <row r="607" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -20000,7 +19993,7 @@
       <c r="AB607" s="1"/>
       <c r="AC607" s="1"/>
     </row>
-    <row r="608" spans="1:29" ht="13.2">
+    <row r="608" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -20031,7 +20024,7 @@
       <c r="AB608" s="1"/>
       <c r="AC608" s="1"/>
     </row>
-    <row r="609" spans="1:29" ht="13.2">
+    <row r="609" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -20062,7 +20055,7 @@
       <c r="AB609" s="1"/>
       <c r="AC609" s="1"/>
     </row>
-    <row r="610" spans="1:29" ht="13.2">
+    <row r="610" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -20093,7 +20086,7 @@
       <c r="AB610" s="1"/>
       <c r="AC610" s="1"/>
     </row>
-    <row r="611" spans="1:29" ht="13.2">
+    <row r="611" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -20124,7 +20117,7 @@
       <c r="AB611" s="1"/>
       <c r="AC611" s="1"/>
     </row>
-    <row r="612" spans="1:29" ht="13.2">
+    <row r="612" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -20155,7 +20148,7 @@
       <c r="AB612" s="1"/>
       <c r="AC612" s="1"/>
     </row>
-    <row r="613" spans="1:29" ht="13.2">
+    <row r="613" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -20186,7 +20179,7 @@
       <c r="AB613" s="1"/>
       <c r="AC613" s="1"/>
     </row>
-    <row r="614" spans="1:29" ht="13.2">
+    <row r="614" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -20217,7 +20210,7 @@
       <c r="AB614" s="1"/>
       <c r="AC614" s="1"/>
     </row>
-    <row r="615" spans="1:29" ht="13.2">
+    <row r="615" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -20248,7 +20241,7 @@
       <c r="AB615" s="1"/>
       <c r="AC615" s="1"/>
     </row>
-    <row r="616" spans="1:29" ht="13.2">
+    <row r="616" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -20279,7 +20272,7 @@
       <c r="AB616" s="1"/>
       <c r="AC616" s="1"/>
     </row>
-    <row r="617" spans="1:29" ht="13.2">
+    <row r="617" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -20310,7 +20303,7 @@
       <c r="AB617" s="1"/>
       <c r="AC617" s="1"/>
     </row>
-    <row r="618" spans="1:29" ht="13.2">
+    <row r="618" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -20341,7 +20334,7 @@
       <c r="AB618" s="1"/>
       <c r="AC618" s="1"/>
     </row>
-    <row r="619" spans="1:29" ht="13.2">
+    <row r="619" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -20372,7 +20365,7 @@
       <c r="AB619" s="1"/>
       <c r="AC619" s="1"/>
     </row>
-    <row r="620" spans="1:29" ht="13.2">
+    <row r="620" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -20403,7 +20396,7 @@
       <c r="AB620" s="1"/>
       <c r="AC620" s="1"/>
     </row>
-    <row r="621" spans="1:29" ht="13.2">
+    <row r="621" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -20434,7 +20427,7 @@
       <c r="AB621" s="1"/>
       <c r="AC621" s="1"/>
     </row>
-    <row r="622" spans="1:29" ht="13.2">
+    <row r="622" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -20465,7 +20458,7 @@
       <c r="AB622" s="1"/>
       <c r="AC622" s="1"/>
     </row>
-    <row r="623" spans="1:29" ht="13.2">
+    <row r="623" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -20496,7 +20489,7 @@
       <c r="AB623" s="1"/>
       <c r="AC623" s="1"/>
     </row>
-    <row r="624" spans="1:29" ht="13.2">
+    <row r="624" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -20527,7 +20520,7 @@
       <c r="AB624" s="1"/>
       <c r="AC624" s="1"/>
     </row>
-    <row r="625" spans="1:29" ht="13.2">
+    <row r="625" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -20558,7 +20551,7 @@
       <c r="AB625" s="1"/>
       <c r="AC625" s="1"/>
     </row>
-    <row r="626" spans="1:29" ht="13.2">
+    <row r="626" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -20589,7 +20582,7 @@
       <c r="AB626" s="1"/>
       <c r="AC626" s="1"/>
     </row>
-    <row r="627" spans="1:29" ht="13.2">
+    <row r="627" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -20620,7 +20613,7 @@
       <c r="AB627" s="1"/>
       <c r="AC627" s="1"/>
     </row>
-    <row r="628" spans="1:29" ht="13.2">
+    <row r="628" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -20651,7 +20644,7 @@
       <c r="AB628" s="1"/>
       <c r="AC628" s="1"/>
     </row>
-    <row r="629" spans="1:29" ht="13.2">
+    <row r="629" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -20682,7 +20675,7 @@
       <c r="AB629" s="1"/>
       <c r="AC629" s="1"/>
     </row>
-    <row r="630" spans="1:29" ht="13.2">
+    <row r="630" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -20713,7 +20706,7 @@
       <c r="AB630" s="1"/>
       <c r="AC630" s="1"/>
     </row>
-    <row r="631" spans="1:29" ht="13.2">
+    <row r="631" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -20744,7 +20737,7 @@
       <c r="AB631" s="1"/>
       <c r="AC631" s="1"/>
     </row>
-    <row r="632" spans="1:29" ht="13.2">
+    <row r="632" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -20775,7 +20768,7 @@
       <c r="AB632" s="1"/>
       <c r="AC632" s="1"/>
     </row>
-    <row r="633" spans="1:29" ht="13.2">
+    <row r="633" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -20806,7 +20799,7 @@
       <c r="AB633" s="1"/>
       <c r="AC633" s="1"/>
     </row>
-    <row r="634" spans="1:29" ht="13.2">
+    <row r="634" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -20837,7 +20830,7 @@
       <c r="AB634" s="1"/>
       <c r="AC634" s="1"/>
     </row>
-    <row r="635" spans="1:29" ht="13.2">
+    <row r="635" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -20868,7 +20861,7 @@
       <c r="AB635" s="1"/>
       <c r="AC635" s="1"/>
     </row>
-    <row r="636" spans="1:29" ht="13.2">
+    <row r="636" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -20899,7 +20892,7 @@
       <c r="AB636" s="1"/>
       <c r="AC636" s="1"/>
     </row>
-    <row r="637" spans="1:29" ht="13.2">
+    <row r="637" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -20930,7 +20923,7 @@
       <c r="AB637" s="1"/>
       <c r="AC637" s="1"/>
     </row>
-    <row r="638" spans="1:29" ht="13.2">
+    <row r="638" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -20961,7 +20954,7 @@
       <c r="AB638" s="1"/>
       <c r="AC638" s="1"/>
     </row>
-    <row r="639" spans="1:29" ht="13.2">
+    <row r="639" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20992,7 +20985,7 @@
       <c r="AB639" s="1"/>
       <c r="AC639" s="1"/>
     </row>
-    <row r="640" spans="1:29" ht="13.2">
+    <row r="640" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -21023,7 +21016,7 @@
       <c r="AB640" s="1"/>
       <c r="AC640" s="1"/>
     </row>
-    <row r="641" spans="1:29" ht="13.2">
+    <row r="641" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -21054,7 +21047,7 @@
       <c r="AB641" s="1"/>
       <c r="AC641" s="1"/>
     </row>
-    <row r="642" spans="1:29" ht="13.2">
+    <row r="642" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -21085,7 +21078,7 @@
       <c r="AB642" s="1"/>
       <c r="AC642" s="1"/>
     </row>
-    <row r="643" spans="1:29" ht="13.2">
+    <row r="643" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -21116,7 +21109,7 @@
       <c r="AB643" s="1"/>
       <c r="AC643" s="1"/>
     </row>
-    <row r="644" spans="1:29" ht="13.2">
+    <row r="644" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -21147,7 +21140,7 @@
       <c r="AB644" s="1"/>
       <c r="AC644" s="1"/>
     </row>
-    <row r="645" spans="1:29" ht="13.2">
+    <row r="645" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -21178,7 +21171,7 @@
       <c r="AB645" s="1"/>
       <c r="AC645" s="1"/>
     </row>
-    <row r="646" spans="1:29" ht="13.2">
+    <row r="646" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -21209,7 +21202,7 @@
       <c r="AB646" s="1"/>
       <c r="AC646" s="1"/>
     </row>
-    <row r="647" spans="1:29" ht="13.2">
+    <row r="647" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -21240,7 +21233,7 @@
       <c r="AB647" s="1"/>
       <c r="AC647" s="1"/>
     </row>
-    <row r="648" spans="1:29" ht="13.2">
+    <row r="648" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -21271,7 +21264,7 @@
       <c r="AB648" s="1"/>
       <c r="AC648" s="1"/>
     </row>
-    <row r="649" spans="1:29" ht="13.2">
+    <row r="649" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -21302,7 +21295,7 @@
       <c r="AB649" s="1"/>
       <c r="AC649" s="1"/>
     </row>
-    <row r="650" spans="1:29" ht="13.2">
+    <row r="650" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -21333,7 +21326,7 @@
       <c r="AB650" s="1"/>
       <c r="AC650" s="1"/>
     </row>
-    <row r="651" spans="1:29" ht="13.2">
+    <row r="651" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -21364,7 +21357,7 @@
       <c r="AB651" s="1"/>
       <c r="AC651" s="1"/>
     </row>
-    <row r="652" spans="1:29" ht="13.2">
+    <row r="652" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -21395,7 +21388,7 @@
       <c r="AB652" s="1"/>
       <c r="AC652" s="1"/>
     </row>
-    <row r="653" spans="1:29" ht="13.2">
+    <row r="653" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -21426,7 +21419,7 @@
       <c r="AB653" s="1"/>
       <c r="AC653" s="1"/>
     </row>
-    <row r="654" spans="1:29" ht="13.2">
+    <row r="654" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -21457,7 +21450,7 @@
       <c r="AB654" s="1"/>
       <c r="AC654" s="1"/>
     </row>
-    <row r="655" spans="1:29" ht="13.2">
+    <row r="655" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -21488,7 +21481,7 @@
       <c r="AB655" s="1"/>
       <c r="AC655" s="1"/>
     </row>
-    <row r="656" spans="1:29" ht="13.2">
+    <row r="656" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -21519,7 +21512,7 @@
       <c r="AB656" s="1"/>
       <c r="AC656" s="1"/>
     </row>
-    <row r="657" spans="1:29" ht="13.2">
+    <row r="657" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -21550,7 +21543,7 @@
       <c r="AB657" s="1"/>
       <c r="AC657" s="1"/>
     </row>
-    <row r="658" spans="1:29" ht="13.2">
+    <row r="658" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -21581,7 +21574,7 @@
       <c r="AB658" s="1"/>
       <c r="AC658" s="1"/>
     </row>
-    <row r="659" spans="1:29" ht="13.2">
+    <row r="659" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -21612,7 +21605,7 @@
       <c r="AB659" s="1"/>
       <c r="AC659" s="1"/>
     </row>
-    <row r="660" spans="1:29" ht="13.2">
+    <row r="660" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -21643,7 +21636,7 @@
       <c r="AB660" s="1"/>
       <c r="AC660" s="1"/>
     </row>
-    <row r="661" spans="1:29" ht="13.2">
+    <row r="661" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -21674,7 +21667,7 @@
       <c r="AB661" s="1"/>
       <c r="AC661" s="1"/>
     </row>
-    <row r="662" spans="1:29" ht="13.2">
+    <row r="662" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -21705,7 +21698,7 @@
       <c r="AB662" s="1"/>
       <c r="AC662" s="1"/>
     </row>
-    <row r="663" spans="1:29" ht="13.2">
+    <row r="663" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -21736,7 +21729,7 @@
       <c r="AB663" s="1"/>
       <c r="AC663" s="1"/>
     </row>
-    <row r="664" spans="1:29" ht="13.2">
+    <row r="664" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -21767,7 +21760,7 @@
       <c r="AB664" s="1"/>
       <c r="AC664" s="1"/>
     </row>
-    <row r="665" spans="1:29" ht="13.2">
+    <row r="665" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -21798,7 +21791,7 @@
       <c r="AB665" s="1"/>
       <c r="AC665" s="1"/>
     </row>
-    <row r="666" spans="1:29" ht="13.2">
+    <row r="666" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -21829,7 +21822,7 @@
       <c r="AB666" s="1"/>
       <c r="AC666" s="1"/>
     </row>
-    <row r="667" spans="1:29" ht="13.2">
+    <row r="667" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -21860,7 +21853,7 @@
       <c r="AB667" s="1"/>
       <c r="AC667" s="1"/>
     </row>
-    <row r="668" spans="1:29" ht="13.2">
+    <row r="668" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -21891,7 +21884,7 @@
       <c r="AB668" s="1"/>
       <c r="AC668" s="1"/>
     </row>
-    <row r="669" spans="1:29" ht="13.2">
+    <row r="669" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -21922,7 +21915,7 @@
       <c r="AB669" s="1"/>
       <c r="AC669" s="1"/>
     </row>
-    <row r="670" spans="1:29" ht="13.2">
+    <row r="670" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -21953,7 +21946,7 @@
       <c r="AB670" s="1"/>
       <c r="AC670" s="1"/>
     </row>
-    <row r="671" spans="1:29" ht="13.2">
+    <row r="671" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -21984,7 +21977,7 @@
       <c r="AB671" s="1"/>
       <c r="AC671" s="1"/>
     </row>
-    <row r="672" spans="1:29" ht="13.2">
+    <row r="672" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -22015,7 +22008,7 @@
       <c r="AB672" s="1"/>
       <c r="AC672" s="1"/>
     </row>
-    <row r="673" spans="1:29" ht="13.2">
+    <row r="673" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -22046,7 +22039,7 @@
       <c r="AB673" s="1"/>
       <c r="AC673" s="1"/>
     </row>
-    <row r="674" spans="1:29" ht="13.2">
+    <row r="674" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -22077,7 +22070,7 @@
       <c r="AB674" s="1"/>
       <c r="AC674" s="1"/>
     </row>
-    <row r="675" spans="1:29" ht="13.2">
+    <row r="675" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -22108,7 +22101,7 @@
       <c r="AB675" s="1"/>
       <c r="AC675" s="1"/>
     </row>
-    <row r="676" spans="1:29" ht="13.2">
+    <row r="676" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -22139,7 +22132,7 @@
       <c r="AB676" s="1"/>
       <c r="AC676" s="1"/>
     </row>
-    <row r="677" spans="1:29" ht="13.2">
+    <row r="677" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -22170,7 +22163,7 @@
       <c r="AB677" s="1"/>
       <c r="AC677" s="1"/>
     </row>
-    <row r="678" spans="1:29" ht="13.2">
+    <row r="678" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -22201,7 +22194,7 @@
       <c r="AB678" s="1"/>
       <c r="AC678" s="1"/>
     </row>
-    <row r="679" spans="1:29" ht="13.2">
+    <row r="679" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -22232,7 +22225,7 @@
       <c r="AB679" s="1"/>
       <c r="AC679" s="1"/>
     </row>
-    <row r="680" spans="1:29" ht="13.2">
+    <row r="680" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -22263,7 +22256,7 @@
       <c r="AB680" s="1"/>
       <c r="AC680" s="1"/>
     </row>
-    <row r="681" spans="1:29" ht="13.2">
+    <row r="681" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -22294,7 +22287,7 @@
       <c r="AB681" s="1"/>
       <c r="AC681" s="1"/>
     </row>
-    <row r="682" spans="1:29" ht="13.2">
+    <row r="682" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -22325,7 +22318,7 @@
       <c r="AB682" s="1"/>
       <c r="AC682" s="1"/>
     </row>
-    <row r="683" spans="1:29" ht="13.2">
+    <row r="683" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -22356,7 +22349,7 @@
       <c r="AB683" s="1"/>
       <c r="AC683" s="1"/>
     </row>
-    <row r="684" spans="1:29" ht="13.2">
+    <row r="684" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -22387,7 +22380,7 @@
       <c r="AB684" s="1"/>
       <c r="AC684" s="1"/>
     </row>
-    <row r="685" spans="1:29" ht="13.2">
+    <row r="685" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -22418,7 +22411,7 @@
       <c r="AB685" s="1"/>
       <c r="AC685" s="1"/>
     </row>
-    <row r="686" spans="1:29" ht="13.2">
+    <row r="686" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -22449,7 +22442,7 @@
       <c r="AB686" s="1"/>
       <c r="AC686" s="1"/>
     </row>
-    <row r="687" spans="1:29" ht="13.2">
+    <row r="687" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -22480,7 +22473,7 @@
       <c r="AB687" s="1"/>
       <c r="AC687" s="1"/>
     </row>
-    <row r="688" spans="1:29" ht="13.2">
+    <row r="688" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -22511,7 +22504,7 @@
       <c r="AB688" s="1"/>
       <c r="AC688" s="1"/>
     </row>
-    <row r="689" spans="1:29" ht="13.2">
+    <row r="689" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -22542,7 +22535,7 @@
       <c r="AB689" s="1"/>
       <c r="AC689" s="1"/>
     </row>
-    <row r="690" spans="1:29" ht="13.2">
+    <row r="690" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -22573,7 +22566,7 @@
       <c r="AB690" s="1"/>
       <c r="AC690" s="1"/>
     </row>
-    <row r="691" spans="1:29" ht="13.2">
+    <row r="691" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -22604,7 +22597,7 @@
       <c r="AB691" s="1"/>
       <c r="AC691" s="1"/>
     </row>
-    <row r="692" spans="1:29" ht="13.2">
+    <row r="692" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -22635,7 +22628,7 @@
       <c r="AB692" s="1"/>
       <c r="AC692" s="1"/>
     </row>
-    <row r="693" spans="1:29" ht="13.2">
+    <row r="693" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -22666,7 +22659,7 @@
       <c r="AB693" s="1"/>
       <c r="AC693" s="1"/>
     </row>
-    <row r="694" spans="1:29" ht="13.2">
+    <row r="694" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -22697,7 +22690,7 @@
       <c r="AB694" s="1"/>
       <c r="AC694" s="1"/>
     </row>
-    <row r="695" spans="1:29" ht="13.2">
+    <row r="695" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -22728,7 +22721,7 @@
       <c r="AB695" s="1"/>
       <c r="AC695" s="1"/>
     </row>
-    <row r="696" spans="1:29" ht="13.2">
+    <row r="696" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -22759,7 +22752,7 @@
       <c r="AB696" s="1"/>
       <c r="AC696" s="1"/>
     </row>
-    <row r="697" spans="1:29" ht="13.2">
+    <row r="697" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -22790,7 +22783,7 @@
       <c r="AB697" s="1"/>
       <c r="AC697" s="1"/>
     </row>
-    <row r="698" spans="1:29" ht="13.2">
+    <row r="698" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -22821,7 +22814,7 @@
       <c r="AB698" s="1"/>
       <c r="AC698" s="1"/>
     </row>
-    <row r="699" spans="1:29" ht="13.2">
+    <row r="699" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -22852,7 +22845,7 @@
       <c r="AB699" s="1"/>
       <c r="AC699" s="1"/>
     </row>
-    <row r="700" spans="1:29" ht="13.2">
+    <row r="700" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -22883,7 +22876,7 @@
       <c r="AB700" s="1"/>
       <c r="AC700" s="1"/>
     </row>
-    <row r="701" spans="1:29" ht="13.2">
+    <row r="701" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -22914,7 +22907,7 @@
       <c r="AB701" s="1"/>
       <c r="AC701" s="1"/>
     </row>
-    <row r="702" spans="1:29" ht="13.2">
+    <row r="702" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -22945,7 +22938,7 @@
       <c r="AB702" s="1"/>
       <c r="AC702" s="1"/>
     </row>
-    <row r="703" spans="1:29" ht="13.2">
+    <row r="703" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -22976,7 +22969,7 @@
       <c r="AB703" s="1"/>
       <c r="AC703" s="1"/>
     </row>
-    <row r="704" spans="1:29" ht="13.2">
+    <row r="704" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -23007,7 +23000,7 @@
       <c r="AB704" s="1"/>
       <c r="AC704" s="1"/>
     </row>
-    <row r="705" spans="1:29" ht="13.2">
+    <row r="705" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -23038,7 +23031,7 @@
       <c r="AB705" s="1"/>
       <c r="AC705" s="1"/>
     </row>
-    <row r="706" spans="1:29" ht="13.2">
+    <row r="706" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -23069,7 +23062,7 @@
       <c r="AB706" s="1"/>
       <c r="AC706" s="1"/>
     </row>
-    <row r="707" spans="1:29" ht="13.2">
+    <row r="707" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -23100,7 +23093,7 @@
       <c r="AB707" s="1"/>
       <c r="AC707" s="1"/>
     </row>
-    <row r="708" spans="1:29" ht="13.2">
+    <row r="708" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -23131,7 +23124,7 @@
       <c r="AB708" s="1"/>
       <c r="AC708" s="1"/>
     </row>
-    <row r="709" spans="1:29" ht="13.2">
+    <row r="709" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -23162,7 +23155,7 @@
       <c r="AB709" s="1"/>
       <c r="AC709" s="1"/>
     </row>
-    <row r="710" spans="1:29" ht="13.2">
+    <row r="710" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -23193,7 +23186,7 @@
       <c r="AB710" s="1"/>
       <c r="AC710" s="1"/>
     </row>
-    <row r="711" spans="1:29" ht="13.2">
+    <row r="711" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -23224,7 +23217,7 @@
       <c r="AB711" s="1"/>
       <c r="AC711" s="1"/>
     </row>
-    <row r="712" spans="1:29" ht="13.2">
+    <row r="712" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -23255,7 +23248,7 @@
       <c r="AB712" s="1"/>
       <c r="AC712" s="1"/>
     </row>
-    <row r="713" spans="1:29" ht="13.2">
+    <row r="713" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -23286,7 +23279,7 @@
       <c r="AB713" s="1"/>
       <c r="AC713" s="1"/>
     </row>
-    <row r="714" spans="1:29" ht="13.2">
+    <row r="714" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -23317,7 +23310,7 @@
       <c r="AB714" s="1"/>
       <c r="AC714" s="1"/>
     </row>
-    <row r="715" spans="1:29" ht="13.2">
+    <row r="715" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -23348,7 +23341,7 @@
       <c r="AB715" s="1"/>
       <c r="AC715" s="1"/>
     </row>
-    <row r="716" spans="1:29" ht="13.2">
+    <row r="716" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -23379,7 +23372,7 @@
       <c r="AB716" s="1"/>
       <c r="AC716" s="1"/>
     </row>
-    <row r="717" spans="1:29" ht="13.2">
+    <row r="717" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -23410,7 +23403,7 @@
       <c r="AB717" s="1"/>
       <c r="AC717" s="1"/>
     </row>
-    <row r="718" spans="1:29" ht="13.2">
+    <row r="718" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -23441,7 +23434,7 @@
       <c r="AB718" s="1"/>
       <c r="AC718" s="1"/>
     </row>
-    <row r="719" spans="1:29" ht="13.2">
+    <row r="719" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -23472,7 +23465,7 @@
       <c r="AB719" s="1"/>
       <c r="AC719" s="1"/>
     </row>
-    <row r="720" spans="1:29" ht="13.2">
+    <row r="720" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -23503,7 +23496,7 @@
       <c r="AB720" s="1"/>
       <c r="AC720" s="1"/>
     </row>
-    <row r="721" spans="1:29" ht="13.2">
+    <row r="721" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -23534,7 +23527,7 @@
       <c r="AB721" s="1"/>
       <c r="AC721" s="1"/>
     </row>
-    <row r="722" spans="1:29" ht="13.2">
+    <row r="722" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -23565,7 +23558,7 @@
       <c r="AB722" s="1"/>
       <c r="AC722" s="1"/>
     </row>
-    <row r="723" spans="1:29" ht="13.2">
+    <row r="723" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -23596,7 +23589,7 @@
       <c r="AB723" s="1"/>
       <c r="AC723" s="1"/>
     </row>
-    <row r="724" spans="1:29" ht="13.2">
+    <row r="724" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -23627,7 +23620,7 @@
       <c r="AB724" s="1"/>
       <c r="AC724" s="1"/>
     </row>
-    <row r="725" spans="1:29" ht="13.2">
+    <row r="725" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -23658,7 +23651,7 @@
       <c r="AB725" s="1"/>
       <c r="AC725" s="1"/>
     </row>
-    <row r="726" spans="1:29" ht="13.2">
+    <row r="726" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -23689,7 +23682,7 @@
       <c r="AB726" s="1"/>
       <c r="AC726" s="1"/>
     </row>
-    <row r="727" spans="1:29" ht="13.2">
+    <row r="727" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -23720,7 +23713,7 @@
       <c r="AB727" s="1"/>
       <c r="AC727" s="1"/>
     </row>
-    <row r="728" spans="1:29" ht="13.2">
+    <row r="728" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -23751,7 +23744,7 @@
       <c r="AB728" s="1"/>
       <c r="AC728" s="1"/>
     </row>
-    <row r="729" spans="1:29" ht="13.2">
+    <row r="729" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -23782,7 +23775,7 @@
       <c r="AB729" s="1"/>
       <c r="AC729" s="1"/>
     </row>
-    <row r="730" spans="1:29" ht="13.2">
+    <row r="730" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -23813,7 +23806,7 @@
       <c r="AB730" s="1"/>
       <c r="AC730" s="1"/>
     </row>
-    <row r="731" spans="1:29" ht="13.2">
+    <row r="731" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -23844,7 +23837,7 @@
       <c r="AB731" s="1"/>
       <c r="AC731" s="1"/>
     </row>
-    <row r="732" spans="1:29" ht="13.2">
+    <row r="732" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -23875,7 +23868,7 @@
       <c r="AB732" s="1"/>
       <c r="AC732" s="1"/>
     </row>
-    <row r="733" spans="1:29" ht="13.2">
+    <row r="733" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -23906,7 +23899,7 @@
       <c r="AB733" s="1"/>
       <c r="AC733" s="1"/>
     </row>
-    <row r="734" spans="1:29" ht="13.2">
+    <row r="734" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -23937,7 +23930,7 @@
       <c r="AB734" s="1"/>
       <c r="AC734" s="1"/>
     </row>
-    <row r="735" spans="1:29" ht="13.2">
+    <row r="735" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -23968,7 +23961,7 @@
       <c r="AB735" s="1"/>
       <c r="AC735" s="1"/>
     </row>
-    <row r="736" spans="1:29" ht="13.2">
+    <row r="736" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -23999,7 +23992,7 @@
       <c r="AB736" s="1"/>
       <c r="AC736" s="1"/>
     </row>
-    <row r="737" spans="1:29" ht="13.2">
+    <row r="737" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -24030,7 +24023,7 @@
       <c r="AB737" s="1"/>
       <c r="AC737" s="1"/>
     </row>
-    <row r="738" spans="1:29" ht="13.2">
+    <row r="738" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -24061,7 +24054,7 @@
       <c r="AB738" s="1"/>
       <c r="AC738" s="1"/>
     </row>
-    <row r="739" spans="1:29" ht="13.2">
+    <row r="739" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -24092,7 +24085,7 @@
       <c r="AB739" s="1"/>
       <c r="AC739" s="1"/>
     </row>
-    <row r="740" spans="1:29" ht="13.2">
+    <row r="740" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -24123,7 +24116,7 @@
       <c r="AB740" s="1"/>
       <c r="AC740" s="1"/>
     </row>
-    <row r="741" spans="1:29" ht="13.2">
+    <row r="741" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -24154,7 +24147,7 @@
       <c r="AB741" s="1"/>
       <c r="AC741" s="1"/>
     </row>
-    <row r="742" spans="1:29" ht="13.2">
+    <row r="742" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -24185,7 +24178,7 @@
       <c r="AB742" s="1"/>
       <c r="AC742" s="1"/>
     </row>
-    <row r="743" spans="1:29" ht="13.2">
+    <row r="743" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -24216,7 +24209,7 @@
       <c r="AB743" s="1"/>
       <c r="AC743" s="1"/>
     </row>
-    <row r="744" spans="1:29" ht="13.2">
+    <row r="744" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -24247,7 +24240,7 @@
       <c r="AB744" s="1"/>
       <c r="AC744" s="1"/>
     </row>
-    <row r="745" spans="1:29" ht="13.2">
+    <row r="745" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -24278,7 +24271,7 @@
       <c r="AB745" s="1"/>
       <c r="AC745" s="1"/>
     </row>
-    <row r="746" spans="1:29" ht="13.2">
+    <row r="746" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -24309,7 +24302,7 @@
       <c r="AB746" s="1"/>
       <c r="AC746" s="1"/>
     </row>
-    <row r="747" spans="1:29" ht="13.2">
+    <row r="747" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -24340,7 +24333,7 @@
       <c r="AB747" s="1"/>
       <c r="AC747" s="1"/>
     </row>
-    <row r="748" spans="1:29" ht="13.2">
+    <row r="748" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -24371,7 +24364,7 @@
       <c r="AB748" s="1"/>
       <c r="AC748" s="1"/>
     </row>
-    <row r="749" spans="1:29" ht="13.2">
+    <row r="749" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -24402,7 +24395,7 @@
       <c r="AB749" s="1"/>
       <c r="AC749" s="1"/>
     </row>
-    <row r="750" spans="1:29" ht="13.2">
+    <row r="750" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -24433,7 +24426,7 @@
       <c r="AB750" s="1"/>
       <c r="AC750" s="1"/>
     </row>
-    <row r="751" spans="1:29" ht="13.2">
+    <row r="751" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -24464,7 +24457,7 @@
       <c r="AB751" s="1"/>
       <c r="AC751" s="1"/>
     </row>
-    <row r="752" spans="1:29" ht="13.2">
+    <row r="752" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -24495,7 +24488,7 @@
       <c r="AB752" s="1"/>
       <c r="AC752" s="1"/>
     </row>
-    <row r="753" spans="1:29" ht="13.2">
+    <row r="753" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -24526,7 +24519,7 @@
       <c r="AB753" s="1"/>
       <c r="AC753" s="1"/>
     </row>
-    <row r="754" spans="1:29" ht="13.2">
+    <row r="754" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -24557,7 +24550,7 @@
       <c r="AB754" s="1"/>
       <c r="AC754" s="1"/>
     </row>
-    <row r="755" spans="1:29" ht="13.2">
+    <row r="755" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -24588,7 +24581,7 @@
       <c r="AB755" s="1"/>
       <c r="AC755" s="1"/>
     </row>
-    <row r="756" spans="1:29" ht="13.2">
+    <row r="756" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -24619,7 +24612,7 @@
       <c r="AB756" s="1"/>
       <c r="AC756" s="1"/>
     </row>
-    <row r="757" spans="1:29" ht="13.2">
+    <row r="757" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -24650,7 +24643,7 @@
       <c r="AB757" s="1"/>
       <c r="AC757" s="1"/>
     </row>
-    <row r="758" spans="1:29" ht="13.2">
+    <row r="758" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -24681,7 +24674,7 @@
       <c r="AB758" s="1"/>
       <c r="AC758" s="1"/>
     </row>
-    <row r="759" spans="1:29" ht="13.2">
+    <row r="759" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -24712,7 +24705,7 @@
       <c r="AB759" s="1"/>
       <c r="AC759" s="1"/>
     </row>
-    <row r="760" spans="1:29" ht="13.2">
+    <row r="760" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -24743,7 +24736,7 @@
       <c r="AB760" s="1"/>
       <c r="AC760" s="1"/>
     </row>
-    <row r="761" spans="1:29" ht="13.2">
+    <row r="761" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -24774,7 +24767,7 @@
       <c r="AB761" s="1"/>
       <c r="AC761" s="1"/>
     </row>
-    <row r="762" spans="1:29" ht="13.2">
+    <row r="762" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -24805,7 +24798,7 @@
       <c r="AB762" s="1"/>
       <c r="AC762" s="1"/>
     </row>
-    <row r="763" spans="1:29" ht="13.2">
+    <row r="763" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -24836,7 +24829,7 @@
       <c r="AB763" s="1"/>
       <c r="AC763" s="1"/>
     </row>
-    <row r="764" spans="1:29" ht="13.2">
+    <row r="764" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -24867,7 +24860,7 @@
       <c r="AB764" s="1"/>
       <c r="AC764" s="1"/>
     </row>
-    <row r="765" spans="1:29" ht="13.2">
+    <row r="765" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -24898,7 +24891,7 @@
       <c r="AB765" s="1"/>
       <c r="AC765" s="1"/>
     </row>
-    <row r="766" spans="1:29" ht="13.2">
+    <row r="766" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -24929,7 +24922,7 @@
       <c r="AB766" s="1"/>
       <c r="AC766" s="1"/>
     </row>
-    <row r="767" spans="1:29" ht="13.2">
+    <row r="767" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -24960,7 +24953,7 @@
       <c r="AB767" s="1"/>
       <c r="AC767" s="1"/>
     </row>
-    <row r="768" spans="1:29" ht="13.2">
+    <row r="768" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -24991,7 +24984,7 @@
       <c r="AB768" s="1"/>
       <c r="AC768" s="1"/>
     </row>
-    <row r="769" spans="1:29" ht="13.2">
+    <row r="769" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -25022,7 +25015,7 @@
       <c r="AB769" s="1"/>
       <c r="AC769" s="1"/>
     </row>
-    <row r="770" spans="1:29" ht="13.2">
+    <row r="770" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -25053,7 +25046,7 @@
       <c r="AB770" s="1"/>
       <c r="AC770" s="1"/>
     </row>
-    <row r="771" spans="1:29" ht="13.2">
+    <row r="771" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -25084,7 +25077,7 @@
       <c r="AB771" s="1"/>
       <c r="AC771" s="1"/>
     </row>
-    <row r="772" spans="1:29" ht="13.2">
+    <row r="772" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -25115,7 +25108,7 @@
       <c r="AB772" s="1"/>
       <c r="AC772" s="1"/>
     </row>
-    <row r="773" spans="1:29" ht="13.2">
+    <row r="773" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -25146,7 +25139,7 @@
       <c r="AB773" s="1"/>
       <c r="AC773" s="1"/>
     </row>
-    <row r="774" spans="1:29" ht="13.2">
+    <row r="774" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -25177,7 +25170,7 @@
       <c r="AB774" s="1"/>
       <c r="AC774" s="1"/>
     </row>
-    <row r="775" spans="1:29" ht="13.2">
+    <row r="775" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -25208,7 +25201,7 @@
       <c r="AB775" s="1"/>
       <c r="AC775" s="1"/>
     </row>
-    <row r="776" spans="1:29" ht="13.2">
+    <row r="776" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -25239,7 +25232,7 @@
       <c r="AB776" s="1"/>
       <c r="AC776" s="1"/>
     </row>
-    <row r="777" spans="1:29" ht="13.2">
+    <row r="777" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -25270,7 +25263,7 @@
       <c r="AB777" s="1"/>
       <c r="AC777" s="1"/>
     </row>
-    <row r="778" spans="1:29" ht="13.2">
+    <row r="778" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -25301,7 +25294,7 @@
       <c r="AB778" s="1"/>
       <c r="AC778" s="1"/>
     </row>
-    <row r="779" spans="1:29" ht="13.2">
+    <row r="779" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -25332,7 +25325,7 @@
       <c r="AB779" s="1"/>
       <c r="AC779" s="1"/>
     </row>
-    <row r="780" spans="1:29" ht="13.2">
+    <row r="780" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -25363,7 +25356,7 @@
       <c r="AB780" s="1"/>
       <c r="AC780" s="1"/>
     </row>
-    <row r="781" spans="1:29" ht="13.2">
+    <row r="781" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -25394,7 +25387,7 @@
       <c r="AB781" s="1"/>
       <c r="AC781" s="1"/>
     </row>
-    <row r="782" spans="1:29" ht="13.2">
+    <row r="782" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -25425,7 +25418,7 @@
       <c r="AB782" s="1"/>
       <c r="AC782" s="1"/>
     </row>
-    <row r="783" spans="1:29" ht="13.2">
+    <row r="783" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -25456,7 +25449,7 @@
       <c r="AB783" s="1"/>
       <c r="AC783" s="1"/>
     </row>
-    <row r="784" spans="1:29" ht="13.2">
+    <row r="784" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -25487,7 +25480,7 @@
       <c r="AB784" s="1"/>
       <c r="AC784" s="1"/>
     </row>
-    <row r="785" spans="1:29" ht="13.2">
+    <row r="785" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -25518,7 +25511,7 @@
       <c r="AB785" s="1"/>
       <c r="AC785" s="1"/>
     </row>
-    <row r="786" spans="1:29" ht="13.2">
+    <row r="786" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -25549,7 +25542,7 @@
       <c r="AB786" s="1"/>
       <c r="AC786" s="1"/>
     </row>
-    <row r="787" spans="1:29" ht="13.2">
+    <row r="787" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -25580,7 +25573,7 @@
       <c r="AB787" s="1"/>
       <c r="AC787" s="1"/>
     </row>
-    <row r="788" spans="1:29" ht="13.2">
+    <row r="788" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -25611,7 +25604,7 @@
       <c r="AB788" s="1"/>
       <c r="AC788" s="1"/>
     </row>
-    <row r="789" spans="1:29" ht="13.2">
+    <row r="789" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -25642,7 +25635,7 @@
       <c r="AB789" s="1"/>
       <c r="AC789" s="1"/>
     </row>
-    <row r="790" spans="1:29" ht="13.2">
+    <row r="790" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -25673,7 +25666,7 @@
       <c r="AB790" s="1"/>
       <c r="AC790" s="1"/>
     </row>
-    <row r="791" spans="1:29" ht="13.2">
+    <row r="791" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -25704,7 +25697,7 @@
       <c r="AB791" s="1"/>
       <c r="AC791" s="1"/>
     </row>
-    <row r="792" spans="1:29" ht="13.2">
+    <row r="792" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -25735,7 +25728,7 @@
       <c r="AB792" s="1"/>
       <c r="AC792" s="1"/>
     </row>
-    <row r="793" spans="1:29" ht="13.2">
+    <row r="793" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -25766,7 +25759,7 @@
       <c r="AB793" s="1"/>
       <c r="AC793" s="1"/>
     </row>
-    <row r="794" spans="1:29" ht="13.2">
+    <row r="794" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -25797,7 +25790,7 @@
       <c r="AB794" s="1"/>
       <c r="AC794" s="1"/>
     </row>
-    <row r="795" spans="1:29" ht="13.2">
+    <row r="795" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -25828,7 +25821,7 @@
       <c r="AB795" s="1"/>
       <c r="AC795" s="1"/>
     </row>
-    <row r="796" spans="1:29" ht="13.2">
+    <row r="796" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -25859,7 +25852,7 @@
       <c r="AB796" s="1"/>
       <c r="AC796" s="1"/>
     </row>
-    <row r="797" spans="1:29" ht="13.2">
+    <row r="797" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -25890,7 +25883,7 @@
       <c r="AB797" s="1"/>
       <c r="AC797" s="1"/>
     </row>
-    <row r="798" spans="1:29" ht="13.2">
+    <row r="798" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -25921,7 +25914,7 @@
       <c r="AB798" s="1"/>
       <c r="AC798" s="1"/>
     </row>
-    <row r="799" spans="1:29" ht="13.2">
+    <row r="799" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -25952,7 +25945,7 @@
       <c r="AB799" s="1"/>
       <c r="AC799" s="1"/>
     </row>
-    <row r="800" spans="1:29" ht="13.2">
+    <row r="800" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -25983,7 +25976,7 @@
       <c r="AB800" s="1"/>
       <c r="AC800" s="1"/>
     </row>
-    <row r="801" spans="1:29" ht="13.2">
+    <row r="801" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -26014,7 +26007,7 @@
       <c r="AB801" s="1"/>
       <c r="AC801" s="1"/>
     </row>
-    <row r="802" spans="1:29" ht="13.2">
+    <row r="802" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -26045,7 +26038,7 @@
       <c r="AB802" s="1"/>
       <c r="AC802" s="1"/>
     </row>
-    <row r="803" spans="1:29" ht="13.2">
+    <row r="803" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -26076,7 +26069,7 @@
       <c r="AB803" s="1"/>
       <c r="AC803" s="1"/>
     </row>
-    <row r="804" spans="1:29" ht="13.2">
+    <row r="804" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -26107,7 +26100,7 @@
       <c r="AB804" s="1"/>
       <c r="AC804" s="1"/>
     </row>
-    <row r="805" spans="1:29" ht="13.2">
+    <row r="805" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -26138,7 +26131,7 @@
       <c r="AB805" s="1"/>
       <c r="AC805" s="1"/>
     </row>
-    <row r="806" spans="1:29" ht="13.2">
+    <row r="806" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -26169,7 +26162,7 @@
       <c r="AB806" s="1"/>
       <c r="AC806" s="1"/>
     </row>
-    <row r="807" spans="1:29" ht="13.2">
+    <row r="807" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -26200,7 +26193,7 @@
       <c r="AB807" s="1"/>
       <c r="AC807" s="1"/>
     </row>
-    <row r="808" spans="1:29" ht="13.2">
+    <row r="808" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -26231,7 +26224,7 @@
       <c r="AB808" s="1"/>
       <c r="AC808" s="1"/>
     </row>
-    <row r="809" spans="1:29" ht="13.2">
+    <row r="809" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -26262,7 +26255,7 @@
       <c r="AB809" s="1"/>
       <c r="AC809" s="1"/>
     </row>
-    <row r="810" spans="1:29" ht="13.2">
+    <row r="810" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -26293,7 +26286,7 @@
       <c r="AB810" s="1"/>
       <c r="AC810" s="1"/>
     </row>
-    <row r="811" spans="1:29" ht="13.2">
+    <row r="811" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -26324,7 +26317,7 @@
       <c r="AB811" s="1"/>
       <c r="AC811" s="1"/>
     </row>
-    <row r="812" spans="1:29" ht="13.2">
+    <row r="812" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -26355,7 +26348,7 @@
       <c r="AB812" s="1"/>
       <c r="AC812" s="1"/>
     </row>
-    <row r="813" spans="1:29" ht="13.2">
+    <row r="813" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -26386,7 +26379,7 @@
       <c r="AB813" s="1"/>
       <c r="AC813" s="1"/>
     </row>
-    <row r="814" spans="1:29" ht="13.2">
+    <row r="814" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -26417,7 +26410,7 @@
       <c r="AB814" s="1"/>
       <c r="AC814" s="1"/>
     </row>
-    <row r="815" spans="1:29" ht="13.2">
+    <row r="815" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -26448,7 +26441,7 @@
       <c r="AB815" s="1"/>
       <c r="AC815" s="1"/>
     </row>
-    <row r="816" spans="1:29" ht="13.2">
+    <row r="816" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -26479,7 +26472,7 @@
       <c r="AB816" s="1"/>
       <c r="AC816" s="1"/>
     </row>
-    <row r="817" spans="1:29" ht="13.2">
+    <row r="817" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -26510,7 +26503,7 @@
       <c r="AB817" s="1"/>
       <c r="AC817" s="1"/>
     </row>
-    <row r="818" spans="1:29" ht="13.2">
+    <row r="818" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -26541,7 +26534,7 @@
       <c r="AB818" s="1"/>
       <c r="AC818" s="1"/>
     </row>
-    <row r="819" spans="1:29" ht="13.2">
+    <row r="819" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -26572,7 +26565,7 @@
       <c r="AB819" s="1"/>
       <c r="AC819" s="1"/>
     </row>
-    <row r="820" spans="1:29" ht="13.2">
+    <row r="820" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -26603,7 +26596,7 @@
       <c r="AB820" s="1"/>
       <c r="AC820" s="1"/>
     </row>
-    <row r="821" spans="1:29" ht="13.2">
+    <row r="821" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -26634,7 +26627,7 @@
       <c r="AB821" s="1"/>
       <c r="AC821" s="1"/>
     </row>
-    <row r="822" spans="1:29" ht="13.2">
+    <row r="822" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -26665,7 +26658,7 @@
       <c r="AB822" s="1"/>
       <c r="AC822" s="1"/>
     </row>
-    <row r="823" spans="1:29" ht="13.2">
+    <row r="823" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -26696,7 +26689,7 @@
       <c r="AB823" s="1"/>
       <c r="AC823" s="1"/>
     </row>
-    <row r="824" spans="1:29" ht="13.2">
+    <row r="824" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -26727,7 +26720,7 @@
       <c r="AB824" s="1"/>
       <c r="AC824" s="1"/>
     </row>
-    <row r="825" spans="1:29" ht="13.2">
+    <row r="825" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -26758,7 +26751,7 @@
       <c r="AB825" s="1"/>
       <c r="AC825" s="1"/>
     </row>
-    <row r="826" spans="1:29" ht="13.2">
+    <row r="826" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -26789,7 +26782,7 @@
       <c r="AB826" s="1"/>
       <c r="AC826" s="1"/>
     </row>
-    <row r="827" spans="1:29" ht="13.2">
+    <row r="827" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -26820,7 +26813,7 @@
       <c r="AB827" s="1"/>
       <c r="AC827" s="1"/>
     </row>
-    <row r="828" spans="1:29" ht="13.2">
+    <row r="828" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -26851,7 +26844,7 @@
       <c r="AB828" s="1"/>
       <c r="AC828" s="1"/>
     </row>
-    <row r="829" spans="1:29" ht="13.2">
+    <row r="829" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -26882,7 +26875,7 @@
       <c r="AB829" s="1"/>
       <c r="AC829" s="1"/>
     </row>
-    <row r="830" spans="1:29" ht="13.2">
+    <row r="830" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -26913,7 +26906,7 @@
       <c r="AB830" s="1"/>
       <c r="AC830" s="1"/>
     </row>
-    <row r="831" spans="1:29" ht="13.2">
+    <row r="831" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -26944,7 +26937,7 @@
       <c r="AB831" s="1"/>
       <c r="AC831" s="1"/>
     </row>
-    <row r="832" spans="1:29" ht="13.2">
+    <row r="832" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -26975,7 +26968,7 @@
       <c r="AB832" s="1"/>
       <c r="AC832" s="1"/>
     </row>
-    <row r="833" spans="1:29" ht="13.2">
+    <row r="833" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -27006,7 +26999,7 @@
       <c r="AB833" s="1"/>
       <c r="AC833" s="1"/>
     </row>
-    <row r="834" spans="1:29" ht="13.2">
+    <row r="834" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -27037,7 +27030,7 @@
       <c r="AB834" s="1"/>
       <c r="AC834" s="1"/>
     </row>
-    <row r="835" spans="1:29" ht="13.2">
+    <row r="835" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -27068,7 +27061,7 @@
       <c r="AB835" s="1"/>
       <c r="AC835" s="1"/>
     </row>
-    <row r="836" spans="1:29" ht="13.2">
+    <row r="836" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -27099,7 +27092,7 @@
       <c r="AB836" s="1"/>
       <c r="AC836" s="1"/>
     </row>
-    <row r="837" spans="1:29" ht="13.2">
+    <row r="837" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -27130,7 +27123,7 @@
       <c r="AB837" s="1"/>
       <c r="AC837" s="1"/>
     </row>
-    <row r="838" spans="1:29" ht="13.2">
+    <row r="838" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -27161,7 +27154,7 @@
       <c r="AB838" s="1"/>
       <c r="AC838" s="1"/>
     </row>
-    <row r="839" spans="1:29" ht="13.2">
+    <row r="839" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -27192,7 +27185,7 @@
       <c r="AB839" s="1"/>
       <c r="AC839" s="1"/>
     </row>
-    <row r="840" spans="1:29" ht="13.2">
+    <row r="840" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -27223,7 +27216,7 @@
       <c r="AB840" s="1"/>
       <c r="AC840" s="1"/>
     </row>
-    <row r="841" spans="1:29" ht="13.2">
+    <row r="841" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -27254,7 +27247,7 @@
       <c r="AB841" s="1"/>
       <c r="AC841" s="1"/>
     </row>
-    <row r="842" spans="1:29" ht="13.2">
+    <row r="842" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -27285,7 +27278,7 @@
       <c r="AB842" s="1"/>
       <c r="AC842" s="1"/>
     </row>
-    <row r="843" spans="1:29" ht="13.2">
+    <row r="843" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -27316,7 +27309,7 @@
       <c r="AB843" s="1"/>
       <c r="AC843" s="1"/>
     </row>
-    <row r="844" spans="1:29" ht="13.2">
+    <row r="844" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -27347,7 +27340,7 @@
       <c r="AB844" s="1"/>
       <c r="AC844" s="1"/>
     </row>
-    <row r="845" spans="1:29" ht="13.2">
+    <row r="845" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -27378,7 +27371,7 @@
       <c r="AB845" s="1"/>
       <c r="AC845" s="1"/>
     </row>
-    <row r="846" spans="1:29" ht="13.2">
+    <row r="846" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -27409,7 +27402,7 @@
       <c r="AB846" s="1"/>
       <c r="AC846" s="1"/>
     </row>
-    <row r="847" spans="1:29" ht="13.2">
+    <row r="847" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -27440,7 +27433,7 @@
       <c r="AB847" s="1"/>
       <c r="AC847" s="1"/>
     </row>
-    <row r="848" spans="1:29" ht="13.2">
+    <row r="848" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -27471,7 +27464,7 @@
       <c r="AB848" s="1"/>
       <c r="AC848" s="1"/>
     </row>
-    <row r="849" spans="1:29" ht="13.2">
+    <row r="849" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -27502,7 +27495,7 @@
       <c r="AB849" s="1"/>
       <c r="AC849" s="1"/>
     </row>
-    <row r="850" spans="1:29" ht="13.2">
+    <row r="850" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -27533,7 +27526,7 @@
       <c r="AB850" s="1"/>
       <c r="AC850" s="1"/>
     </row>
-    <row r="851" spans="1:29" ht="13.2">
+    <row r="851" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -27564,7 +27557,7 @@
       <c r="AB851" s="1"/>
       <c r="AC851" s="1"/>
     </row>
-    <row r="852" spans="1:29" ht="13.2">
+    <row r="852" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -27595,7 +27588,7 @@
       <c r="AB852" s="1"/>
       <c r="AC852" s="1"/>
     </row>
-    <row r="853" spans="1:29" ht="13.2">
+    <row r="853" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -27626,7 +27619,7 @@
       <c r="AB853" s="1"/>
       <c r="AC853" s="1"/>
     </row>
-    <row r="854" spans="1:29" ht="13.2">
+    <row r="854" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -27657,7 +27650,7 @@
       <c r="AB854" s="1"/>
       <c r="AC854" s="1"/>
     </row>
-    <row r="855" spans="1:29" ht="13.2">
+    <row r="855" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -27688,7 +27681,7 @@
       <c r="AB855" s="1"/>
       <c r="AC855" s="1"/>
     </row>
-    <row r="856" spans="1:29" ht="13.2">
+    <row r="856" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -27719,7 +27712,7 @@
       <c r="AB856" s="1"/>
       <c r="AC856" s="1"/>
     </row>
-    <row r="857" spans="1:29" ht="13.2">
+    <row r="857" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -27750,7 +27743,7 @@
       <c r="AB857" s="1"/>
       <c r="AC857" s="1"/>
     </row>
-    <row r="858" spans="1:29" ht="13.2">
+    <row r="858" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -27781,7 +27774,7 @@
       <c r="AB858" s="1"/>
       <c r="AC858" s="1"/>
     </row>
-    <row r="859" spans="1:29" ht="13.2">
+    <row r="859" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -27812,7 +27805,7 @@
       <c r="AB859" s="1"/>
       <c r="AC859" s="1"/>
     </row>
-    <row r="860" spans="1:29" ht="13.2">
+    <row r="860" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -27843,7 +27836,7 @@
       <c r="AB860" s="1"/>
       <c r="AC860" s="1"/>
     </row>
-    <row r="861" spans="1:29" ht="13.2">
+    <row r="861" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -27874,7 +27867,7 @@
       <c r="AB861" s="1"/>
       <c r="AC861" s="1"/>
     </row>
-    <row r="862" spans="1:29" ht="13.2">
+    <row r="862" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -27905,7 +27898,7 @@
       <c r="AB862" s="1"/>
       <c r="AC862" s="1"/>
     </row>
-    <row r="863" spans="1:29" ht="13.2">
+    <row r="863" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -27936,7 +27929,7 @@
       <c r="AB863" s="1"/>
       <c r="AC863" s="1"/>
     </row>
-    <row r="864" spans="1:29" ht="13.2">
+    <row r="864" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -27967,7 +27960,7 @@
       <c r="AB864" s="1"/>
       <c r="AC864" s="1"/>
     </row>
-    <row r="865" spans="1:29" ht="13.2">
+    <row r="865" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -27998,7 +27991,7 @@
       <c r="AB865" s="1"/>
       <c r="AC865" s="1"/>
     </row>
-    <row r="866" spans="1:29" ht="13.2">
+    <row r="866" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -28029,7 +28022,7 @@
       <c r="AB866" s="1"/>
       <c r="AC866" s="1"/>
     </row>
-    <row r="867" spans="1:29" ht="13.2">
+    <row r="867" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -28060,7 +28053,7 @@
       <c r="AB867" s="1"/>
       <c r="AC867" s="1"/>
     </row>
-    <row r="868" spans="1:29" ht="13.2">
+    <row r="868" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -28091,7 +28084,7 @@
       <c r="AB868" s="1"/>
       <c r="AC868" s="1"/>
     </row>
-    <row r="869" spans="1:29" ht="13.2">
+    <row r="869" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -28122,7 +28115,7 @@
       <c r="AB869" s="1"/>
       <c r="AC869" s="1"/>
     </row>
-    <row r="870" spans="1:29" ht="13.2">
+    <row r="870" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -28153,7 +28146,7 @@
       <c r="AB870" s="1"/>
       <c r="AC870" s="1"/>
     </row>
-    <row r="871" spans="1:29" ht="13.2">
+    <row r="871" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -28184,7 +28177,7 @@
       <c r="AB871" s="1"/>
       <c r="AC871" s="1"/>
     </row>
-    <row r="872" spans="1:29" ht="13.2">
+    <row r="872" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -28215,7 +28208,7 @@
       <c r="AB872" s="1"/>
       <c r="AC872" s="1"/>
     </row>
-    <row r="873" spans="1:29" ht="13.2">
+    <row r="873" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -28246,7 +28239,7 @@
       <c r="AB873" s="1"/>
       <c r="AC873" s="1"/>
     </row>
-    <row r="874" spans="1:29" ht="13.2">
+    <row r="874" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -28277,7 +28270,7 @@
       <c r="AB874" s="1"/>
       <c r="AC874" s="1"/>
     </row>
-    <row r="875" spans="1:29" ht="13.2">
+    <row r="875" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -28308,7 +28301,7 @@
       <c r="AB875" s="1"/>
       <c r="AC875" s="1"/>
     </row>
-    <row r="876" spans="1:29" ht="13.2">
+    <row r="876" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -28339,7 +28332,7 @@
       <c r="AB876" s="1"/>
       <c r="AC876" s="1"/>
     </row>
-    <row r="877" spans="1:29" ht="13.2">
+    <row r="877" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -28370,7 +28363,7 @@
       <c r="AB877" s="1"/>
       <c r="AC877" s="1"/>
     </row>
-    <row r="878" spans="1:29" ht="13.2">
+    <row r="878" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -28401,7 +28394,7 @@
       <c r="AB878" s="1"/>
       <c r="AC878" s="1"/>
     </row>
-    <row r="879" spans="1:29" ht="13.2">
+    <row r="879" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -28432,7 +28425,7 @@
       <c r="AB879" s="1"/>
       <c r="AC879" s="1"/>
     </row>
-    <row r="880" spans="1:29" ht="13.2">
+    <row r="880" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -28463,7 +28456,7 @@
       <c r="AB880" s="1"/>
       <c r="AC880" s="1"/>
     </row>
-    <row r="881" spans="1:29" ht="13.2">
+    <row r="881" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -28494,7 +28487,7 @@
       <c r="AB881" s="1"/>
       <c r="AC881" s="1"/>
     </row>
-    <row r="882" spans="1:29" ht="13.2">
+    <row r="882" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -28525,7 +28518,7 @@
       <c r="AB882" s="1"/>
       <c r="AC882" s="1"/>
     </row>
-    <row r="883" spans="1:29" ht="13.2">
+    <row r="883" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -28556,7 +28549,7 @@
       <c r="AB883" s="1"/>
       <c r="AC883" s="1"/>
     </row>
-    <row r="884" spans="1:29" ht="13.2">
+    <row r="884" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -28587,7 +28580,7 @@
       <c r="AB884" s="1"/>
       <c r="AC884" s="1"/>
     </row>
-    <row r="885" spans="1:29" ht="13.2">
+    <row r="885" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -28618,7 +28611,7 @@
       <c r="AB885" s="1"/>
       <c r="AC885" s="1"/>
     </row>
-    <row r="886" spans="1:29" ht="13.2">
+    <row r="886" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -28649,7 +28642,7 @@
       <c r="AB886" s="1"/>
       <c r="AC886" s="1"/>
     </row>
-    <row r="887" spans="1:29" ht="13.2">
+    <row r="887" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -28680,7 +28673,7 @@
       <c r="AB887" s="1"/>
       <c r="AC887" s="1"/>
     </row>
-    <row r="888" spans="1:29" ht="13.2">
+    <row r="888" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -28711,7 +28704,7 @@
       <c r="AB888" s="1"/>
       <c r="AC888" s="1"/>
     </row>
-    <row r="889" spans="1:29" ht="13.2">
+    <row r="889" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -28742,7 +28735,7 @@
       <c r="AB889" s="1"/>
       <c r="AC889" s="1"/>
     </row>
-    <row r="890" spans="1:29" ht="13.2">
+    <row r="890" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -28773,7 +28766,7 @@
       <c r="AB890" s="1"/>
       <c r="AC890" s="1"/>
     </row>
-    <row r="891" spans="1:29" ht="13.2">
+    <row r="891" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -28804,7 +28797,7 @@
       <c r="AB891" s="1"/>
       <c r="AC891" s="1"/>
     </row>
-    <row r="892" spans="1:29" ht="13.2">
+    <row r="892" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -28835,7 +28828,7 @@
       <c r="AB892" s="1"/>
       <c r="AC892" s="1"/>
     </row>
-    <row r="893" spans="1:29" ht="13.2">
+    <row r="893" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -28866,7 +28859,7 @@
       <c r="AB893" s="1"/>
       <c r="AC893" s="1"/>
     </row>
-    <row r="894" spans="1:29" ht="13.2">
+    <row r="894" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -28897,7 +28890,7 @@
       <c r="AB894" s="1"/>
       <c r="AC894" s="1"/>
     </row>
-    <row r="895" spans="1:29" ht="13.2">
+    <row r="895" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -28928,7 +28921,7 @@
       <c r="AB895" s="1"/>
       <c r="AC895" s="1"/>
     </row>
-    <row r="896" spans="1:29" ht="13.2">
+    <row r="896" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -28959,7 +28952,7 @@
       <c r="AB896" s="1"/>
       <c r="AC896" s="1"/>
     </row>
-    <row r="897" spans="1:29" ht="13.2">
+    <row r="897" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -28990,7 +28983,7 @@
       <c r="AB897" s="1"/>
       <c r="AC897" s="1"/>
     </row>
-    <row r="898" spans="1:29" ht="13.2">
+    <row r="898" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -29021,7 +29014,7 @@
       <c r="AB898" s="1"/>
       <c r="AC898" s="1"/>
     </row>
-    <row r="899" spans="1:29" ht="13.2">
+    <row r="899" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -29052,7 +29045,7 @@
       <c r="AB899" s="1"/>
       <c r="AC899" s="1"/>
     </row>
-    <row r="900" spans="1:29" ht="13.2">
+    <row r="900" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -29083,7 +29076,7 @@
       <c r="AB900" s="1"/>
       <c r="AC900" s="1"/>
     </row>
-    <row r="901" spans="1:29" ht="13.2">
+    <row r="901" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -29114,7 +29107,7 @@
       <c r="AB901" s="1"/>
       <c r="AC901" s="1"/>
     </row>
-    <row r="902" spans="1:29" ht="13.2">
+    <row r="902" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -29145,7 +29138,7 @@
       <c r="AB902" s="1"/>
       <c r="AC902" s="1"/>
     </row>
-    <row r="903" spans="1:29" ht="13.2">
+    <row r="903" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -29176,7 +29169,7 @@
       <c r="AB903" s="1"/>
       <c r="AC903" s="1"/>
     </row>
-    <row r="904" spans="1:29" ht="13.2">
+    <row r="904" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -29207,7 +29200,7 @@
       <c r="AB904" s="1"/>
       <c r="AC904" s="1"/>
     </row>
-    <row r="905" spans="1:29" ht="13.2">
+    <row r="905" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -29238,7 +29231,7 @@
       <c r="AB905" s="1"/>
       <c r="AC905" s="1"/>
     </row>
-    <row r="906" spans="1:29" ht="13.2">
+    <row r="906" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -29269,7 +29262,7 @@
       <c r="AB906" s="1"/>
       <c r="AC906" s="1"/>
     </row>
-    <row r="907" spans="1:29" ht="13.2">
+    <row r="907" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -29300,7 +29293,7 @@
       <c r="AB907" s="1"/>
       <c r="AC907" s="1"/>
     </row>
-    <row r="908" spans="1:29" ht="13.2">
+    <row r="908" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -29331,7 +29324,7 @@
       <c r="AB908" s="1"/>
       <c r="AC908" s="1"/>
     </row>
-    <row r="909" spans="1:29" ht="13.2">
+    <row r="909" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -29362,7 +29355,7 @@
       <c r="AB909" s="1"/>
       <c r="AC909" s="1"/>
     </row>
-    <row r="910" spans="1:29" ht="13.2">
+    <row r="910" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -29393,7 +29386,7 @@
       <c r="AB910" s="1"/>
       <c r="AC910" s="1"/>
     </row>
-    <row r="911" spans="1:29" ht="13.2">
+    <row r="911" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -29424,7 +29417,7 @@
       <c r="AB911" s="1"/>
       <c r="AC911" s="1"/>
     </row>
-    <row r="912" spans="1:29" ht="13.2">
+    <row r="912" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -29455,7 +29448,7 @@
       <c r="AB912" s="1"/>
       <c r="AC912" s="1"/>
     </row>
-    <row r="913" spans="1:29" ht="13.2">
+    <row r="913" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -29486,7 +29479,7 @@
       <c r="AB913" s="1"/>
       <c r="AC913" s="1"/>
     </row>
-    <row r="914" spans="1:29" ht="13.2">
+    <row r="914" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -29517,7 +29510,7 @@
       <c r="AB914" s="1"/>
       <c r="AC914" s="1"/>
     </row>
-    <row r="915" spans="1:29" ht="13.2">
+    <row r="915" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -29548,7 +29541,7 @@
       <c r="AB915" s="1"/>
       <c r="AC915" s="1"/>
     </row>
-    <row r="916" spans="1:29" ht="13.2">
+    <row r="916" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -29579,7 +29572,7 @@
       <c r="AB916" s="1"/>
       <c r="AC916" s="1"/>
     </row>
-    <row r="917" spans="1:29" ht="13.2">
+    <row r="917" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -29610,7 +29603,7 @@
       <c r="AB917" s="1"/>
       <c r="AC917" s="1"/>
     </row>
-    <row r="918" spans="1:29" ht="13.2">
+    <row r="918" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -29641,7 +29634,7 @@
       <c r="AB918" s="1"/>
       <c r="AC918" s="1"/>
     </row>
-    <row r="919" spans="1:29" ht="13.2">
+    <row r="919" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -29672,7 +29665,7 @@
       <c r="AB919" s="1"/>
       <c r="AC919" s="1"/>
     </row>
-    <row r="920" spans="1:29" ht="13.2">
+    <row r="920" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -29703,7 +29696,7 @@
       <c r="AB920" s="1"/>
       <c r="AC920" s="1"/>
     </row>
-    <row r="921" spans="1:29" ht="13.2">
+    <row r="921" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -29734,7 +29727,7 @@
       <c r="AB921" s="1"/>
       <c r="AC921" s="1"/>
     </row>
-    <row r="922" spans="1:29" ht="13.2">
+    <row r="922" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -29765,7 +29758,7 @@
       <c r="AB922" s="1"/>
       <c r="AC922" s="1"/>
     </row>
-    <row r="923" spans="1:29" ht="13.2">
+    <row r="923" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -29796,7 +29789,7 @@
       <c r="AB923" s="1"/>
       <c r="AC923" s="1"/>
     </row>
-    <row r="924" spans="1:29" ht="13.2">
+    <row r="924" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -29827,7 +29820,7 @@
       <c r="AB924" s="1"/>
       <c r="AC924" s="1"/>
     </row>
-    <row r="925" spans="1:29" ht="13.2">
+    <row r="925" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -29858,7 +29851,7 @@
       <c r="AB925" s="1"/>
       <c r="AC925" s="1"/>
     </row>
-    <row r="926" spans="1:29" ht="13.2">
+    <row r="926" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -29889,7 +29882,7 @@
       <c r="AB926" s="1"/>
       <c r="AC926" s="1"/>
     </row>
-    <row r="927" spans="1:29" ht="13.2">
+    <row r="927" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -29920,7 +29913,7 @@
       <c r="AB927" s="1"/>
       <c r="AC927" s="1"/>
     </row>
-    <row r="928" spans="1:29" ht="13.2">
+    <row r="928" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -29951,7 +29944,7 @@
       <c r="AB928" s="1"/>
       <c r="AC928" s="1"/>
     </row>
-    <row r="929" spans="1:29" ht="13.2">
+    <row r="929" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -29982,7 +29975,7 @@
       <c r="AB929" s="1"/>
       <c r="AC929" s="1"/>
     </row>
-    <row r="930" spans="1:29" ht="13.2">
+    <row r="930" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -30013,7 +30006,7 @@
       <c r="AB930" s="1"/>
       <c r="AC930" s="1"/>
     </row>
-    <row r="931" spans="1:29" ht="13.2">
+    <row r="931" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -30044,7 +30037,7 @@
       <c r="AB931" s="1"/>
       <c r="AC931" s="1"/>
     </row>
-    <row r="932" spans="1:29" ht="13.2">
+    <row r="932" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -30075,7 +30068,7 @@
       <c r="AB932" s="1"/>
       <c r="AC932" s="1"/>
     </row>
-    <row r="933" spans="1:29" ht="13.2">
+    <row r="933" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -30106,7 +30099,7 @@
       <c r="AB933" s="1"/>
       <c r="AC933" s="1"/>
     </row>
-    <row r="934" spans="1:29" ht="13.2">
+    <row r="934" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -30137,7 +30130,7 @@
       <c r="AB934" s="1"/>
       <c r="AC934" s="1"/>
     </row>
-    <row r="935" spans="1:29" ht="13.2">
+    <row r="935" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -30168,7 +30161,7 @@
       <c r="AB935" s="1"/>
       <c r="AC935" s="1"/>
     </row>
-    <row r="936" spans="1:29" ht="13.2">
+    <row r="936" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -30199,7 +30192,7 @@
       <c r="AB936" s="1"/>
       <c r="AC936" s="1"/>
     </row>
-    <row r="937" spans="1:29" ht="13.2">
+    <row r="937" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -30230,7 +30223,7 @@
       <c r="AB937" s="1"/>
       <c r="AC937" s="1"/>
     </row>
-    <row r="938" spans="1:29" ht="13.2">
+    <row r="938" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -30261,7 +30254,7 @@
       <c r="AB938" s="1"/>
       <c r="AC938" s="1"/>
     </row>
-    <row r="939" spans="1:29" ht="13.2">
+    <row r="939" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -30292,7 +30285,7 @@
       <c r="AB939" s="1"/>
       <c r="AC939" s="1"/>
     </row>
-    <row r="940" spans="1:29" ht="13.2">
+    <row r="940" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -30323,7 +30316,7 @@
       <c r="AB940" s="1"/>
       <c r="AC940" s="1"/>
     </row>
-    <row r="941" spans="1:29" ht="13.2">
+    <row r="941" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -30354,7 +30347,7 @@
       <c r="AB941" s="1"/>
       <c r="AC941" s="1"/>
     </row>
-    <row r="942" spans="1:29" ht="13.2">
+    <row r="942" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -30385,7 +30378,7 @@
       <c r="AB942" s="1"/>
       <c r="AC942" s="1"/>
     </row>
-    <row r="943" spans="1:29" ht="13.2">
+    <row r="943" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -30416,7 +30409,7 @@
       <c r="AB943" s="1"/>
       <c r="AC943" s="1"/>
     </row>
-    <row r="944" spans="1:29" ht="13.2">
+    <row r="944" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -30447,7 +30440,7 @@
       <c r="AB944" s="1"/>
       <c r="AC944" s="1"/>
     </row>
-    <row r="945" spans="1:29" ht="13.2">
+    <row r="945" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -30478,7 +30471,7 @@
       <c r="AB945" s="1"/>
       <c r="AC945" s="1"/>
     </row>
-    <row r="946" spans="1:29" ht="13.2">
+    <row r="946" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -30509,7 +30502,7 @@
       <c r="AB946" s="1"/>
       <c r="AC946" s="1"/>
     </row>
-    <row r="947" spans="1:29" ht="13.2">
+    <row r="947" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -30540,7 +30533,7 @@
       <c r="AB947" s="1"/>
       <c r="AC947" s="1"/>
     </row>
-    <row r="948" spans="1:29" ht="13.2">
+    <row r="948" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -30571,7 +30564,7 @@
       <c r="AB948" s="1"/>
       <c r="AC948" s="1"/>
     </row>
-    <row r="949" spans="1:29" ht="13.2">
+    <row r="949" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -30602,7 +30595,7 @@
       <c r="AB949" s="1"/>
       <c r="AC949" s="1"/>
     </row>
-    <row r="950" spans="1:29" ht="13.2">
+    <row r="950" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -30633,7 +30626,7 @@
       <c r="AB950" s="1"/>
       <c r="AC950" s="1"/>
     </row>
-    <row r="951" spans="1:29" ht="13.2">
+    <row r="951" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -30664,7 +30657,7 @@
       <c r="AB951" s="1"/>
       <c r="AC951" s="1"/>
     </row>
-    <row r="952" spans="1:29" ht="13.2">
+    <row r="952" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -30695,7 +30688,7 @@
       <c r="AB952" s="1"/>
       <c r="AC952" s="1"/>
     </row>
-    <row r="953" spans="1:29" ht="13.2">
+    <row r="953" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -30726,7 +30719,7 @@
       <c r="AB953" s="1"/>
       <c r="AC953" s="1"/>
     </row>
-    <row r="954" spans="1:29" ht="13.2">
+    <row r="954" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -30757,7 +30750,7 @@
       <c r="AB954" s="1"/>
       <c r="AC954" s="1"/>
     </row>
-    <row r="955" spans="1:29" ht="13.2">
+    <row r="955" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -30788,7 +30781,7 @@
       <c r="AB955" s="1"/>
       <c r="AC955" s="1"/>
     </row>
-    <row r="956" spans="1:29" ht="13.2">
+    <row r="956" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -30819,7 +30812,7 @@
       <c r="AB956" s="1"/>
       <c r="AC956" s="1"/>
     </row>
-    <row r="957" spans="1:29" ht="13.2">
+    <row r="957" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -30850,7 +30843,7 @@
       <c r="AB957" s="1"/>
       <c r="AC957" s="1"/>
     </row>
-    <row r="958" spans="1:29" ht="13.2">
+    <row r="958" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -30881,7 +30874,7 @@
       <c r="AB958" s="1"/>
       <c r="AC958" s="1"/>
     </row>
-    <row r="959" spans="1:29" ht="13.2">
+    <row r="959" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -30912,7 +30905,7 @@
       <c r="AB959" s="1"/>
       <c r="AC959" s="1"/>
     </row>
-    <row r="960" spans="1:29" ht="13.2">
+    <row r="960" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -30943,7 +30936,7 @@
       <c r="AB960" s="1"/>
       <c r="AC960" s="1"/>
     </row>
-    <row r="961" spans="1:29" ht="13.2">
+    <row r="961" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -30974,7 +30967,7 @@
       <c r="AB961" s="1"/>
       <c r="AC961" s="1"/>
     </row>
-    <row r="962" spans="1:29" ht="13.2">
+    <row r="962" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -31005,7 +30998,7 @@
       <c r="AB962" s="1"/>
       <c r="AC962" s="1"/>
     </row>
-    <row r="963" spans="1:29" ht="13.2">
+    <row r="963" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -31036,7 +31029,7 @@
       <c r="AB963" s="1"/>
       <c r="AC963" s="1"/>
     </row>
-    <row r="964" spans="1:29" ht="13.2">
+    <row r="964" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -31067,7 +31060,7 @@
       <c r="AB964" s="1"/>
       <c r="AC964" s="1"/>
     </row>
-    <row r="965" spans="1:29" ht="13.2">
+    <row r="965" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -31098,7 +31091,7 @@
       <c r="AB965" s="1"/>
       <c r="AC965" s="1"/>
     </row>
-    <row r="966" spans="1:29" ht="13.2">
+    <row r="966" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -31129,7 +31122,7 @@
       <c r="AB966" s="1"/>
       <c r="AC966" s="1"/>
     </row>
-    <row r="967" spans="1:29" ht="13.2">
+    <row r="967" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -31160,7 +31153,7 @@
       <c r="AB967" s="1"/>
       <c r="AC967" s="1"/>
     </row>
-    <row r="968" spans="1:29" ht="13.2">
+    <row r="968" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -31191,7 +31184,7 @@
       <c r="AB968" s="1"/>
       <c r="AC968" s="1"/>
     </row>
-    <row r="969" spans="1:29" ht="13.2">
+    <row r="969" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -31222,7 +31215,7 @@
       <c r="AB969" s="1"/>
       <c r="AC969" s="1"/>
     </row>
-    <row r="970" spans="1:29" ht="13.2">
+    <row r="970" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -31253,7 +31246,7 @@
       <c r="AB970" s="1"/>
       <c r="AC970" s="1"/>
     </row>
-    <row r="971" spans="1:29" ht="13.2">
+    <row r="971" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -31284,7 +31277,7 @@
       <c r="AB971" s="1"/>
       <c r="AC971" s="1"/>
     </row>
-    <row r="972" spans="1:29" ht="13.2">
+    <row r="972" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -31315,7 +31308,7 @@
       <c r="AB972" s="1"/>
       <c r="AC972" s="1"/>
     </row>
-    <row r="973" spans="1:29" ht="13.2">
+    <row r="973" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -31346,7 +31339,7 @@
       <c r="AB973" s="1"/>
       <c r="AC973" s="1"/>
     </row>
-    <row r="974" spans="1:29" ht="13.2">
+    <row r="974" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -31377,7 +31370,7 @@
       <c r="AB974" s="1"/>
       <c r="AC974" s="1"/>
     </row>
-    <row r="975" spans="1:29" ht="13.2">
+    <row r="975" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -31408,7 +31401,7 @@
       <c r="AB975" s="1"/>
       <c r="AC975" s="1"/>
     </row>
-    <row r="976" spans="1:29" ht="13.2">
+    <row r="976" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -31439,7 +31432,7 @@
       <c r="AB976" s="1"/>
       <c r="AC976" s="1"/>
     </row>
-    <row r="977" spans="1:29" ht="13.2">
+    <row r="977" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -31470,7 +31463,7 @@
       <c r="AB977" s="1"/>
       <c r="AC977" s="1"/>
     </row>
-    <row r="978" spans="1:29" ht="13.2">
+    <row r="978" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -31501,7 +31494,7 @@
       <c r="AB978" s="1"/>
       <c r="AC978" s="1"/>
     </row>
-    <row r="979" spans="1:29" ht="13.2">
+    <row r="979" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -31532,7 +31525,7 @@
       <c r="AB979" s="1"/>
       <c r="AC979" s="1"/>
     </row>
-    <row r="980" spans="1:29" ht="13.2">
+    <row r="980" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -31563,7 +31556,7 @@
       <c r="AB980" s="1"/>
       <c r="AC980" s="1"/>
     </row>
-    <row r="981" spans="1:29" ht="13.2">
+    <row r="981" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -31594,7 +31587,7 @@
       <c r="AB981" s="1"/>
       <c r="AC981" s="1"/>
     </row>
-    <row r="982" spans="1:29" ht="13.2">
+    <row r="982" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -31625,7 +31618,7 @@
       <c r="AB982" s="1"/>
       <c r="AC982" s="1"/>
     </row>
-    <row r="983" spans="1:29" ht="13.2">
+    <row r="983" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -31656,7 +31649,7 @@
       <c r="AB983" s="1"/>
       <c r="AC983" s="1"/>
     </row>
-    <row r="984" spans="1:29" ht="13.2">
+    <row r="984" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -31687,7 +31680,7 @@
       <c r="AB984" s="1"/>
       <c r="AC984" s="1"/>
     </row>
-    <row r="985" spans="1:29" ht="13.2">
+    <row r="985" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -31718,7 +31711,7 @@
       <c r="AB985" s="1"/>
       <c r="AC985" s="1"/>
     </row>
-    <row r="986" spans="1:29" ht="13.2">
+    <row r="986" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -31749,7 +31742,7 @@
       <c r="AB986" s="1"/>
       <c r="AC986" s="1"/>
     </row>
-    <row r="987" spans="1:29" ht="13.2">
+    <row r="987" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -31780,7 +31773,7 @@
       <c r="AB987" s="1"/>
       <c r="AC987" s="1"/>
     </row>
-    <row r="988" spans="1:29" ht="13.2">
+    <row r="988" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -31811,7 +31804,7 @@
       <c r="AB988" s="1"/>
       <c r="AC988" s="1"/>
     </row>
-    <row r="989" spans="1:29" ht="13.2">
+    <row r="989" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -31842,7 +31835,7 @@
       <c r="AB989" s="1"/>
       <c r="AC989" s="1"/>
     </row>
-    <row r="990" spans="1:29" ht="13.2">
+    <row r="990" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -31873,7 +31866,7 @@
       <c r="AB990" s="1"/>
       <c r="AC990" s="1"/>
     </row>
-    <row r="991" spans="1:29" ht="13.2">
+    <row r="991" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -31904,7 +31897,7 @@
       <c r="AB991" s="1"/>
       <c r="AC991" s="1"/>
     </row>
-    <row r="992" spans="1:29" ht="13.2">
+    <row r="992" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -31935,7 +31928,7 @@
       <c r="AB992" s="1"/>
       <c r="AC992" s="1"/>
     </row>
-    <row r="993" spans="1:29" ht="13.2">
+    <row r="993" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -31966,7 +31959,7 @@
       <c r="AB993" s="1"/>
       <c r="AC993" s="1"/>
     </row>
-    <row r="994" spans="1:29" ht="13.2">
+    <row r="994" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -31997,7 +31990,7 @@
       <c r="AB994" s="1"/>
       <c r="AC994" s="1"/>
     </row>
-    <row r="995" spans="1:29" ht="13.2">
+    <row r="995" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -32028,7 +32021,7 @@
       <c r="AB995" s="1"/>
       <c r="AC995" s="1"/>
     </row>
-    <row r="996" spans="1:29" ht="13.2">
+    <row r="996" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -32059,7 +32052,7 @@
       <c r="AB996" s="1"/>
       <c r="AC996" s="1"/>
     </row>
-    <row r="997" spans="1:29" ht="13.2">
+    <row r="997" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -32090,7 +32083,7 @@
       <c r="AB997" s="1"/>
       <c r="AC997" s="1"/>
     </row>
-    <row r="998" spans="1:29" ht="13.2">
+    <row r="998" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -32121,7 +32114,7 @@
       <c r="AB998" s="1"/>
       <c r="AC998" s="1"/>
     </row>
-    <row r="999" spans="1:29" ht="13.2">
+    <row r="999" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -32152,7 +32145,7 @@
       <c r="AB999" s="1"/>
       <c r="AC999" s="1"/>
     </row>
-    <row r="1000" spans="1:29" ht="13.2">
+    <row r="1000" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -32183,7 +32176,7 @@
       <c r="AB1000" s="1"/>
       <c r="AC1000" s="1"/>
     </row>
-    <row r="1001" spans="1:29" ht="13.2">
+    <row r="1001" spans="1:29" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B70D5A4-DD5C-4205-A377-E45B698C91CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB0E77D-B4C8-4DD9-9FE4-0F27352BC083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -247,7 +247,7 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Leave a fire trail when moving, dealing {Skilldamage} damage to the enemy within</t>
+          <t xml:space="preserve">Leave a fire trail when moving, dealing </t>
         </r>
         <r>
           <rPr>
@@ -257,7 +257,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve"> per second</t>
+          <t xml:space="preserve">ball's attack </t>
         </r>
         <r>
           <rPr>
@@ -266,7 +266,69 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">. The trial will last {Skillduration} seconds.
+          <t>damage to the enemy within</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> per x second</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">. The trial will last </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">y </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">seconds.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Variables needed: 
+{LeaveDuration}: float, the duration of the ball leaving the trail, unit in seconds.
+{TrailDuration}: float, the duration of the fire trail, unit in seconds.
+{DamageFrequency}: float, the amount of time required for the trail to calculate damage once, unit in seconds.
+{TrailSize}:  The trail's width, unit in scale. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -280,7 +342,7 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The pinball will split into {Skill</t>
+          <t xml:space="preserve">The pinball will split into </t>
         </r>
         <r>
           <rPr>
@@ -290,7 +352,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>effect</t>
+          <t>x</t>
         </r>
         <r>
           <rPr>
@@ -299,7 +361,7 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">} balls, each ball </t>
+          <t xml:space="preserve"> balls, each ball </t>
         </r>
         <r>
           <rPr>
@@ -310,6 +372,9 @@
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">cannot be split again further.
+Variables needed:
+{SplitCount}: int, The number of balls that the origin ball split into.
+{SplitSize}: int, The size of the splitted balls, unit in scale.
 </t>
         </r>
       </text>
@@ -323,7 +388,87 @@
             <rFont val="Arial"/>
             <scheme val="minor"/>
           </rPr>
-          <t>When the skill triggers, the ball will shoot out a ring of spikes, dealing {Skilldamage} amount of damage to enemies hit. The spike can travel {Skilldistance}, and ignore terrains.</t>
+          <t xml:space="preserve">When the skill triggers, the ball will shoot out a ring of spikes, dealing </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ball's attack </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">damage to enemies hit. The spike </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>lasts x seconds as they travel</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>, and ignore terrains.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (each ring of spikes contains 16 of them(or 8 if optimization becomes an issue)).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>{SpikeSpeed}: float, the speed of the flying spikes.
+{SpikeSize}: float, the size of the flying spikes.
+{SpikeDuration}: float, the duration of the spike before it disappears.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -347,7 +492,10 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Enemies within the area's movement speed will be reduced to zero. The area effect is {Skilleffect}(size multiplier), and the zone lasts{Skillduration}.</t>
+Enemies within the area's movement speed will be reduced to zero. The area effect is x , and the zone lasts y.
+variables needed:
+{ZoneSize}: float, the size of the vfx/area of the icezone, unit in scale.
+{ZoneDuration}: int, the duration of the zone, unit in seconds.</t>
         </r>
       </text>
     </comment>
@@ -371,7 +519,37 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Summons an invisible area surrounding the ball. The area will strike down lightning bolts to enemies contacted, dealing ball's base attack value to them. The area size is {Skilleffect}, and lasts {Skillduration}.</t>
+Summons an invisible area surrounding the ball. The area will strike down lightning bolts to enemies contacted, dealing ball's attack value to them. The area size is x, and lasts y.
+varaibles needed:
+{LightningSize}: float, the detection size of the thunder area, unit in scale.
+{LightningDuration}: float, the duration of the skill.
+{LightningFreq}: float, the cooldown of the thunders on each individual enemies, unit in seconds.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="1" shapeId="0" xr:uid="{18C1C359-D740-41E3-BF5F-1F545E62F512}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Hannya T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unleashes a burst from the ball's current location. The burst will stay at the location where's it's triggered, and does not move with the ball. The burst only deal damage once, and disappears as the vfx fades.
+Varaibles needed:
+{CrystalSize}: float, the size of the burst, unit in scale.</t>
         </r>
       </text>
     </comment>
@@ -380,7 +558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -555,33 +733,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Uses </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plexus AoE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as skill effect vfx.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FireTrail</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -622,6 +773,116 @@
   </si>
   <si>
     <t>Drops a fire trail that deals ball's attack damage to enemies within overtime.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Crystals crossfade 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as skill effect vfx.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrystalBall</t>
+  </si>
+  <si>
+    <t>CrystalBall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrystalCrash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Summons a crystal burst at the ball's current location, dealing ball's attack damage to enemies within.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Attach </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Lightning aura </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to the ball</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">during skill duraton, and Uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Plexus AoE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as skill effect vfx.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -945,7 +1206,7 @@
   <cols>
     <col min="11" max="11" width="14.6640625" customWidth="1"/>
     <col min="13" max="13" width="69.33203125" customWidth="1"/>
-    <col min="15" max="15" width="36.21875" customWidth="1"/>
+    <col min="15" max="15" width="38.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1193,7 +1454,7 @@
         <v>500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
@@ -1205,13 +1466,13 @@
         <v>25</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1249,7 +1510,7 @@
         <v>0.75</v>
       </c>
       <c r="H7" s="1">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>19</v>
@@ -1264,7 +1525,7 @@
         <v>27</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1485,7 +1746,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="K11" s="1">
         <v>30</v>
@@ -1494,13 +1755,13 @@
         <v>39</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>43</v>
+      <c r="O11" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1517,22 +1778,48 @@
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="B12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>500</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="1">
+        <v>650</v>
+      </c>
+      <c r="K12" s="1">
+        <v>30</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="O12" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB0E77D-B4C8-4DD9-9FE4-0F27352BC083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B185303B-3968-4679-881E-7E83030467D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1448,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H6" s="1">
         <v>500</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B185303B-3968-4679-881E-7E83030467D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A845CE-BAF4-4098-B5C3-D462411333F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H7" s="1">
         <v>7000</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A845CE-BAF4-4098-B5C3-D462411333F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA54106-AA6F-46CD-9264-5DCA215A8596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1451,7 +1451,7 @@
         <v>0.8</v>
       </c>
       <c r="H6" s="1">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>43</v>
@@ -1567,7 +1567,7 @@
         <v>1.35</v>
       </c>
       <c r="H8" s="1">
-        <v>700</v>
+        <v>4000</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>41</v>
@@ -1681,7 +1681,7 @@
         <v>1.25</v>
       </c>
       <c r="H10" s="1">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>42</v>
@@ -1740,7 +1740,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>900</v>
+        <v>4000</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>40</v>
@@ -1799,7 +1799,7 @@
         <v>1.25</v>
       </c>
       <c r="H12" s="1">
-        <v>500</v>
+        <v>5500</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>51</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA54106-AA6F-46CD-9264-5DCA215A8596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1D0388-752B-4AF6-8F2B-EFFCD0526A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
         <v>1.5</v>
       </c>
       <c r="G5" s="1">
-        <v>1.1499999999999999</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H6" s="1">
         <v>3500</v>
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>1.1000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="H7" s="1">
         <v>7000</v>
@@ -1737,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>1.1499999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="H11" s="1">
         <v>4000</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1D0388-752B-4AF6-8F2B-EFFCD0526A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CF6A01-29F7-4607-8AC4-EAF846F17019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -639,10 +639,6 @@
   </si>
   <si>
     <t>Fireball</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -966,15 +962,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1247,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="1"/>
@@ -1423,11 +1416,14 @@
       <c r="K5" s="1">
         <v>80</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>26</v>
+      <c r="L5" s="1" t="s">
+        <v>16</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>31</v>
+      <c r="M5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1454,7 +1450,7 @@
         <v>3500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
@@ -1465,14 +1461,14 @@
       <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>47</v>
+      <c r="M6" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1522,10 +1518,10 @@
         <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>45</v>
+      <c r="M7" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1570,7 +1566,7 @@
         <v>4000</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
@@ -1581,8 +1577,8 @@
       <c r="L8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>32</v>
+      <c r="M8" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>20</v>
@@ -1606,7 +1602,7 @@
     <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
@@ -1636,14 +1632,14 @@
       <c r="L9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1663,7 +1659,7 @@
     <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -1684,7 +1680,7 @@
         <v>3000</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J10" s="1">
         <v>200</v>
@@ -1693,16 +1689,16 @@
         <v>70</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1722,7 +1718,7 @@
     <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1">
         <v>17</v>
@@ -1743,7 +1739,7 @@
         <v>4000</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="1">
         <v>600</v>
@@ -1752,16 +1748,16 @@
         <v>30</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>46</v>
+      <c r="M11" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>53</v>
+      <c r="O11" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1781,7 +1777,7 @@
     <row r="12" spans="1:29" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1">
         <v>25</v>
@@ -1802,7 +1798,7 @@
         <v>5500</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J12" s="1">
         <v>650</v>
@@ -1811,14 +1807,16 @@
         <v>30</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>52</v>
+      <c r="M12" s="4" t="s">
+        <v>51</v>
       </c>
-      <c r="N12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="O12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CF6A01-29F7-4607-8AC4-EAF846F17019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C72AFE-6009-4EB8-B94C-DE324ECDADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -621,9 +621,6 @@
   </si>
   <si>
     <t>Spikeball</t>
-  </si>
-  <si>
-    <t>Radiantball</t>
   </si>
   <si>
     <t>float</t>
@@ -1237,13 +1234,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="1"/>
@@ -1272,16 +1269,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -1296,13 +1293,13 @@
         <v>13</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -1420,7 +1417,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>16</v>
@@ -1450,25 +1447,25 @@
         <v>3500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="1">
         <v>250</v>
       </c>
       <c r="K6" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1515,13 +1512,13 @@
         <v>400</v>
       </c>
       <c r="K7" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1566,7 +1563,7 @@
         <v>4000</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
@@ -1578,7 +1575,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>20</v>
@@ -1602,7 +1599,7 @@
     <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
@@ -1627,19 +1624,19 @@
         <v>300</v>
       </c>
       <c r="K9" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>21</v>
+      <c r="L9" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="M9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1659,7 +1656,7 @@
     <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -1680,25 +1677,25 @@
         <v>3000</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>200</v>
       </c>
       <c r="K10" s="1">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1718,7 +1715,7 @@
     <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1">
         <v>17</v>
@@ -1739,7 +1736,7 @@
         <v>4000</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J11" s="1">
         <v>600</v>
@@ -1748,16 +1745,16 @@
         <v>30</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1777,7 +1774,7 @@
     <row r="12" spans="1:29" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1">
         <v>25</v>
@@ -1798,7 +1795,7 @@
         <v>5500</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" s="1">
         <v>650</v>
@@ -1807,16 +1804,16 @@
         <v>30</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C72AFE-6009-4EB8-B94C-DE324ECDADFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD65FEBE-BE8C-426C-A68F-81D08BAFEFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1801,7 +1801,7 @@
         <v>650</v>
       </c>
       <c r="K12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>47</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD65FEBE-BE8C-426C-A68F-81D08BAFEFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D82358-F96C-41B1-B4BA-E9B85BDCB449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1627,7 +1627,7 @@
         <v>40</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>31</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D82358-F96C-41B1-B4BA-E9B85BDCB449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0369997-52D1-46BC-81C4-72D4CBD61B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -648,10 +648,6 @@
   </si>
   <si>
     <t>BallIcon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stentball</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1408,7 +1404,7 @@
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K5" s="1">
         <v>80</v>
@@ -1417,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>16</v>
@@ -1447,10 +1443,10 @@
         <v>3500</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K6" s="1">
         <v>40</v>
@@ -1459,13 +1455,13 @@
         <v>24</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1509,7 +1505,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="1">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K7" s="1">
         <v>20</v>
@@ -1518,7 +1514,7 @@
         <v>25</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>18</v>
@@ -1563,19 +1559,19 @@
         <v>4000</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1">
         <v>500</v>
       </c>
       <c r="K8" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>20</v>
@@ -1599,7 +1595,7 @@
     <row r="9" spans="1:29" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1">
         <v>15</v>
@@ -1621,22 +1617,22 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K9" s="1">
         <v>40</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1656,7 +1652,7 @@
     <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>13</v>
@@ -1677,7 +1673,7 @@
         <v>3000</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="1">
         <v>200</v>
@@ -1686,16 +1682,16 @@
         <v>40</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1715,7 +1711,7 @@
     <row r="11" spans="1:29" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1">
         <v>17</v>
@@ -1736,25 +1732,25 @@
         <v>4000</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" s="1">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="K11" s="1">
         <v>30</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1774,7 +1770,7 @@
     <row r="12" spans="1:29" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1">
         <v>25</v>
@@ -1795,7 +1791,7 @@
         <v>5500</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J12" s="1">
         <v>650</v>
@@ -1804,16 +1800,16 @@
         <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0369997-52D1-46BC-81C4-72D4CBD61B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DD02A2-B0F3-440C-84E6-2678721637BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1565,7 +1565,7 @@
         <v>500</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>20</v>
@@ -1797,7 +1797,7 @@
         <v>650</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>46</v>

--- a/LubanConfig/DataTables/Datas/#BallParam.xlsx
+++ b/LubanConfig/DataTables/Datas/#BallParam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\monster-ball\LubanConfig\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5E7E1D-C27C-4673-B724-F29D02AA7FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DB818E-45B9-438B-A005-31BB2D56E186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,7 +388,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -708,23 +708,11 @@
     <t>Behold, the mighty FullBall!</t>
   </si>
   <si>
-    <t>NucelarBall</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>NuclearRaindown</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CrystalCrash</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>NuclearBall</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Randomly calls down 3 missile bombarding areas on the map that deals damage over time to the enemies within.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -752,6 +740,18 @@
       </rPr>
       <t>as skill effect vfx.</t>
     </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuclearball</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystalball</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Randomly calls down missile bombarding areas on the map that deals damage over time to the enemies within.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1682,7 +1682,7 @@
         <v>5500</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="1">
         <v>650</v>
@@ -1697,7 +1697,7 @@
         <v>44</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>45</v>
@@ -1808,7 +1808,9 @@
       <c r="M14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -1843,7 +1845,7 @@
         <v>1.5</v>
       </c>
       <c r="G15" s="1">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1861,7 +1863,9 @@
       <c r="M15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -1881,7 +1885,7 @@
     <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C16" s="1">
         <v>20</v>
@@ -1896,16 +1900,16 @@
         <v>0.8</v>
       </c>
       <c r="G16" s="1">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H16" s="1">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J16" s="1">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="K16" s="1">
         <v>20</v>
@@ -1914,13 +1918,13 @@
         <v>55</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>55</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
